--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,16 +35,16 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
-    </font>
-    <font>
       <color rgb="000CA30C"/>
     </font>
     <font>
       <color rgb="00898781"/>
     </font>
+    <font>
+      <color rgb="00D03B3B"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,22 +74,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -536,49 +550,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>5151</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HEXTAR</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>-0.006500000000000001</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>14129100</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H2" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1917800</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 60.15未超买，现价高于50日均线约11.8%，技术面信号较为可靠。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,42 +610,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E3" s="8" t="n">
+          <t>Nwe Resources Group Bhd</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>12199600</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H3" t="n">
-        <v>24.46</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.297</v>
-      </c>
+      <c r="F3" s="11" t="n">
+        <v>39260800</v>
+      </c>
+      <c r="G3" s="12" t="n"/>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="n"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,42 +646,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-0.0106</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>4656000</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.14</v>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>16882100</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.04</v>
       </c>
       <c r="H4" t="n">
-        <v>79.34</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.294</v>
+        <v>24.46</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.297</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,42 +691,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>4375600</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.05</v>
+          <t>TANCO</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>13112900</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.97</v>
       </c>
       <c r="H5" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.261</v>
+        <v>37.84</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.184</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -731,34 +744,34 @@
           <t>GIIB</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-0.0071</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>2824700</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.11</v>
+      <c r="D6" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>10475900</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.41</v>
       </c>
       <c r="H6" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+        <v>80.62</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.542</v>
+      <c r="J6" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.543</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,42 +781,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DNEX</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0.0241</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>1092600</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.03</v>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>-0.0278</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>10166400</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0.47</v>
       </c>
       <c r="H7" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.48</v>
+        <v>41.19</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.186</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -813,42 +826,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DESTINI</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1006000</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>3.96</v>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>8677500</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.25</v>
       </c>
       <c r="H8" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0.243</v>
+        <v>79.34</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.294</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -858,42 +871,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.635</v>
+          <t>VELOCITY</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.075</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.29</v>
+        <v>0</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>8110300</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>7.96</v>
       </c>
       <c r="H9" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+        <v>59.28</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.625</v>
+      <c r="J9" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.06900000000000001</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -903,45 +916,2146 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>6630500</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H10" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2259</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TALAMT</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>6450100</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H11" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>6222500</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>4858800</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5253</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ECONBHD</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>4267100</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H14" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>3853100</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H15" t="n">
+        <v>37.59</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>3528400</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H16" t="n">
+        <v>61.51</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>3092700</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H17" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AVANGAAD</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>2540000</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H18" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>2509800</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H19" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>2.723</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>2.867</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>7113</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>TOPGLOV</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.005500000000000001</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>503200</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H10" t="n">
-        <v>67.05</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="D20" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>2343500</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H20" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
-        <v>0.843</v>
-      </c>
-      <c r="K10" s="2" t="n">
+      <c r="J20" s="9" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>0.748</v>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" s="7" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>2176900</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>1967100</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H22" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>1862100</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>1635600</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>4.881</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>4.742</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>1547800</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H25" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>1.947</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>1.765</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>1440600</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H26" t="n">
+        <v>47.64</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1309300</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H27" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>1295000</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H28" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>1268500</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H29" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>1236800</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H30" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>1220900</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H31" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>4.726</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>4.832</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>1193200</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H32" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1180900</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H33" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DATASONIC</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>1139600</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>45</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>1124800</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H35" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>2.911</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>1120800</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H36" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>1086600</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H37" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>2.234</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BNASTRA</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>1080100</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>2.452</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>1078900</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H39" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>1069900</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H40" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>7.439</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>7.659</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7212</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DESTINI</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>1040400</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="H41" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>1010700</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H42" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>992100</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H43" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>5.482</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>940000</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H44" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>937700</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>909400</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H46" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>868200</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H47" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>856900</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H48" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>829300</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H49" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>815400</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H50" t="n">
+        <v>44.61</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>2.743</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>644200</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>614800</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>604500</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H53" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>3.689</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>3.103</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>589800</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H55" t="n">
+        <v>58.26</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>540700</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>517800</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H57" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>1.757</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.425</v>
+        <v>0.42</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0241</v>
+        <v>0.012</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1917800</v>
+        <v>2651400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>60.15</v>
+        <v>58.95</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.397</v>
+        <v>0.396</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.38</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 60.15未超买，现价高于50日均线约11.8%，技术面信号较为可靠。</t>
+          <t>SAR转多信号，RSI 58.95未超买，现价高于50日均线约10.5%，技术面信号较为可靠。</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>39260800</v>
+        <v>40509500</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -661,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>16882100</v>
+        <v>18734200</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H4" t="n">
         <v>24.46</v>
@@ -706,10 +706,10 @@
         <v>0.0345</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>13112900</v>
+        <v>13362200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H5" t="n">
         <v>37.84</v>
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.71</v>
+        <v>0.715</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.0071</v>
+        <v>0.0142</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>10475900</v>
+        <v>12291100</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="H6" t="n">
-        <v>80.62</v>
+        <v>81.19</v>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.634</v>
+        <v>0.635</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.543</v>
@@ -781,39 +781,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>-0.0278</v>
+        <v>0.92</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.011</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>10166400</v>
+        <v>11511200</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.47</v>
+        <v>0.16</v>
       </c>
       <c r="H7" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.187</v>
+        <v>0.843</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.186</v>
+        <v>0.748</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -826,39 +826,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>-0.0106</v>
+        <v>0.18</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>8677500</v>
+        <v>10226400</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
       <c r="H8" t="n">
-        <v>79.34</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.11</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.4</v>
+        <v>0.187</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.294</v>
+        <v>0.186</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -871,28 +871,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>8110300</v>
+        <v>8739000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>7.96</v>
+        <v>0.25</v>
       </c>
       <c r="H9" t="n">
-        <v>59.28</v>
+        <v>79.34</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.294</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -916,39 +916,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.14</v>
+        <v>0.075</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>6630500</v>
+        <v>8110800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.11</v>
+        <v>7.96</v>
       </c>
       <c r="H10" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.28</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.155</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.142</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,28 +961,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TALAMT</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>6450100</v>
+        <v>7117900</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>4.74</v>
+        <v>0.09</v>
       </c>
       <c r="H11" t="n">
-        <v>44.56</v>
+        <v>66.27</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.078</v>
+        <v>0.31</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.081</v>
+        <v>0.261</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.0152</v>
+        <v>0.14</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>6222500</v>
+        <v>6682700</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H12" t="n">
-        <v>64.98999999999999</v>
+        <v>42.15</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.31</v>
+        <v>0.155</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.261</v>
+        <v>0.142</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,33 +1051,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>TALAMT</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.0204</v>
+        <v>0.075</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>4858800</v>
+        <v>6658300</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.21</v>
+        <v>4.89</v>
+      </c>
+      <c r="H13" t="n">
+        <v>44.56</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
+      <c r="J13" s="9" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.081</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
     </row>
@@ -1089,40 +1096,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.0417</v>
+        <v>0.0204</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>4267100</v>
+        <v>5763800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H14" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>0.124</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
     </row>
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.28</v>
+        <v>0.275</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.0566</v>
+        <v>0.0377</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>3853100</v>
+        <v>4889500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="H15" t="n">
-        <v>37.59</v>
+        <v>35.22</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.97</v>
+        <v>0.955</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>0.0601</v>
+        <v>0.0437</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3528400</v>
+        <v>4784700</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="H16" t="n">
-        <v>61.51</v>
+        <v>60.78</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.859</v>
+        <v>0.858</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0.6</v>
@@ -1224,28 +1224,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.0361</v>
+        <v>0.12</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>3092700</v>
+        <v>4336600</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.08</v>
+        <v>1.19</v>
       </c>
       <c r="H17" t="n">
-        <v>37.98</v>
+        <v>44.15</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.467</v>
+        <v>0.122</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.48</v>
+        <v>0.124</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1269,28 +1269,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0</v>
+        <v>2.43</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0611</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2540000</v>
+        <v>4307800</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="H18" t="n">
-        <v>49.15</v>
+        <v>35.27</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.295</v>
+        <v>2.728</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.295</v>
+        <v>2.868</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.0393</v>
+        <v>4.72</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>2509800</v>
+        <v>4103300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.49</v>
+        <v>0.2</v>
       </c>
       <c r="H19" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.71</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2.723</v>
+        <v>4.728</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>2.867</v>
+        <v>4.832</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1359,39 +1359,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>0.57</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.027</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>2343500</v>
+        <v>3914500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="H20" t="n">
-        <v>66.47</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.13</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.842</v>
+        <v>0.571</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.748</v>
+        <v>0.544</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1404,28 +1404,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.018</v>
+        <v>0.295</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2176900</v>
+        <v>3855100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.11</v>
+        <v>1.15</v>
       </c>
       <c r="H21" t="n">
-        <v>50.16</v>
+        <v>49.15</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.571</v>
+        <v>0.295</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.544</v>
+        <v>0.295</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1449,28 +1449,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.011</v>
+        <v>0.0225</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>1967100</v>
+        <v>3627800</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H22" t="n">
-        <v>42.02</v>
+        <v>60.16</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.508</v>
+        <v>0.428</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.465</v>
+        <v>0.375</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1494,39 +1494,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.175</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1862100</v>
+        <v>3621800</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.12</v>
+        <v>0.65</v>
       </c>
       <c r="H23" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.775</v>
+        <v>0.174</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.776</v>
+        <v>0.181</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,39 +1539,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>4.81</v>
+        <v>0.775</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.0126</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1635600</v>
+        <v>3600100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="H24" t="n">
-        <v>47.25</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.16</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>4.881</v>
+        <v>0.775</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>4.742</v>
+        <v>0.776</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,39 +1584,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2.04</v>
+        <v>0.435</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.0482</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1547800</v>
+        <v>3518000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H25" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.67</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.947</v>
+        <v>0.468</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.765</v>
+        <v>0.48</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,28 +1629,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.0118</v>
+        <v>0.265</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1440600</v>
+        <v>2682300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="H26" t="n">
-        <v>47.64</v>
+        <v>38.25</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.63</v>
+        <v>0.292</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.56</v>
+        <v>0.28</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1674,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0308</v>
+        <v>0.82</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1309300</v>
+        <v>2626200</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H27" t="n">
-        <v>47.84</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.6</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.343</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.335</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,28 +1719,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>0.79</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.026</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1295000</v>
+        <v>2598000</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.08</v>
+        <v>0.98</v>
       </c>
       <c r="H28" t="n">
-        <v>55.6</v>
+        <v>59.75</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.744</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.707</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,28 +1764,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.655</v>
+        <v>0.46</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.0315</v>
+        <v>0.011</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1268500</v>
+        <v>2257300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="H29" t="n">
-        <v>38.75</v>
+        <v>42.02</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.739</v>
+        <v>0.508</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.465</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,28 +1809,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.84</v>
+        <v>4.79</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.0307</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1236800</v>
+        <v>2178300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.35</v>
+        <v>0.09</v>
       </c>
       <c r="H30" t="n">
-        <v>53.97</v>
+        <v>46.13</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.826</v>
+        <v>4.879</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.789</v>
+        <v>4.741</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>-0.0063</v>
+        <v>0.765</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1220900</v>
+        <v>2051400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="H31" t="n">
-        <v>46.14</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.57</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>4.726</v>
+        <v>0.769</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4.832</v>
+        <v>0.771</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>0.0213</v>
+        <v>0.63</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>1193200</v>
+        <v>1979900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="H32" t="n">
-        <v>41.22</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.032</v>
+        <v>0.62</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.969</v>
+        <v>0.616</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.535</v>
+        <v>2.04</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0303</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1180900</v>
+        <v>1959500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.94</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.626</v>
+        <v>1.947</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.618</v>
+        <v>1.765</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,28 +1989,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.275</v>
+        <v>0.55</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.0185</v>
+        <v>0.0377</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>1139600</v>
+        <v>1898300</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H34" t="n">
-        <v>45</v>
+        <v>36.2</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.287</v>
+        <v>0.627</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.283</v>
+        <v>0.619</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,39 +2034,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>3.28</v>
+        <v>0.965</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>0.0061</v>
+        <v>0.0266</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1124800</v>
+        <v>1880000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="H35" t="n">
-        <v>86.72</v>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.97</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>2.911</v>
+        <v>1.032</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>2.484</v>
+        <v>0.969</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,39 +2079,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>3.81</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>-0.0206</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>1120800</v>
+        <v>1848700</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="H36" t="n">
-        <v>61.94</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.14</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.212</v>
+        <v>3.688</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.196</v>
+        <v>3.103</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,39 +2124,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>-0.005</v>
+        <v>3.29</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1086600</v>
+        <v>1764200</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.09</v>
+        <v>0.55</v>
       </c>
       <c r="H37" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.91</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.123</v>
+        <v>2.912</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.234</v>
+        <v>2.484</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>-0.0036</v>
+        <v>2.59</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1080100</v>
+        <v>1703100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.8</v>
+        <v>0.09</v>
       </c>
       <c r="H38" t="n">
-        <v>74.44</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.28</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
         <v>2.631</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.452</v>
+        <v>2.56</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,28 +2214,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0294</v>
+        <v>2.02</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1078900</v>
+        <v>1697700</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0.14</v>
       </c>
       <c r="H39" t="n">
-        <v>50.72</v>
+        <v>33.19</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.352</v>
+        <v>2.124</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.328</v>
+        <v>2.235</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,28 +2259,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>7.14</v>
+        <v>0.39</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>-0.0014</v>
+        <v>-0.025</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1069900</v>
+        <v>1648100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H40" t="n">
-        <v>32.57</v>
+        <v>27.8</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>7.439</v>
+        <v>0.499</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>7.659</v>
+        <v>0.601</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,39 +2304,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DESTINI</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+        <v>0.475</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0215</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1040400</v>
+        <v>1642300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>4.09</v>
+        <v>0.71</v>
       </c>
       <c r="H41" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.75</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.229</v>
+        <v>0.427</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.243</v>
+        <v>0.434</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2349,28 +2349,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.765</v>
+        <v>0.66</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.0394</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1010700</v>
+        <v>1515600</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="H42" t="n">
-        <v>48.57</v>
+        <v>39.58</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.769</v>
+        <v>0.74</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.771</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,28 +2394,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.0075</v>
+        <v>0.84</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0307</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>992100</v>
+        <v>1515000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.08</v>
+        <v>0.43</v>
       </c>
       <c r="H43" t="n">
-        <v>40.9</v>
+        <v>53.97</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>5.467</v>
+        <v>0.826</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>5.482</v>
+        <v>0.789</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2439,39 +2439,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.255</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>940000</v>
+        <v>1503800</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
       <c r="H44" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.73</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.636</v>
+        <v>0.272</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.625</v>
+        <v>0.298</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2484,33 +2484,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.775</v>
+        <v>0.335</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>0.0131</v>
+        <v>0.0308</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>937700</v>
+        <v>1503200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
+      </c>
+      <c r="H45" t="n">
+        <v>47.84</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="9" t="n"/>
+      <c r="J45" s="9" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0.335</v>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
     </row>
@@ -2522,39 +2529,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.415</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.0641</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>909400</v>
+        <v>1423500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="H46" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.93</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.62</v>
+        <v>0.394</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.616</v>
+        <v>0.363</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,28 +2574,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>0.0305</v>
+        <v>0.25</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>868200</v>
+        <v>1377100</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="H47" t="n">
-        <v>41.84</v>
+        <v>38.79</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2596,10 +2603,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.91</v>
+        <v>0.269</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.853</v>
+        <v>0.29</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,28 +2619,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.58</v>
+        <v>7.16</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>0.0118</v>
+        <v>0.0014</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>856900</v>
+        <v>1354400</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H48" t="n">
-        <v>48.15</v>
+        <v>33.49</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2641,10 +2648,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.601</v>
+        <v>7.441</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.61</v>
+        <v>7.66</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,40 +2664,33 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.585</v>
+        <v>0.77</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>0.0446</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>829300</v>
+        <v>1314600</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H49" t="n">
-        <v>55.24</v>
+        <v>0.03</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J49" s="9" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="K49" s="9" t="n">
-        <v>0.476</v>
-      </c>
+      <c r="J49" s="9" t="n"/>
+      <c r="K49" s="9" t="n"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
     </row>
@@ -2702,39 +2702,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.68</v>
+        <v>1.29</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>0.0075</v>
+        <v>0.0157</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>815400</v>
+        <v>1310400</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H50" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.98</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.746</v>
+        <v>1.213</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.743</v>
+        <v>1.197</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>644200</v>
+        <v>1233800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H51" t="n">
-        <v>37.52</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.42</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.284</v>
+        <v>0.867</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.314</v>
+        <v>0.869</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.96</v>
+        <v>5.25</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>-0.0103</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>614800</v>
+        <v>1219800</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H52" t="n">
-        <v>62.05</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.58</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>5.466</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.882</v>
+        <v>5.482</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,28 +2837,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1.15</v>
+        <v>0.765</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.0268</v>
+        <v>0.0132</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>604500</v>
+        <v>1204400</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.13</v>
+        <v>0.91</v>
       </c>
       <c r="H53" t="n">
-        <v>62.11</v>
+        <v>60.12</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.07</v>
+        <v>0.749</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.721</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>-0.018</v>
+        <v>0.275</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>600000</v>
+        <v>1168300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H54" t="n">
-        <v>57.48</v>
+        <v>45</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>3.689</v>
+        <v>0.287</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>3.103</v>
+        <v>0.283</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>DESTINI</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0066</v>
+        <v>0.23</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>589800</v>
+        <v>1157300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.45</v>
+        <v>4.55</v>
       </c>
       <c r="H55" t="n">
-        <v>58.26</v>
+        <v>48.6</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.749</v>
+        <v>0.229</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.721</v>
+        <v>0.243</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,28 +2972,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>0.026</v>
+        <v>0.0268</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>540700</v>
+        <v>1148000</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H56" t="n">
-        <v>59.75</v>
+        <v>62.11</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.744</v>
+        <v>1.07</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.707</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,45 +3017,1215 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>2.76</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>517800</v>
+        <v>1138600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.08</v>
+        <v>0.84</v>
       </c>
       <c r="H57" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.65000000000001</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.69</v>
+        <v>2.63</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.757</v>
+        <v>2.452</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>1127200</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H58" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>1107500</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H59" t="n">
+        <v>38</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>1098600</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H60" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>2.747</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>2.743</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>1084300</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H61" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>1041500</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H62" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0298</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>WENTEL</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>1020300</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5336</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CKI</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>1016600</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H64" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>940000</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H65" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>925400</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H66" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>852700</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H67" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.008199999999999999</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>731100</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H68" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>726600</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H69" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>2.248</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>701600</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>53.66</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>656800</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H71" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>643500</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H72" t="n">
+        <v>65</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>636000</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H73" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>624400</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H74" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>1.874</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>612400</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>1.689</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>1.756</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>571000</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H76" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>570700</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H77" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>3.821</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>3.711</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>565900</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H78" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>1.918</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>557900</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H79" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>546600</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H80" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>519000</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H81" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>5.054</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>5.049</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>513900</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H82" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>1.994</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>505000</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H83" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M57"/>
+  <autoFilter ref="A1:M83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,9 +96,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.012</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2651400</v>
+        <v>3849000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>58.95</v>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>40509500</v>
+        <v>47131100</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -655,19 +655,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>18734200</v>
+        <v>23657500</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H4" t="n">
-        <v>24.46</v>
+        <v>23.84</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.297</v>
@@ -691,39 +691,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.915</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>13362200</v>
+        <v>16945400</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.98</v>
+        <v>0.23</v>
       </c>
       <c r="H5" t="n">
-        <v>37.84</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.05</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.155</v>
+        <v>0.843</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.184</v>
+        <v>0.748</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -736,39 +736,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.0142</v>
+        <v>0.155</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.06900000000000001</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>12291100</v>
+        <v>15800500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.48</v>
+        <v>1.16</v>
       </c>
       <c r="H6" t="n">
-        <v>81.19</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.27</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.635</v>
+        <v>0.155</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.543</v>
+        <v>0.184</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -781,39 +781,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.011</v>
+        <v>0.345</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>11511200</v>
+        <v>14014700</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H7" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.47</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.843</v>
+        <v>0.311</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.748</v>
+        <v>0.261</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -826,39 +826,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.055</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.1</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>10226400</v>
+        <v>13770800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.48</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>44.11</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.49</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.187</v>
+        <v>0.048</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.186</v>
+        <v>0.047</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -871,39 +871,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>-0.0106</v>
+        <v>0.715</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.0142</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>8739000</v>
+        <v>12816200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="H9" t="n">
-        <v>79.34</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
+        <v>81.19</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.4</v>
+        <v>0.635</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.294</v>
+        <v>0.543</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -916,39 +916,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>8110800</v>
+        <v>11903700</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>7.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>59.28</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.19</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.186</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,28 +961,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.145</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>7117900</v>
+        <v>11322300</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="H11" t="n">
-        <v>66.27</v>
+        <v>45.07</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.31</v>
+        <v>0.156</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.261</v>
+        <v>0.142</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,39 +1006,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>6682700</v>
+        <v>8924300</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="H12" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.34</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.155</v>
+        <v>0.4</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.142</v>
+        <v>0.294</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TALAMT</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
@@ -1066,24 +1066,24 @@
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6658300</v>
+        <v>8110800</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>4.89</v>
+        <v>7.96</v>
       </c>
       <c r="H13" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.28</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.081</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,33 +1096,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.0204</v>
+        <v>0.58</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.045</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>5763800</v>
+        <v>7619800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
+      </c>
+      <c r="H14" t="n">
+        <v>52.97</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="J14" s="9" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.545</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
     </row>
@@ -1134,28 +1141,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>TALAMT</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.0377</v>
+        <v>0.075</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>4889500</v>
+        <v>7050100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.73</v>
+        <v>5.18</v>
       </c>
       <c r="H15" t="n">
-        <v>35.22</v>
+        <v>44.56</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1163,10 +1170,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.307</v>
+        <v>0.078</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.331</v>
+        <v>0.081</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1179,39 +1186,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0.0437</v>
+        <v>1.29</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>4784700</v>
+        <v>6426000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="H16" t="n">
-        <v>60.78</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.98</v>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.858</v>
+        <v>1.213</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.6</v>
+        <v>1.197</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1224,40 +1231,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>4336600</v>
+        <v>6132300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="H17" t="n">
-        <v>44.15</v>
+        <v>0.27</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J17" s="9" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>0.124</v>
-      </c>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
     </row>
@@ -1269,28 +1269,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0611</v>
+        <v>0.43</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>4307800</v>
+        <v>5831400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.83</v>
+        <v>0.16</v>
       </c>
       <c r="H18" t="n">
-        <v>35.27</v>
+        <v>37.98</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2.728</v>
+        <v>0.467</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2.868</v>
+        <v>0.48</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>-0.0021</v>
+        <v>0.445</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4103300</v>
+        <v>5620500</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="H19" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.07</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>4.728</v>
+        <v>0.427</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>4.832</v>
+        <v>0.375</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1359,39 +1359,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.027</v>
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>3914500</v>
+        <v>5611800</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="H20" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.16</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.571</v>
+        <v>0.775</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.544</v>
+        <v>0.776</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1404,28 +1404,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>2.44</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0.0655</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>3855100</v>
+        <v>5311600</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="H21" t="n">
-        <v>49.15</v>
+        <v>35.8</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.295</v>
+        <v>2.729</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.295</v>
+        <v>2.868</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1449,28 +1449,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>0.0225</v>
+        <v>0.275</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0.0377</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3627800</v>
+        <v>5223700</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.17</v>
+        <v>0.77</v>
       </c>
       <c r="H22" t="n">
-        <v>60.16</v>
+        <v>35.22</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.428</v>
+        <v>0.307</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.375</v>
+        <v>0.331</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1494,28 +1494,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.955</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0.0437</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3621800</v>
+        <v>5198600</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.65</v>
+        <v>1.24</v>
       </c>
       <c r="H23" t="n">
-        <v>48.63</v>
+        <v>60.78</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.174</v>
+        <v>0.858</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.181</v>
+        <v>0.6</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,39 +1539,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.82</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3600100</v>
+        <v>4967600</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="H24" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
+        <v>55.6</v>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.775</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.776</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,39 +1584,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.435</v>
+        <v>4.72</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0482</v>
+        <v>-0.0021</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3518000</v>
+        <v>4747600</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="H25" t="n">
-        <v>39.67</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.71</v>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.468</v>
+        <v>4.728</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.48</v>
+        <v>4.832</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,39 +1629,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.125</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>2682300</v>
+        <v>4337600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.27</v>
+        <v>1.19</v>
       </c>
       <c r="H26" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.292</v>
+        <v>0.123</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.28</v>
+        <v>0.124</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1674,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.82</v>
+        <v>0.295</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2626200</v>
+        <v>3855100</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.16</v>
+        <v>1.15</v>
       </c>
       <c r="H27" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.295</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,39 +1719,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.026</v>
+        <v>0.175</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>2598000</v>
+        <v>3702800</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.98</v>
+        <v>0.66</v>
       </c>
       <c r="H28" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.744</v>
+        <v>0.174</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.707</v>
+        <v>0.181</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,39 +1764,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.011</v>
+        <v>0.48</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2257300</v>
+        <v>3618900</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.22</v>
+        <v>1.55</v>
       </c>
       <c r="H29" t="n">
-        <v>42.02</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.91</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.508</v>
+        <v>0.427</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.465</v>
+        <v>0.434</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,28 +1809,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.115</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>2178300</v>
+        <v>3475200</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H30" t="n">
-        <v>46.13</v>
+        <v>34.73</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>4.879</v>
+        <v>0.138</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>4.741</v>
+        <v>0.148</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,28 +1854,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0132</v>
+        <v>2.69</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0.0113</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2051400</v>
+        <v>3312000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H31" t="n">
-        <v>48.57</v>
+        <v>45.46</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.769</v>
+        <v>2.747</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.771</v>
+        <v>2.743</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.265</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>1979900</v>
+        <v>3275800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="H32" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.25</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.62</v>
+        <v>0.292</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.616</v>
+        <v>0.28</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.785</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1959500</v>
+        <v>3253500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="H33" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
+        <v>59.1</v>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.947</v>
+        <v>0.744</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.765</v>
+        <v>0.707</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,28 +1989,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>3250600</v>
+      </c>
+      <c r="G34" s="12" t="n">
         <v>0.55</v>
       </c>
-      <c r="E34" s="15" t="n">
-        <v>0.0377</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>1898300</v>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>0.2</v>
-      </c>
       <c r="H34" t="n">
-        <v>36.2</v>
+        <v>58.6</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.627</v>
+        <v>0.574</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.619</v>
+        <v>0.477</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.0266</v>
+        <v>0.765</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1880000</v>
+        <v>3064400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.22</v>
+        <v>0.38</v>
       </c>
       <c r="H35" t="n">
-        <v>41.97</v>
+        <v>48.57</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.032</v>
+        <v>0.769</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.969</v>
+        <v>0.771</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,28 +2079,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>-0.0206</v>
+        <v>2.03</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>1848700</v>
+        <v>3025400</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.23</v>
+        <v>0.92</v>
       </c>
       <c r="H36" t="n">
-        <v>57.14</v>
+        <v>46.01</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>3.688</v>
+        <v>2.042</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>3.103</v>
+        <v>2.068</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,39 +2124,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.0092</v>
+        <v>0.555</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.0472</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1764200</v>
+        <v>2852000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="H37" t="n">
-        <v>86.91</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.22</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.912</v>
+        <v>0.628</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.484</v>
+        <v>0.619</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.59</v>
+        <v>0.63</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.0157</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1703100</v>
+        <v>2806300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="H38" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>2.631</v>
+        <v>0.62</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.56</v>
+        <v>0.616</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,39 +2214,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1697700</v>
+        <v>2716400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="H39" t="n">
-        <v>33.19</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.94</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>2.124</v>
+        <v>1.947</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>2.235</v>
+        <v>1.765</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,28 +2259,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>-0.025</v>
+        <v>2.58</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1648100</v>
+        <v>2666100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H40" t="n">
-        <v>27.8</v>
+        <v>47.64</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.499</v>
+        <v>2.63</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.601</v>
+        <v>2.56</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,39 +2304,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.475</v>
+        <v>0.39</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.0215</v>
+        <v>-0.025</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1642300</v>
+        <v>2512200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.71</v>
+        <v>0.24</v>
       </c>
       <c r="H41" t="n">
-        <v>72.75</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.8</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.427</v>
+        <v>0.499</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.434</v>
+        <v>0.601</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2349,28 +2349,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>0.0394</v>
+        <v>4.78</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1515600</v>
+        <v>2472900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.29</v>
+        <v>0.1</v>
       </c>
       <c r="H42" t="n">
-        <v>39.58</v>
+        <v>45.54</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.74</v>
+        <v>4.878</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>4.741</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,28 +2394,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0307</v>
+        <v>0.46</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.011</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1515000</v>
+        <v>2469800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H43" t="n">
-        <v>53.97</v>
+        <v>42.02</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.826</v>
+        <v>0.508</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.789</v>
+        <v>0.465</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2439,28 +2439,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0</v>
+        <v>7.17</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>0.0028</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1503800</v>
+        <v>2399800</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H44" t="n">
-        <v>27.73</v>
+        <v>34.09</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.272</v>
+        <v>7.442</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.298</v>
+        <v>7.66</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2484,39 +2484,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.0308</v>
+        <v>0.38</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1503200</v>
+        <v>2336000</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="H45" t="n">
-        <v>47.84</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.97</v>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.343</v>
+        <v>0.372</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.335</v>
+        <v>0.37</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2529,39 +2529,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.0641</v>
+        <v>0.865</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1423500</v>
+        <v>2156800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="H46" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.09</v>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.394</v>
+        <v>0.868</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.363</v>
+        <v>0.869</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2574,28 +2574,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>2.01</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1377100</v>
+        <v>2148400</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="H47" t="n">
-        <v>38.79</v>
+        <v>32.39</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.269</v>
+        <v>2.123</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.29</v>
+        <v>2.234</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2619,28 +2619,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.0014</v>
+        <v>0.97</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0.0319</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1354400</v>
+        <v>2103500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="H48" t="n">
-        <v>33.49</v>
+        <v>42.7</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>7.441</v>
+        <v>1.032</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>7.66</v>
+        <v>0.969</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2664,33 +2664,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.83</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1314600</v>
+        <v>2097100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.03</v>
+        <v>0.6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>52.36</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J49" s="9" t="n"/>
-      <c r="K49" s="9" t="n"/>
+      <c r="J49" s="9" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.789</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
     </row>
@@ -2702,39 +2709,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.29</v>
+        <v>3.8</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>0.0157</v>
+        <v>-0.0231</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1310400</v>
+        <v>2055100</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.81</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.213</v>
+        <v>3.687</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1.197</v>
+        <v>3.103</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2754,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.0058</v>
+        <v>5.21</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>-0.017</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1233800</v>
+        <v>2006500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="H51" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.33</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.867</v>
+        <v>5.462</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.869</v>
+        <v>5.481</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,28 +2799,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.255</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>0.02</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1219800</v>
+        <v>1912600</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="H52" t="n">
-        <v>40.58</v>
+        <v>41.5</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2821,10 +2828,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>5.466</v>
+        <v>0.27</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>5.482</v>
+        <v>0.29</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,28 +2844,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.665</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0.0472</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1204400</v>
+        <v>1886900</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
       <c r="H53" t="n">
-        <v>60.12</v>
+        <v>40.39</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2866,10 +2873,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.749</v>
+        <v>0.74</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.721</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,39 +2889,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0.0185</v>
+        <v>3.31</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>0.0153</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1168300</v>
+        <v>1874700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="H54" t="n">
-        <v>45</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>87.28</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.287</v>
+        <v>2.914</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.283</v>
+        <v>2.484</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,28 +2934,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DESTINI</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1157300</v>
+        <v>1833300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>4.55</v>
+        <v>0.26</v>
       </c>
       <c r="H55" t="n">
-        <v>48.6</v>
+        <v>52.23</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2956,10 +2963,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.229</v>
+        <v>0.424</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.243</v>
+        <v>0.417</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,28 +2979,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.0268</v>
+        <v>0.67</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0.0388</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1148000</v>
+        <v>1802000</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H56" t="n">
-        <v>62.11</v>
+        <v>40.2</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3001,10 +3008,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.07</v>
+        <v>0.732</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,39 +3024,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>-0.0072</v>
+        <v>0.335</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1138600</v>
+        <v>1715000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.84</v>
+        <v>0.17</v>
       </c>
       <c r="H57" t="n">
-        <v>72.65000000000001</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.84</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.63</v>
+        <v>0.343</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.452</v>
+        <v>0.335</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,39 +3069,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0.0625</v>
+        <v>0.24</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1127200</v>
+        <v>1712300</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.19</v>
+        <v>4.92</v>
       </c>
       <c r="H58" t="n">
-        <v>56.42</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.31</v>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.572</v>
+        <v>0.226</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.476</v>
+        <v>0.225</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,28 +3114,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.2</v>
+        <v>0.255</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1107500</v>
+        <v>1698500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="H59" t="n">
-        <v>38</v>
+        <v>27.73</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3136,10 +3143,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.215</v>
+        <v>0.272</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.233</v>
+        <v>0.298</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,28 +3159,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.0113</v>
+        <v>0.41</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1098600</v>
+        <v>1693000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="H60" t="n">
-        <v>45.46</v>
+        <v>55.11</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3181,10 +3188,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.747</v>
+        <v>0.393</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.743</v>
+        <v>0.363</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3204,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.0294</v>
+        <v>1.22</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1084300</v>
+        <v>1676700</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="H61" t="n">
-        <v>50.72</v>
+        <v>37.52</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3226,10 +3233,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.352</v>
+        <v>1.284</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.328</v>
+        <v>1.314</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,28 +3249,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0.0305</v>
+        <v>1.14</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1041500</v>
+        <v>1623500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="H62" t="n">
-        <v>41.84</v>
+        <v>61.32</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3271,10 +3278,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.91</v>
+        <v>1.069</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.853</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,39 +3294,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.235</v>
+        <v>0.625</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1020300</v>
+        <v>1505100</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="H63" t="n">
-        <v>36.07</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.251</v>
+        <v>0.618</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.272</v>
+        <v>0.607</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,40 +3339,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.345</v>
+        <v>0.765</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1016600</v>
+        <v>1440700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H64" t="n">
-        <v>40.21</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J64" s="9" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="K64" s="9" t="n">
-        <v>0.383</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n"/>
+      <c r="K64" s="9" t="n"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
     </row>
@@ -3377,39 +3377,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.635</v>
+        <v>2.75</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0108</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>940000</v>
+        <v>1424700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.45</v>
+        <v>1.06</v>
       </c>
       <c r="H65" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
+        <v>70.95</v>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.636</v>
+        <v>2.629</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.625</v>
+        <v>2.452</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3422,28 +3422,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.275</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>925400</v>
+        <v>1287800</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="H66" t="n">
-        <v>47.18</v>
+        <v>45</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.6</v>
+        <v>0.287</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.61</v>
+        <v>0.283</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,39 +3467,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>-0.0052</v>
+        <v>0.305</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>852700</v>
+        <v>1242300</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="H67" t="n">
-        <v>63.97</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.41</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.308</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.883</v>
+        <v>0.301</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.2</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>731100</v>
+        <v>1238400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H68" t="n">
-        <v>39.47</v>
+        <v>38</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.285</v>
+        <v>0.215</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.315</v>
+        <v>0.233</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3557,39 +3557,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.235</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>726600</v>
+        <v>1221200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.21</v>
+        <v>0.71</v>
       </c>
       <c r="H69" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.07</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>2.248</v>
+        <v>0.251</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>2.185</v>
+        <v>0.272</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3602,28 +3602,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>701600</v>
+        <v>1216100</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.1</v>
+        <v>0.92</v>
       </c>
       <c r="H70" t="n">
-        <v>53.66</v>
+        <v>60.12</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.173</v>
+        <v>0.749</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.143</v>
+        <v>0.721</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3647,28 +3647,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.0481</v>
+        <v>0.35</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>656800</v>
+        <v>1175800</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H71" t="n">
-        <v>49.45</v>
+        <v>50.72</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.555</v>
+        <v>0.352</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.52</v>
+        <v>0.328</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>DESTINI</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>643500</v>
+        <v>1160300</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.12</v>
+        <v>4.56</v>
       </c>
       <c r="H72" t="n">
-        <v>65</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.6</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.797</v>
+        <v>0.229</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.774</v>
+        <v>0.243</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3737,39 +3737,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E73" s="15" t="n">
-        <v>0.0348</v>
+        <v>0.845</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>0.0305</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>636000</v>
+        <v>1158200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H73" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.84</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.524</v>
+        <v>0.91</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.475</v>
+        <v>0.853</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3782,39 +3782,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>-0.0117</v>
+        <v>1.17</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>624400</v>
+        <v>1154800</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H74" t="n">
-        <v>33.13</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.42</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.76</v>
+        <v>1.222</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.874</v>
+        <v>1.31</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3827,39 +3827,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.54</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E75" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>612400</v>
+        <v>1105400</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="H75" t="n">
-        <v>28.25</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65</v>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.689</v>
+        <v>0.797</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.756</v>
+        <v>0.774</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3872,39 +3872,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.0248</v>
+        <v>0.58</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>571000</v>
+        <v>1071600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="H76" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.3</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.667</v>
+        <v>0.523</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.475</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3917,28 +3917,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0.0192</v>
+        <v>5.11</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>570700</v>
+        <v>1068800</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H77" t="n">
-        <v>46.42</v>
+        <v>53.94</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>3.821</v>
+        <v>5.054</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>3.711</v>
+        <v>5.049</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3962,39 +3962,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.35</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>565900</v>
+        <v>1027000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.05</v>
+        <v>0.66</v>
       </c>
       <c r="H78" t="n">
-        <v>23.15</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.59</v>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.646</v>
+        <v>0.356</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.918</v>
+        <v>0.384</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4007,28 +4007,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.012</v>
+        <v>2.56</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>557900</v>
+        <v>972600</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H79" t="n">
-        <v>21.23</v>
+        <v>46.18</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.901</v>
+        <v>2.599</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.966</v>
+        <v>2.61</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4052,39 +4052,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.0187</v>
+        <v>9.98</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0.003</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>546600</v>
+        <v>971100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="H80" t="n">
-        <v>43.04</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47</v>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1.142</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.105</v>
+        <v>10.129</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4097,28 +4097,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.0323</v>
+        <v>0.835</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0.006</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>519000</v>
+        <v>945200</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="H81" t="n">
-        <v>53.94</v>
+        <v>18.43</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>5.054</v>
+        <v>0.901</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>5.049</v>
+        <v>0.966</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4142,39 +4142,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>0.0366</v>
+        <v>0.635</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>513900</v>
+        <v>940000</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="H82" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.03</v>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.083</v>
+        <v>0.636</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.994</v>
+        <v>0.625</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4187,28 +4187,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0</v>
+        <v>1.69</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>-0.0117</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>505000</v>
+        <v>908900</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="H83" t="n">
-        <v>55.46</v>
+        <v>33.13</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4216,16 +4216,1411 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.084</v>
+        <v>1.76</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.05</v>
+        <v>1.874</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5273</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CHINHIN</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>906300</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H84" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>2.078</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>903000</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H85" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>890400</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H86" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>2.246</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>2.184</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>870800</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H87" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>857100</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H88" t="n">
+        <v>53.66</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>786600</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H89" t="n">
+        <v>41</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>784700</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H90" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>764900</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H91" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>1.757</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>744200</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H92" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>2.114</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>734900</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H93" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>1.918</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>717100</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H94" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>707800</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H95" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>3.819</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>706800</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H96" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>7.425</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>7.893</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>686400</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H97" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>683200</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H98" t="n">
+        <v>44.06</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>682800</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H99" t="n">
+        <v>33</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>666600</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H100" t="n">
+        <v>54.44</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>663900</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H101" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SAG</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>637100</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="H102" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>629300</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H103" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>3.002</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>605200</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H104" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>7.306</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>6.915</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>590000</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H105" t="n">
+        <v>32</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>7.126</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>7.559</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>584800</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H106" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>578700</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H107" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>1.594</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>569800</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H108" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>2.793</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>2.677</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>561500</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H109" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>559400</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H110" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>7.561</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>7.745</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>532400</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H111" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>525500</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H112" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>522200</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H113" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>517400</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H114" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M83"/>
+  <autoFilter ref="A1:M114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,9 +96,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.012</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3849000</v>
+        <v>5385500</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>58.95</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 58.95未超买，现价高于50日均线约10.5%，技术面信号较为可靠。</t>
+          <t>SAR转多信号，现价0.42高于50日均线0.38，RSI 58.95处中性偏上区间，未超买，信号技术面尚属可靠。</t>
         </is>
       </c>
     </row>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.225</v>
+        <v>0.23</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>47131100</v>
+        <v>54449200</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -646,28 +646,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.0345</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>23657500</v>
+        <v>30512000</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.06</v>
+        <v>2.25</v>
       </c>
       <c r="H4" t="n">
-        <v>23.84</v>
+        <v>37.84</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.11</v>
+        <v>0.155</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.297</v>
+        <v>0.184</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -691,39 +691,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.055</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>16945400</v>
+        <v>25934000</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>67.05</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.46</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.843</v>
+        <v>0.111</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.748</v>
+        <v>0.297</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -736,39 +736,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.915</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>15800500</v>
+        <v>21125000</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.16</v>
+        <v>0.29</v>
       </c>
       <c r="H6" t="n">
-        <v>43.27</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.05</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.155</v>
+        <v>0.843</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.184</v>
+        <v>0.748</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.0455</v>
+        <v>0.35</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.06059999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>14014700</v>
+        <v>20988800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="n">
-        <v>67.47</v>
+        <v>68.58</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -826,39 +826,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.1</v>
+        <v>0.185</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-0.075</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>13770800</v>
+        <v>16953000</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.2</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.048</v>
+        <v>0.213</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.047</v>
+        <v>0.233</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -871,39 +871,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.0142</v>
+        <v>0.15</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.07139999999999999</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12816200</v>
+        <v>15444000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.51</v>
+        <v>0.25</v>
       </c>
       <c r="H9" t="n">
-        <v>81.19</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.71</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.635</v>
+        <v>0.156</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.543</v>
+        <v>0.142</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -927,14 +927,14 @@
       <c r="D10" s="9" t="n">
         <v>0.175</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="17" t="n">
         <v>-0.0278</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>11903700</v>
+        <v>14456900</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H10" t="n">
         <v>41.19</v>
@@ -961,39 +961,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.0357</v>
+        <v>0.055</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.1</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11322300</v>
+        <v>13770900</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.19</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="n">
-        <v>45.07</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.49</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.156</v>
+        <v>0.048</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.142</v>
+        <v>0.047</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,39 +1006,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.465</v>
+        <v>0.715</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.0106</v>
+        <v>0.0142</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>8924300</v>
+        <v>13291300</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="H12" t="n">
-        <v>79.34</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
+        <v>81.19</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.4</v>
+        <v>0.635</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.294</v>
+        <v>0.543</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,39 +1051,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>8110800</v>
+        <v>9575800</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>7.96</v>
+        <v>0.28</v>
       </c>
       <c r="H13" t="n">
-        <v>59.28</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
+        <v>79.34</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.294</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0.045</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.0667</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7619800</v>
+        <v>9176000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.37</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.64</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.572</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.545</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,28 +1141,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TALAMT</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
+        <v>0.58</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.045</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7050100</v>
+        <v>9013500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>5.18</v>
+        <v>0.44</v>
       </c>
       <c r="H15" t="n">
-        <v>44.56</v>
+        <v>52.97</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.078</v>
+        <v>0.572</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.081</v>
+        <v>0.545</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,39 +1186,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>0.0157</v>
+        <v>0.775</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6426000</v>
+        <v>8838800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.01</v>
+        <v>0.57</v>
       </c>
       <c r="H16" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
+        <v>50.16</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.213</v>
+        <v>0.775</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1.197</v>
+        <v>0.776</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1242,14 +1242,14 @@
       <c r="D17" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="15" t="n">
         <v>0.0204</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6132300</v>
+        <v>8354300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -1269,28 +1269,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0.0361</v>
+        <v>0.44</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5831400</v>
+        <v>8063200</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="H18" t="n">
-        <v>37.98</v>
+        <v>56.58</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.467</v>
+        <v>0.426</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.48</v>
+        <v>0.374</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1314,28 +1314,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>TALAMT</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.445</v>
+        <v>0.075</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5620500</v>
+        <v>7528700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.27</v>
+        <v>5.53</v>
       </c>
       <c r="H19" t="n">
-        <v>58.07</v>
+        <v>44.56</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.427</v>
+        <v>0.078</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.375</v>
+        <v>0.081</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1359,39 +1359,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.82</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5611800</v>
+        <v>7519400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="H20" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
+        <v>55.6</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.776</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1404,39 +1404,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0.0655</v>
+        <v>1.29</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5311600</v>
+        <v>7225700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="H21" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.98</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>2.729</v>
+        <v>1.213</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>2.868</v>
+        <v>1.197</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1449,28 +1449,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>0.0377</v>
+        <v>2.45</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0699</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5223700</v>
+        <v>6166400</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.77</v>
+        <v>1.19</v>
       </c>
       <c r="H22" t="n">
-        <v>35.22</v>
+        <v>36.32</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.307</v>
+        <v>2.73</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.331</v>
+        <v>2.869</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1494,28 +1494,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0.0437</v>
+        <v>0.435</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.0482</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5198600</v>
+        <v>5958700</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1.24</v>
+        <v>0.16</v>
       </c>
       <c r="H23" t="n">
-        <v>60.78</v>
+        <v>39.67</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.858</v>
+        <v>0.468</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,39 +1539,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0</v>
+        <v>0.275</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.0377</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>4967600</v>
+        <v>5468000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.31</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.22</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.331</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,39 +1584,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>4.72</v>
+        <v>0.95</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>-0.0021</v>
+        <v>0.0383</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4747600</v>
+        <v>5285500</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.23</v>
+        <v>1.27</v>
       </c>
       <c r="H25" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.53</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>4.728</v>
+        <v>0.857</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>4.832</v>
+        <v>0.6</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,39 +1629,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>0.0417</v>
+        <v>4.72</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4337600</v>
+        <v>5219100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1.19</v>
+        <v>0.26</v>
       </c>
       <c r="H26" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
+        <v>47.71</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.123</v>
+        <v>4.728</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.124</v>
+        <v>4.832</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,28 +1674,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3855100</v>
+        <v>4974900</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1.15</v>
+        <v>0.38</v>
       </c>
       <c r="H27" t="n">
-        <v>49.15</v>
+        <v>32.4</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.295</v>
+        <v>0.23</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.295</v>
+        <v>0.279</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3702800</v>
+        <v>4568800</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="H28" t="n">
         <v>48.63</v>
@@ -1764,39 +1764,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0.0323</v>
+        <v>7.12</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3618900</v>
+        <v>4443200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1.55</v>
+        <v>0.26</v>
       </c>
       <c r="H29" t="n">
-        <v>73.91</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.99</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.427</v>
+        <v>7.437</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.434</v>
+        <v>7.659</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,28 +1809,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>0.0455</v>
+        <v>0.58</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.09429999999999999</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3475200</v>
+        <v>4368400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.18</v>
+        <v>0.47</v>
       </c>
       <c r="H30" t="n">
-        <v>34.73</v>
+        <v>41.87</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.138</v>
+        <v>0.63</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.148</v>
+        <v>0.619</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0.0113</v>
+        <v>0.125</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3312000</v>
+        <v>4337600</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.27</v>
+        <v>1.19</v>
       </c>
       <c r="H31" t="n">
-        <v>45.46</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.747</v>
+        <v>0.123</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.743</v>
+        <v>0.124</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0354</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3275800</v>
+        <v>4229000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="H32" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.42</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.292</v>
+        <v>1.948</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.28</v>
+        <v>1.765</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0.0195</v>
+        <v>0.305</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3253500</v>
+        <v>4219300</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.23</v>
+        <v>0.22</v>
       </c>
       <c r="H33" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.41</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.744</v>
+        <v>0.308</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.707</v>
+        <v>0.301</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,28 +1989,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>0.09820000000000001</v>
+        <v>2.03</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3250600</v>
+        <v>4133800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.55</v>
+        <v>1.26</v>
       </c>
       <c r="H34" t="n">
-        <v>58.6</v>
+        <v>46.01</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.574</v>
+        <v>2.042</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.477</v>
+        <v>2.068</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>0.0132</v>
+        <v>0.265</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3064400</v>
+        <v>4103500</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="H35" t="n">
-        <v>48.57</v>
+        <v>38.25</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.769</v>
+        <v>0.292</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.771</v>
+        <v>0.28</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,39 +2079,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.043</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3025400</v>
+        <v>3999600</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.92</v>
+        <v>1.72</v>
       </c>
       <c r="H36" t="n">
-        <v>46.01</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.97</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>2.042</v>
+        <v>0.428</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>2.068</v>
+        <v>0.434</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,28 +2124,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>0.0472</v>
+        <v>0.115</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2852000</v>
+        <v>3949300</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="H37" t="n">
-        <v>37.22</v>
+        <v>34.73</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.628</v>
+        <v>0.138</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.619</v>
+        <v>0.148</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2806300</v>
+        <v>3855100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.26</v>
+        <v>1.15</v>
       </c>
       <c r="H38" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.62</v>
+        <v>0.295</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.616</v>
+        <v>0.295</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,39 +2214,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0.0303</v>
+        <v>0.865</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2716400</v>
+        <v>3846500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H39" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
+        <v>46.09</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>1.947</v>
+        <v>0.868</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1.765</v>
+        <v>0.869</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,28 +2259,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>0.0118</v>
+        <v>0.62</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>0.1071</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2666100</v>
+        <v>3716600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.15</v>
+        <v>0.63</v>
       </c>
       <c r="H40" t="n">
-        <v>47.64</v>
+        <v>59.11</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.63</v>
+        <v>0.574</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.56</v>
+        <v>0.477</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,28 +2304,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.39</v>
+        <v>2.69</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.0113</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2512200</v>
+        <v>3453400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="H41" t="n">
-        <v>27.8</v>
+        <v>45.46</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.499</v>
+        <v>2.747</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.601</v>
+        <v>2.743</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2349,39 +2349,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0.0063</v>
+        <v>0.785</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2472900</v>
+        <v>3445000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="H42" t="n">
-        <v>45.54</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.1</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>4.878</v>
+        <v>0.744</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>4.741</v>
+        <v>0.707</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,28 +2394,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0.011</v>
+        <v>2.58</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2469800</v>
+        <v>3291600</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H43" t="n">
-        <v>42.02</v>
+        <v>47.64</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.508</v>
+        <v>2.63</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.465</v>
+        <v>2.56</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2439,28 +2439,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>0.0028</v>
+        <v>0.13</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.04</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2399800</v>
+        <v>3260000</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.14</v>
+        <v>2.17</v>
       </c>
       <c r="H44" t="n">
-        <v>34.09</v>
+        <v>51.04</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>7.442</v>
+        <v>0.129</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>7.66</v>
+        <v>0.13</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2484,39 +2484,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.115</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2336000</v>
+        <v>3256200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.32</v>
+        <v>0.74</v>
       </c>
       <c r="H45" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
+        <v>64.04000000000001</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.372</v>
+        <v>0.1</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.37</v>
+        <v>0.091</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2529,39 +2529,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2156800</v>
+        <v>3186700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H46" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I46" s="17" t="inlineStr">
+        <v>60.97</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.868</v>
+        <v>0.372</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.869</v>
+        <v>0.37</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2574,28 +2574,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2.01</v>
+        <v>0.44</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.0602</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2148400</v>
+        <v>3182700</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="H47" t="n">
-        <v>32.39</v>
+        <v>54.38</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2.123</v>
+        <v>0.425</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2.234</v>
+        <v>0.417</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2619,39 +2619,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.0319</v>
+        <v>0.165</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2103500</v>
+        <v>3176900</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.25</v>
+        <v>0.57</v>
       </c>
       <c r="H48" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.032</v>
+        <v>0.175</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.969</v>
+        <v>0.195</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2664,28 +2664,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0.0184</v>
+        <v>0.765</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2097100</v>
+        <v>3121400</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="H49" t="n">
-        <v>52.36</v>
+        <v>48.57</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.826</v>
+        <v>0.769</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.789</v>
+        <v>0.771</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2709,28 +2709,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>3.8</v>
+        <v>4.79</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>-0.0231</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2055100</v>
+        <v>3084700</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H50" t="n">
-        <v>56.81</v>
+        <v>46.13</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>3.687</v>
+        <v>4.879</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>3.103</v>
+        <v>4.741</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2754,28 +2754,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>-0.017</v>
+        <v>0.385</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.0375</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2006500</v>
+        <v>3060600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="H51" t="n">
-        <v>39.33</v>
+        <v>27.37</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>5.462</v>
+        <v>0.498</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>5.481</v>
+        <v>0.601</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2799,28 +2799,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0.02</v>
+        <v>0.47</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.033</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1912600</v>
+        <v>3020000</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0.29</v>
       </c>
       <c r="H52" t="n">
-        <v>41.5</v>
+        <v>44.03</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.27</v>
+        <v>0.509</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.29</v>
+        <v>0.465</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2844,28 +2844,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>0.0472</v>
+        <v>2.02</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1886900</v>
+        <v>2961100</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="H53" t="n">
-        <v>40.39</v>
+        <v>33.19</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.74</v>
+        <v>2.124</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>2.235</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2889,39 +2889,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>0.0153</v>
+        <v>0.625</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1874700</v>
+        <v>2890000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="H54" t="n">
-        <v>87.28</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>2.914</v>
+        <v>0.618</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2.484</v>
+        <v>0.607</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2934,39 +2934,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>0.0361</v>
+        <v>0.63</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1833300</v>
+        <v>2806300</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0.26</v>
       </c>
       <c r="H55" t="n">
-        <v>52.23</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.424</v>
+        <v>0.62</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.417</v>
+        <v>0.616</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2988,19 +2988,19 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0.0388</v>
+        <v>0.68</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.05429999999999999</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1802000</v>
+        <v>2626800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="H56" t="n">
-        <v>40.2</v>
+        <v>41.88</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0.722</v>
@@ -3024,28 +3024,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>0.0308</v>
+        <v>5.21</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>-0.017</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1715000</v>
+        <v>2545900</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H57" t="n">
-        <v>47.84</v>
+        <v>39.33</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.343</v>
+        <v>5.462</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.335</v>
+        <v>5.481</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3069,39 +3069,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>0.0667</v>
+        <v>0.825</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1712300</v>
+        <v>2345900</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>4.92</v>
+        <v>0.67</v>
       </c>
       <c r="H58" t="n">
-        <v>78.31</v>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.51</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.226</v>
+        <v>0.825</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.225</v>
+        <v>0.789</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3114,28 +3114,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>3.82</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1698500</v>
+        <v>2192500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H59" t="n">
-        <v>27.73</v>
+        <v>57.48</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.272</v>
+        <v>3.689</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.298</v>
+        <v>3.103</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3159,28 +3159,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0.0513</v>
+        <v>0.965</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0266</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1693000</v>
+        <v>2180000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H60" t="n">
-        <v>55.11</v>
+        <v>41.97</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.393</v>
+        <v>1.032</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.363</v>
+        <v>0.969</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3204,28 +3204,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.02</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1676700</v>
+        <v>2068600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="H61" t="n">
-        <v>37.52</v>
+        <v>41.5</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.284</v>
+        <v>0.27</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.314</v>
+        <v>0.29</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3249,28 +3249,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0.0179</v>
+        <v>0.67</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.0551</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1623500</v>
+        <v>2054300</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="H62" t="n">
-        <v>61.32</v>
+        <v>41.18</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.069</v>
+        <v>0.741</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3294,39 +3294,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0</v>
+        <v>3.32</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1505100</v>
+        <v>2011300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="H63" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I63" s="17" t="inlineStr">
+        <v>87.45</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.618</v>
+        <v>2.914</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.607</v>
+        <v>2.485</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3339,33 +3339,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.0462</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1440700</v>
+        <v>1911200</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
+      </c>
+      <c r="H64" t="n">
+        <v>49.7</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J64" s="9" t="n"/>
-      <c r="K64" s="9" t="n"/>
+      <c r="J64" s="9" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0.335</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
     </row>
@@ -3377,39 +3384,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>-0.0108</v>
+        <v>0.51</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1424700</v>
+        <v>1834700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="H65" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="I65" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.45</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.629</v>
+        <v>0.537</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.452</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3422,28 +3429,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>0.0185</v>
+        <v>0.41</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1287800</v>
+        <v>1834200</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.11</v>
+        <v>0.31</v>
       </c>
       <c r="H66" t="n">
-        <v>45</v>
+        <v>55.11</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3451,10 +3458,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.287</v>
+        <v>0.393</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.283</v>
+        <v>0.363</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,28 +3474,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1242300</v>
+        <v>1821400</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="H67" t="n">
-        <v>47.41</v>
+        <v>22.13</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3496,10 +3503,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.308</v>
+        <v>0.321</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.301</v>
+        <v>0.366</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,39 +3519,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1238400</v>
+        <v>1802400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
       <c r="H68" t="n">
-        <v>38</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.31</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.215</v>
+        <v>0.226</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.233</v>
+        <v>0.225</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3557,28 +3564,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0</v>
+        <v>1.23</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1221200</v>
+        <v>1757900</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.71</v>
+        <v>0.2</v>
       </c>
       <c r="H69" t="n">
-        <v>36.07</v>
+        <v>39.47</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3586,10 +3593,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.251</v>
+        <v>1.285</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.272</v>
+        <v>1.315</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3602,28 +3609,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>0.0132</v>
+        <v>1.13</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1216100</v>
+        <v>1756000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.92</v>
+        <v>0.38</v>
       </c>
       <c r="H70" t="n">
-        <v>60.12</v>
+        <v>60.5</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3631,10 +3638,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.749</v>
+        <v>1.068</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.721</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3647,40 +3654,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0.0294</v>
+        <v>0.765</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1175800</v>
+        <v>1752100</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H71" t="n">
-        <v>50.72</v>
+        <v>0.03</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J71" s="9" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="K71" s="9" t="n">
-        <v>0.328</v>
-      </c>
+      <c r="J71" s="9" t="n"/>
+      <c r="K71" s="9" t="n"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
     </row>
@@ -3692,28 +3692,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DESTINI</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.23</v>
+        <v>0.255</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1160300</v>
+        <v>1712600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>4.56</v>
+        <v>0.21</v>
       </c>
       <c r="H72" t="n">
-        <v>48.6</v>
+        <v>27.73</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.229</v>
+        <v>0.272</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.243</v>
+        <v>0.298</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3737,28 +3737,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>0.0305</v>
+        <v>0.355</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.0441</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1158200</v>
+        <v>1531700</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H73" t="n">
-        <v>41.84</v>
+        <v>52.77</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.91</v>
+        <v>0.353</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.853</v>
+        <v>0.328</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3782,39 +3782,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1154800</v>
+        <v>1528500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H74" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
+        <v>51.66</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.222</v>
+        <v>1.627</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.31</v>
+        <v>1.686</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3827,39 +3827,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0</v>
+        <v>0.58</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1105400</v>
+        <v>1471300</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="H75" t="n">
-        <v>65</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
+        <v>65.3</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.797</v>
+        <v>0.523</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.774</v>
+        <v>0.475</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3872,39 +3872,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>0.008699999999999999</v>
+        <v>2.74</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>-0.0144</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1071600</v>
+        <v>1435400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.26</v>
+        <v>1.06</v>
       </c>
       <c r="H76" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I76" s="17" t="inlineStr">
+        <v>69.31999999999999</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.523</v>
+        <v>2.628</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.475</v>
+        <v>2.452</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3917,28 +3917,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="E77" s="16" t="n">
-        <v>0.0323</v>
+        <v>0.845</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0181</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1068800</v>
+        <v>1402700</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="H77" t="n">
-        <v>53.94</v>
+        <v>23.84</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>5.054</v>
+        <v>0.902</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>5.049</v>
+        <v>0.966</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3962,39 +3962,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0.0145</v>
+        <v>2.46</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1027000</v>
+        <v>1401700</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.66</v>
+        <v>0.12</v>
       </c>
       <c r="H78" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.17</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.356</v>
+        <v>2.449</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.384</v>
+        <v>2.399</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4007,39 +4007,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>0.0039</v>
+        <v>7.28</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>-0.0027</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>972600</v>
+        <v>1367900</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H79" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.599</v>
+        <v>7.424</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.61</v>
+        <v>7.892</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4052,39 +4052,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0.003</v>
+        <v>0.275</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>971100</v>
+        <v>1367800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H80" t="n">
-        <v>47</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>9.994999999999999</v>
+        <v>0.287</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>10.129</v>
+        <v>0.283</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4097,39 +4097,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>0.006</v>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.002</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>945200</v>
+        <v>1367400</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.29</v>
+        <v>0.11</v>
       </c>
       <c r="H81" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.34</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.901</v>
+        <v>9.994</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.966</v>
+        <v>10.129</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4142,40 +4142,38 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>940000</v>
+        <v>1367200</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="H82" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
+        <v>68.41</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="K82" s="9" t="n">
-        <v>0.625</v>
-      </c>
+        <v>0.331</v>
+      </c>
+      <c r="K82" s="9" t="n"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
     </row>
@@ -4187,28 +4185,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.69</v>
+        <v>5.12</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>-0.0117</v>
+        <v>0.0343</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>908900</v>
+        <v>1304600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="H83" t="n">
-        <v>33.13</v>
+        <v>54.48</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4216,10 +4214,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.76</v>
+        <v>5.055</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.874</v>
+        <v>5.05</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4232,39 +4230,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>906300</v>
+        <v>1290400</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>4.92</v>
+        <v>0.24</v>
       </c>
       <c r="H84" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
+        <v>61.34</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>2.078</v>
+        <v>0.797</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.083</v>
+        <v>0.774</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4277,28 +4275,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>0.0481</v>
+        <v>0.235</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>903000</v>
+        <v>1259200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.17</v>
+        <v>0.74</v>
       </c>
       <c r="H85" t="n">
-        <v>49.45</v>
+        <v>36.07</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4306,10 +4304,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.555</v>
+        <v>0.251</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.52</v>
+        <v>0.272</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4322,39 +4320,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.33</v>
+        <v>0.455</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>-0.0169</v>
+        <v>0.0111</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>890400</v>
+        <v>1248200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="H86" t="n">
-        <v>58.82</v>
-      </c>
-      <c r="I86" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.55</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>2.246</v>
+        <v>0.489</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2.184</v>
+        <v>0.548</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4367,39 +4365,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>-0.0052</v>
+        <v>1.16</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>870800</v>
+        <v>1245100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H87" t="n">
-        <v>63.97</v>
-      </c>
-      <c r="I87" s="17" t="inlineStr">
+        <v>35.17</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.221</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.883</v>
+        <v>1.31</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4412,28 +4410,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>857100</v>
+        <v>1216200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.13</v>
+        <v>0.92</v>
       </c>
       <c r="H88" t="n">
-        <v>53.66</v>
+        <v>60.12</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4441,10 +4439,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.173</v>
+        <v>0.749</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1.143</v>
+        <v>0.721</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4457,28 +4455,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>0.0331</v>
+        <v>1.18</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>786600</v>
+        <v>1207000</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H89" t="n">
-        <v>41</v>
+        <v>52.11</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4486,10 +4484,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.667</v>
+        <v>1.173</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>1.143</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4502,39 +4500,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>0.0266</v>
+        <v>0.845</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.0305</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>784700</v>
+        <v>1198800</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H90" t="n">
-        <v>57.13</v>
-      </c>
-      <c r="I90" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.84</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>6.23</v>
+        <v>0.91</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>5.95</v>
+        <v>0.853</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4547,28 +4545,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>DESTINI</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.23</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>764900</v>
+        <v>1160300</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.12</v>
+        <v>4.56</v>
       </c>
       <c r="H91" t="n">
-        <v>29.96</v>
+        <v>48.6</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -4576,10 +4574,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.69</v>
+        <v>0.229</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.757</v>
+        <v>0.243</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4592,39 +4590,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>0.0142</v>
+        <v>2.35</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>744200</v>
+        <v>1150200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="H92" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
+        <v>60.8</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.114</v>
+        <v>2.248</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.07</v>
+        <v>2.185</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4637,28 +4635,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>0.006999999999999999</v>
+        <v>1.1</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>734900</v>
+        <v>1145600</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H93" t="n">
-        <v>23.15</v>
+        <v>53.75</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4666,10 +4664,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.646</v>
+        <v>1.083</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.918</v>
+        <v>1.05</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4682,28 +4680,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0</v>
+        <v>1.42</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>717100</v>
+        <v>1118500</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H94" t="n">
-        <v>55.46</v>
+        <v>21.29</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4711,10 +4709,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.084</v>
+        <v>1.644</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.05</v>
+        <v>1.918</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4727,28 +4725,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0.0137</v>
+        <v>2.56</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>707800</v>
+        <v>1093200</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="H95" t="n">
-        <v>45.48</v>
+        <v>46.18</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4756,10 +4754,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>3.819</v>
+        <v>2.599</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>3.71</v>
+        <v>2.61</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4772,39 +4770,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>7.29</v>
+        <v>0.62</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>-0.0014</v>
+        <v>0.0248</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>706800</v>
+        <v>1058200</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H96" t="n">
-        <v>37.39</v>
-      </c>
-      <c r="I96" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.89</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>7.425</v>
+        <v>0.667</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>7.893</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4817,28 +4815,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>0.0407</v>
+        <v>1.18</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>686400</v>
+        <v>1043700</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H97" t="n">
-        <v>35.5</v>
+        <v>21.3</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4846,10 +4844,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.707</v>
+        <v>1.356</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.742</v>
+        <v>1.54</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4862,39 +4860,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>0.0262</v>
+        <v>0.35</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>683200</v>
+        <v>1037100</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.26</v>
+        <v>0.67</v>
       </c>
       <c r="H98" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.59</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>2.081</v>
+        <v>0.356</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.993</v>
+        <v>0.384</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4907,28 +4905,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>1.7</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>682800</v>
+        <v>1022600</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="H99" t="n">
-        <v>33</v>
+        <v>34.28</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4936,10 +4934,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.839</v>
+        <v>1.761</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.859</v>
+        <v>1.874</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4952,28 +4950,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.545</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.0481</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>666600</v>
+        <v>1020000</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="H100" t="n">
-        <v>54.44</v>
+        <v>49.45</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4981,10 +4979,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>2.449</v>
+        <v>0.555</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>2.4</v>
+        <v>0.52</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4997,39 +4995,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>0.0442</v>
+        <v>6.58</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>663900</v>
+        <v>952300</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H101" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.54</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.594</v>
+        <v>6.233</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.586</v>
+        <v>5.95</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5042,39 +5040,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0360</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SAG</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
         <v>0.635</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>637100</v>
+        <v>940000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>3.57</v>
+        <v>0.45</v>
       </c>
       <c r="H102" t="n">
-        <v>47.94</v>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
+        <v>51.03</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.638</v>
+        <v>0.636</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.644</v>
+        <v>0.625</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5087,39 +5085,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>0.0109</v>
+        <v>0.97</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>629300</v>
+        <v>922600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H103" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.02</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>2.87</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>3.002</v>
+        <v>0.883</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5132,39 +5130,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>0.0388</v>
+        <v>2.07</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>605200</v>
+        <v>906300</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.13</v>
+        <v>4.92</v>
       </c>
       <c r="H104" t="n">
-        <v>50.18</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.34</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>7.306</v>
+        <v>2.078</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>6.915</v>
+        <v>2.083</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5186,19 +5184,19 @@
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0</v>
+        <v>6.77</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>590000</v>
+        <v>881600</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H105" t="n">
-        <v>32</v>
+        <v>32.94</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5206,7 +5204,7 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>7.126</v>
+        <v>7.128</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>7.559</v>
@@ -5222,28 +5220,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>0.0187</v>
+        <v>1.97</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0.0314</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>584800</v>
+        <v>852100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="H106" t="n">
-        <v>43.04</v>
+        <v>44.65</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5251,10 +5249,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.142</v>
+        <v>2.082</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.105</v>
+        <v>1.993</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5267,39 +5265,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>0.0137</v>
+        <v>1.95</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>578700</v>
+        <v>843200</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="H107" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.97</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.594</v>
+        <v>1.926</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.656</v>
+        <v>1.951</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5312,28 +5310,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E108" s="16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E108" s="15" t="n">
         <v>0.0109</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>569800</v>
+        <v>839000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="H108" t="n">
-        <v>51.36</v>
+        <v>40.89</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5341,10 +5339,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.793</v>
+        <v>2.87</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.677</v>
+        <v>3.002</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5357,28 +5355,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.19</v>
+        <v>0.645</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>-0.0083</v>
+        <v>0.0488</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>561500</v>
+        <v>816400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="H109" t="n">
-        <v>21.84</v>
+        <v>36.61</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5386,10 +5384,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.357</v>
+        <v>0.707</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.54</v>
+        <v>0.742</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5402,39 +5400,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E110" s="16" t="n">
-        <v>0.0027</v>
+        <v>1.55</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>559400</v>
+        <v>806300</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="H110" t="n">
-        <v>45.97</v>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.96</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>7.561</v>
+        <v>1.69</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>7.745</v>
+        <v>1.757</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5447,28 +5445,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>0.0431</v>
+        <v>3.72</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>532400</v>
+        <v>795300</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H111" t="n">
-        <v>50.8</v>
+        <v>46.42</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5476,10 +5474,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.23</v>
+        <v>3.821</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.086</v>
+        <v>3.711</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5492,39 +5490,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0</v>
+        <v>2.14</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>525500</v>
+        <v>754200</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.04</v>
+        <v>0.36</v>
       </c>
       <c r="H112" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I112" s="17" t="inlineStr">
+        <v>55.85</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2.104</v>
+        <v>2.113</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.103</v>
+        <v>2.07</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5537,28 +5535,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E113" s="16" t="n">
-        <v>0.0167</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>522200</v>
+        <v>746500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="H113" t="n">
-        <v>51.28</v>
+        <v>33</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5566,10 +5564,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.914</v>
+        <v>0.839</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.883</v>
+        <v>0.859</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5582,28 +5580,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>0.0049</v>
+        <v>7.23</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0.0388</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>517400</v>
+        <v>745200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.42</v>
+        <v>0.17</v>
       </c>
       <c r="H114" t="n">
-        <v>42.57</v>
+        <v>50.18</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5611,16 +5609,1051 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>2.111</v>
+        <v>7.306</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>2.265</v>
+        <v>6.915</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>736500</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H115" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>1.593</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>726000</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H116" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>3.343</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>3.582</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>714100</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H117" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>697700</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H118" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>669400</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>2.793</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>2.677</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>656800</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H120" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SAG</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>652200</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H121" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>648100</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H122" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>647500</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H123" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>7.561</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>7.745</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>639500</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H124" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>10.424</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>9.805</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>625000</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H125" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>622700</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H126" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>583400</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H127" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>5.859</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>6.145</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>577200</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H128" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>575100</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H129" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>573500</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H130" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>544700</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H131" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>536600</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H132" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>534300</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H133" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>530000</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H134" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>524600</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H135" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>522200</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H136" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>503700</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H137" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>3.161</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>2.911</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M114"/>
+  <autoFilter ref="A1:M137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,8 +97,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.012</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5385500</v>
+        <v>5975700</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>58.95</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.42高于50日均线0.38，RSI 58.95处中性偏上区间，未超买，信号技术面尚属可靠。</t>
+          <t>SAR转多信号，RSI 58.95未超买，现价高于50日均线约10.5%，技术面信号较为可靠。</t>
         </is>
       </c>
     </row>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.23</v>
+        <v>0.235</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>54449200</v>
+        <v>57902200</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -661,10 +661,10 @@
         <v>0.0345</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>30512000</v>
+        <v>31840000</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="H4" t="n">
         <v>37.84</v>
@@ -706,10 +706,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>25934000</v>
+        <v>28607400</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H5" t="n">
         <v>24.46</v>
@@ -736,39 +736,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.19</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>21125000</v>
+        <v>25966400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.29</v>
+        <v>1.22</v>
       </c>
       <c r="H6" t="n">
-        <v>67.05</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.93</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.843</v>
+        <v>0.214</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.748</v>
+        <v>0.233</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -781,39 +781,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>25131900</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>0.35</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0.06059999999999999</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>20988800</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0.25</v>
-      </c>
       <c r="H7" t="n">
-        <v>68.58</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.05</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.311</v>
+        <v>0.843</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.261</v>
+        <v>0.748</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -826,28 +826,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>-0.075</v>
+        <v>0.345</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>16953000</v>
+        <v>23296800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="H8" t="n">
-        <v>32.2</v>
+        <v>67.47</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.213</v>
+        <v>0.311</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.233</v>
+        <v>0.261</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,19 +880,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.15</v>
+        <v>0.155</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.1071</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>15444000</v>
+        <v>21626800</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H9" t="n">
-        <v>47.71</v>
+        <v>50.11</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0.142</v>
@@ -927,14 +927,14 @@
       <c r="D10" s="9" t="n">
         <v>0.175</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="16" t="n">
         <v>-0.0278</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>14456900</v>
+        <v>18369800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="H10" t="n">
         <v>41.19</v>
@@ -976,15 +976,15 @@
         <v>0.1</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>13770900</v>
+        <v>13819200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="H11" t="n">
         <v>60.49</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1021,15 +1021,15 @@
         <v>0.0142</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>13291300</v>
+        <v>13418000</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="H12" t="n">
         <v>81.19</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1051,39 +1051,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>-0.0106</v>
+        <v>1.3</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.0236</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9575800</v>
+        <v>11392600</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.28</v>
+        <v>1.78</v>
       </c>
       <c r="H13" t="n">
-        <v>79.34</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
+        <v>63.96</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.4</v>
+        <v>1.214</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.294</v>
+        <v>1.197</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>-0.0667</v>
+        <v>0.575</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.036</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9176000</v>
+        <v>10454100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>9</v>
+        <v>0.51</v>
       </c>
       <c r="H14" t="n">
-        <v>51.64</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.07</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.572</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.544</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.045</v>
+        <v>0.82</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>9013500</v>
+        <v>10249000</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="H15" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.6</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.572</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.545</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,39 +1186,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.465</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8838800</v>
+        <v>10050000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
       <c r="H16" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
+        <v>79.34</v>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.775</v>
+        <v>0.4</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.776</v>
+        <v>0.294</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,33 +1231,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.0204</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>-0.0667</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8354300</v>
+        <v>9279300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
+        <v>9.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.06900000000000001</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
     </row>
@@ -1269,39 +1276,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>-0.0112</v>
+        <v>0.775</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8063200</v>
+        <v>9259200</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
-        <v>56.58</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.16</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.426</v>
+        <v>0.775</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.374</v>
+        <v>0.776</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1314,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TALAMT</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7528700</v>
+        <v>8940500</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>5.53</v>
+        <v>0.43</v>
       </c>
       <c r="H19" t="n">
-        <v>44.56</v>
+        <v>59.14</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1343,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.078</v>
+        <v>0.427</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.081</v>
+        <v>0.375</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1359,40 +1366,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7519400</v>
+        <v>8364800</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H20" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>0.8120000000000001</v>
-      </c>
+        <v>0.37</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
     </row>
@@ -1404,39 +1404,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>TALAMT</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.0157</v>
+        <v>0.075</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7225700</v>
+        <v>7528700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.13</v>
+        <v>5.53</v>
       </c>
       <c r="H21" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.56</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.213</v>
+        <v>0.078</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.197</v>
+        <v>0.081</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1449,28 +1449,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>0.0699</v>
+        <v>0.305</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6166400</v>
+        <v>6416300</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.19</v>
+        <v>0.33</v>
       </c>
       <c r="H22" t="n">
-        <v>36.32</v>
+        <v>47.41</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>2.73</v>
+        <v>0.308</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.869</v>
+        <v>0.301</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1494,28 +1494,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.435</v>
+        <v>2.43</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>0.0482</v>
+        <v>0.0611</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5958700</v>
+        <v>6351300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.16</v>
+        <v>1.23</v>
       </c>
       <c r="H23" t="n">
-        <v>39.67</v>
+        <v>35.27</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.468</v>
+        <v>2.728</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.48</v>
+        <v>2.868</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,28 +1539,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.275</v>
+        <v>0.58</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.0377</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5468000</v>
+        <v>6273600</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="H24" t="n">
-        <v>35.22</v>
+        <v>41.87</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.307</v>
+        <v>0.63</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.331</v>
+        <v>0.619</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,28 +1584,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.95</v>
+        <v>0.43</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0383</v>
+        <v>0.0361</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>5285500</v>
+        <v>6261200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.27</v>
+        <v>0.17</v>
       </c>
       <c r="H25" t="n">
-        <v>60.53</v>
+        <v>37.98</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.857</v>
+        <v>0.467</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1638,27 +1638,27 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>-0.0021</v>
+        <v>4.71</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5219100</v>
+        <v>6171900</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H26" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
+        <v>46.91</v>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>4.728</v>
+        <v>4.727</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>4.832</v>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0244</v>
+        <v>0.205</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4974900</v>
+        <v>5838800</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="H27" t="n">
-        <v>32.4</v>
+        <v>28.46</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0.279</v>
@@ -1719,28 +1719,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4568800</v>
+        <v>5813300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.82</v>
+        <v>1.39</v>
       </c>
       <c r="H28" t="n">
-        <v>48.63</v>
+        <v>59.5</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.174</v>
+        <v>0.856</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.181</v>
+        <v>0.599</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,28 +1764,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>-0.0042</v>
+        <v>0.275</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.0377</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4443200</v>
+        <v>5636100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.26</v>
+        <v>0.84</v>
       </c>
       <c r="H29" t="n">
-        <v>31.99</v>
+        <v>35.22</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>7.437</v>
+        <v>0.307</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>7.659</v>
+        <v>0.331</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,28 +1809,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0.09429999999999999</v>
+        <v>7.15</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4368400</v>
+        <v>5577600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="H30" t="n">
-        <v>41.87</v>
+        <v>32.87</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.63</v>
+        <v>7.44</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.619</v>
+        <v>7.66</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0417</v>
+        <v>0.865</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4337600</v>
+        <v>5388100</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.19</v>
+        <v>0.27</v>
       </c>
       <c r="H31" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
+        <v>46.09</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.123</v>
+        <v>0.868</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.124</v>
+        <v>0.869</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2.05</v>
+        <v>0.12</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>0.0354</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4229000</v>
+        <v>5288100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.15</v>
+        <v>1.21</v>
       </c>
       <c r="H32" t="n">
-        <v>59.42</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
+        <v>66.59</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.948</v>
+        <v>0.101</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1.765</v>
+        <v>0.091</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,28 +1944,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.305</v>
+        <v>0.175</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4219300</v>
+        <v>4943800</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.22</v>
+        <v>0.88</v>
       </c>
       <c r="H33" t="n">
-        <v>47.41</v>
+        <v>48.63</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.308</v>
+        <v>0.174</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.301</v>
+        <v>0.181</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,39 +1989,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4133800</v>
+        <v>4915900</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.26</v>
+        <v>0.14</v>
       </c>
       <c r="H34" t="n">
-        <v>46.01</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.42</v>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>2.042</v>
+        <v>0.155</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.068</v>
+        <v>0.156</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4103500</v>
+        <v>4834800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="H35" t="n">
         <v>38.25</v>
@@ -2079,39 +2079,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.485</v>
+        <v>2.05</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>0.043</v>
+        <v>0.0354</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3999600</v>
+        <v>4808300</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.72</v>
+        <v>0.17</v>
       </c>
       <c r="H36" t="n">
-        <v>74.97</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
+        <v>59.42</v>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.428</v>
+        <v>1.948</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.434</v>
+        <v>1.765</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,39 +2124,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.63</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3949300</v>
+        <v>4350500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H37" t="n">
-        <v>34.73</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.138</v>
+        <v>0.62</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.148</v>
+        <v>0.616</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0</v>
+        <v>0.125</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3855100</v>
+        <v>4344600</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="H38" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.295</v>
+        <v>0.123</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.295</v>
+        <v>0.124</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,39 +2214,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3846500</v>
+        <v>4245000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.19</v>
+        <v>1.3</v>
       </c>
       <c r="H39" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.15</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.868</v>
+        <v>2.043</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.869</v>
+        <v>2.068</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,39 +2259,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.1071</v>
+        <v>0.0538</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3716600</v>
+        <v>4236800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.63</v>
+        <v>1.82</v>
       </c>
       <c r="H40" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.95</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.574</v>
+        <v>0.428</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.477</v>
+        <v>0.434</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,28 +2304,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.69</v>
+        <v>0.115</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.0113</v>
+        <v>0.0455</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3453400</v>
+        <v>4171500</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="H41" t="n">
-        <v>45.46</v>
+        <v>34.73</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.747</v>
+        <v>0.138</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.743</v>
+        <v>0.148</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2349,39 +2349,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.785</v>
+        <v>0.61</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>0.0195</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3445000</v>
+        <v>4051900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.3</v>
+        <v>0.68</v>
       </c>
       <c r="H42" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.07</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.744</v>
+        <v>0.573</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.707</v>
+        <v>0.476</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,40 +2394,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0118</v>
+        <v>0.105</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3291600</v>
+        <v>3926000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H43" t="n">
-        <v>47.64</v>
+        <v>0.11</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J43" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="K43" s="9" t="n">
-        <v>2.56</v>
-      </c>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
     </row>
@@ -2439,39 +2432,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>0.04</v>
+        <v>0.0133</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3260000</v>
+        <v>3870500</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>2.17</v>
+        <v>0.54</v>
       </c>
       <c r="H44" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.97</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.129</v>
+        <v>0.372</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.13</v>
+        <v>0.37</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2484,39 +2477,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.295</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3256200</v>
+        <v>3855100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.74</v>
+        <v>1.15</v>
       </c>
       <c r="H45" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.1</v>
+        <v>0.295</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.091</v>
+        <v>0.295</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2529,39 +2522,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.39</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3186700</v>
+        <v>3828900</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="H46" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.8</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.372</v>
+        <v>0.499</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.37</v>
+        <v>0.601</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2589,10 +2582,10 @@
         <v>0.0602</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3182700</v>
+        <v>3790600</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="H47" t="n">
         <v>54.38</v>
@@ -2619,39 +2612,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3176900</v>
+        <v>3750100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="H48" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.33</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.175</v>
+        <v>2.628</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.195</v>
+        <v>2.559</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2664,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.625</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3121400</v>
+        <v>3657100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.38</v>
+        <v>1.07</v>
       </c>
       <c r="H49" t="n">
-        <v>48.57</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.769</v>
+        <v>0.618</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.771</v>
+        <v>0.607</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2709,28 +2702,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>4.79</v>
+        <v>2.03</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3084700</v>
+        <v>3622800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.12</v>
+        <v>0.31</v>
       </c>
       <c r="H50" t="n">
-        <v>46.13</v>
+        <v>34.81</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2738,10 +2731,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>4.879</v>
+        <v>2.125</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>4.741</v>
+        <v>2.235</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2754,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.0375</v>
+        <v>0.165</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3060600</v>
+        <v>3613900</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.29</v>
+        <v>0.65</v>
       </c>
       <c r="H51" t="n">
-        <v>27.37</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.498</v>
+        <v>0.175</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.601</v>
+        <v>0.195</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2799,28 +2792,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0.033</v>
+        <v>5.28</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>-0.0038</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3020000</v>
+        <v>3576700</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H52" t="n">
-        <v>44.03</v>
+        <v>41.57</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2828,10 +2821,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.509</v>
+        <v>5.469</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.465</v>
+        <v>5.482</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2844,28 +2837,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>2.68</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2961100</v>
+        <v>3534700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="H53" t="n">
-        <v>33.19</v>
+        <v>44.61</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2873,10 +2866,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.124</v>
+        <v>2.746</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.235</v>
+        <v>2.743</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2889,39 +2882,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0</v>
+        <v>7.34</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2890000</v>
+        <v>3472600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.85</v>
+        <v>0.33</v>
       </c>
       <c r="H54" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
+        <v>40.3</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.618</v>
+        <v>7.43</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.607</v>
+        <v>7.894</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2934,39 +2927,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.79</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.026</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2806300</v>
+        <v>3471500</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.26</v>
+        <v>1.31</v>
       </c>
       <c r="H55" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
+        <v>59.75</v>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.62</v>
+        <v>0.744</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.616</v>
+        <v>0.707</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2979,28 +2972,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.125</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2626800</v>
+        <v>3313200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.18</v>
+        <v>2.21</v>
       </c>
       <c r="H56" t="n">
-        <v>41.88</v>
+        <v>41.39</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3008,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.733</v>
+        <v>0.129</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.722</v>
+        <v>0.13</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3024,40 +3017,36 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>-0.017</v>
+        <v>0.215</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2545900</v>
+        <v>3233400</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="H57" t="n">
-        <v>39.33</v>
+        <v>87.13</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J57" s="9" t="n">
-        <v>5.462</v>
-      </c>
-      <c r="K57" s="9" t="n">
-        <v>5.481</v>
-      </c>
+      <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
     </row>
@@ -3069,28 +3058,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.825</v>
+        <v>4.8</v>
       </c>
       <c r="E58" s="15" t="n">
-        <v>0.0123</v>
+        <v>0.0105</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2345900</v>
+        <v>3206000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.67</v>
+        <v>0.13</v>
       </c>
       <c r="H58" t="n">
-        <v>51.51</v>
+        <v>46.7</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3098,10 +3087,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.825</v>
+        <v>4.88</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.789</v>
+        <v>4.741</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3114,28 +3103,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>-0.018</v>
+        <v>0.465</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.022</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2192500</v>
+        <v>3179800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="H59" t="n">
-        <v>57.48</v>
+        <v>43.04</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3143,10 +3132,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>3.689</v>
+        <v>0.508</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>3.103</v>
+        <v>0.465</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3159,28 +3148,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.965</v>
+        <v>0.765</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>0.0266</v>
+        <v>0.0132</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2180000</v>
+        <v>3121400</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H60" t="n">
-        <v>41.97</v>
+        <v>48.57</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3188,10 +3177,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.032</v>
+        <v>0.769</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.969</v>
+        <v>0.771</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3204,28 +3193,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.255</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>0.02</v>
+        <v>0.0698</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2068600</v>
+        <v>3109000</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="H61" t="n">
-        <v>41.5</v>
+        <v>43.48</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3233,10 +3222,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.27</v>
+        <v>0.734</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.29</v>
+        <v>0.723</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3249,28 +3238,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>0.0551</v>
+        <v>0.0184</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2054300</v>
+        <v>2962900</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.39</v>
+        <v>0.84</v>
       </c>
       <c r="H62" t="n">
-        <v>41.18</v>
+        <v>52.36</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3278,10 +3267,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.741</v>
+        <v>0.826</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3294,39 +3283,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3.32</v>
+        <v>0.97</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0184</v>
+        <v>0.0319</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2011300</v>
+        <v>2385100</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.63</v>
+        <v>0.28</v>
       </c>
       <c r="H63" t="n">
-        <v>87.45</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.7</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>2.914</v>
+        <v>1.032</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.485</v>
+        <v>0.969</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3339,28 +3328,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0.0462</v>
+        <v>3.82</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1911200</v>
+        <v>2320000</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="H64" t="n">
-        <v>49.7</v>
+        <v>57.48</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3368,10 +3357,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.344</v>
+        <v>3.689</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.335</v>
+        <v>3.103</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3384,28 +3373,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>-0.0097</v>
+        <v>0.335</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1834700</v>
+        <v>2187300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="H65" t="n">
-        <v>31.45</v>
+        <v>47.84</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3413,10 +3402,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.537</v>
+        <v>0.343</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.335</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3429,28 +3418,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0.0513</v>
+        <v>2.46</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1834200</v>
+        <v>2173000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
       <c r="H66" t="n">
-        <v>55.11</v>
+        <v>53.17</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3458,10 +3447,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.393</v>
+        <v>2.449</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.363</v>
+        <v>2.399</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3474,28 +3463,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.27</v>
+        <v>0.67</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.0189</v>
+        <v>0.0551</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1821400</v>
+        <v>2151800</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="H67" t="n">
-        <v>22.13</v>
+        <v>41.18</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3503,10 +3492,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.321</v>
+        <v>0.741</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.366</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3519,39 +3508,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.235</v>
+        <v>9.98</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>0.0444</v>
+        <v>0.003</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1802400</v>
+        <v>2119700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>5.18</v>
+        <v>0.17</v>
       </c>
       <c r="H68" t="n">
-        <v>73.31</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
+        <v>47</v>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.226</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.225</v>
+        <v>10.129</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3564,28 +3553,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.51</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1757900</v>
+        <v>2108700</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.2</v>
+        <v>0.77</v>
       </c>
       <c r="H69" t="n">
-        <v>39.47</v>
+        <v>31.45</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3593,10 +3582,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.285</v>
+        <v>0.537</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.315</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3609,28 +3598,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.13</v>
+        <v>0.255</v>
       </c>
       <c r="E70" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.02</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1756000</v>
+        <v>2099700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H70" t="n">
-        <v>60.5</v>
+        <v>41.5</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3638,10 +3627,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.068</v>
+        <v>0.27</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3654,33 +3643,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0</v>
+        <v>3.34</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.0245</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1752100</v>
+        <v>2062400</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="n"/>
-      <c r="K71" s="9" t="n"/>
+        <v>0.64</v>
+      </c>
+      <c r="H71" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>2.916</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>2.485</v>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
     </row>
@@ -3692,40 +3688,33 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1712600</v>
+        <v>2031000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H72" t="n">
-        <v>27.73</v>
+        <v>0.04</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J72" s="9" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K72" s="9" t="n">
-        <v>0.298</v>
-      </c>
+      <c r="J72" s="9" t="n"/>
+      <c r="K72" s="9" t="n"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
     </row>
@@ -3737,28 +3726,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.355</v>
+        <v>5.1</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>0.0441</v>
+        <v>0.0303</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1531700</v>
+        <v>1999100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.2</v>
+        <v>0.49</v>
       </c>
       <c r="H73" t="n">
-        <v>52.77</v>
+        <v>53.39</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3766,10 +3755,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.353</v>
+        <v>5.053</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.328</v>
+        <v>5.049</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3791,27 +3780,27 @@
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.0061</v>
+        <v>1.64</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1528500</v>
+        <v>1989400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="H74" t="n">
-        <v>51.66</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
+        <v>50.4</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.627</v>
+        <v>1.626</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>1.686</v>
@@ -3827,39 +3816,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.58</v>
+        <v>0.275</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0377</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1471300</v>
+        <v>1952500</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="H75" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.26</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.523</v>
+        <v>0.321</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.475</v>
+        <v>0.366</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3872,39 +3861,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>-0.0144</v>
+        <v>1.23</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1435400</v>
+        <v>1924000</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1.06</v>
+        <v>0.22</v>
       </c>
       <c r="H76" t="n">
-        <v>69.31999999999999</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.47</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>2.628</v>
+        <v>1.285</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2.452</v>
+        <v>1.315</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3917,28 +3906,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.845</v>
+        <v>1.13</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>0.0181</v>
+        <v>0.0089</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1402700</v>
+        <v>1874400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="H77" t="n">
-        <v>23.84</v>
+        <v>60.5</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3946,10 +3935,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.902</v>
+        <v>1.068</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.966</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3962,28 +3951,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1401700</v>
+        <v>1866900</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H78" t="n">
-        <v>53.17</v>
+        <v>30.55</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3991,10 +3980,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>2.449</v>
+        <v>0.489</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2.399</v>
+        <v>0.548</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4007,39 +3996,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>-0.0027</v>
+        <v>0.405</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.0385</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1367900</v>
+        <v>1844500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="H79" t="n">
-        <v>37</v>
-      </c>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.26</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>7.424</v>
+        <v>0.393</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>7.892</v>
+        <v>0.363</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4052,28 +4041,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.275</v>
+        <v>1.25</v>
       </c>
       <c r="E80" s="15" t="n">
-        <v>0.0185</v>
+        <v>0.0246</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1367800</v>
+        <v>1805600</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.12</v>
+        <v>0.59</v>
       </c>
       <c r="H80" t="n">
-        <v>45</v>
+        <v>48.41</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4081,10 +4070,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.287</v>
+        <v>1.278</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.283</v>
+        <v>1.23</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4097,39 +4086,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>9.970000000000001</v>
+        <v>0.235</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0.002</v>
+        <v>0.0444</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1367400</v>
+        <v>1802400</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.11</v>
+        <v>5.18</v>
       </c>
       <c r="H81" t="n">
-        <v>46.34</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
+        <v>73.31</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>9.994</v>
+        <v>0.226</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>10.129</v>
+        <v>0.225</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4142,38 +4131,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.385</v>
+        <v>0.26</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.0196</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1367200</v>
+        <v>1766600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H82" t="n">
-        <v>68.41</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.79</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="K82" s="9" t="n"/>
+        <v>0.273</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.298</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
     </row>
@@ -4185,39 +4176,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>0.0343</v>
+        <v>1.17</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1304600</v>
+        <v>1720600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H83" t="n">
-        <v>54.48</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.42</v>
+      </c>
+      <c r="I83" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>5.055</v>
+        <v>1.222</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>5.05</v>
+        <v>1.31</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4230,39 +4221,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>-0.0061</v>
+        <v>0.355</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>0.0441</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1290400</v>
+        <v>1658700</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="H84" t="n">
-        <v>61.34</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.77</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.797</v>
+        <v>0.353</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.774</v>
+        <v>0.328</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4275,39 +4266,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.0174</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1259200</v>
+        <v>1643500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="H85" t="n">
-        <v>36.07</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.97</v>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.251</v>
+        <v>0.523</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.272</v>
+        <v>0.475</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4320,39 +4311,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>0.0111</v>
+        <v>0.97</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1248200</v>
+        <v>1634900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="H86" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.02</v>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.489</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.548</v>
+        <v>0.883</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4365,39 +4356,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.96</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1245100</v>
+        <v>1626600</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="H87" t="n">
-        <v>35.17</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
+        <v>54.29</v>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.221</v>
+        <v>1.927</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.31</v>
+        <v>1.951</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4410,28 +4401,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.765</v>
+        <v>0.85</v>
       </c>
       <c r="E88" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.0241</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1216200</v>
+        <v>1604800</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="H88" t="n">
-        <v>60.12</v>
+        <v>26.29</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4439,10 +4430,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.749</v>
+        <v>0.902</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.721</v>
+        <v>0.967</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4455,39 +4446,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>1596000</v>
+      </c>
+      <c r="G89" s="12" t="n">
         <v>1.18</v>
       </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.008399999999999999</v>
-      </c>
-      <c r="F89" s="11" t="n">
-        <v>1207000</v>
-      </c>
-      <c r="G89" s="12" t="n">
-        <v>0.18</v>
-      </c>
       <c r="H89" t="n">
-        <v>52.11</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.173</v>
+        <v>2.627</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.143</v>
+        <v>2.452</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4500,28 +4491,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>0.0305</v>
+        <v>6.2</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1198800</v>
+        <v>1536500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H90" t="n">
-        <v>41.84</v>
+        <v>37.39</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4529,10 +4520,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.91</v>
+        <v>6.357</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.853</v>
+        <v>6.709</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4545,28 +4536,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DESTINI</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1160300</v>
+        <v>1534900</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>4.56</v>
+        <v>0.16</v>
       </c>
       <c r="H91" t="n">
-        <v>48.6</v>
+        <v>53.75</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -4574,10 +4565,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.229</v>
+        <v>1.083</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.243</v>
+        <v>1.05</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4590,39 +4581,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.82</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1150200</v>
+        <v>1455200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="H92" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
+        <v>66.97</v>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.248</v>
+        <v>0.798</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.185</v>
+        <v>0.774</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4635,39 +4626,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>-0.009000000000000001</v>
+        <v>2.07</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1145600</v>
+        <v>1408600</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.12</v>
+        <v>7.64</v>
       </c>
       <c r="H93" t="n">
-        <v>53.75</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.34</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.083</v>
+        <v>2.078</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.05</v>
+        <v>2.083</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4680,28 +4671,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.85</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.0366</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1118500</v>
+        <v>1400600</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H94" t="n">
-        <v>21.29</v>
+        <v>42.57</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4709,10 +4700,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.644</v>
+        <v>0.911</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.918</v>
+        <v>0.853</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4725,39 +4716,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>0.0039</v>
+        <v>2.09</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1093200</v>
+        <v>1400100</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="H95" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.56</v>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>2.599</v>
+        <v>2.104</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>2.61</v>
+        <v>2.103</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4770,28 +4761,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.62</v>
+        <v>0.275</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>0.0248</v>
+        <v>0.0185</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1058200</v>
+        <v>1392800</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>0.12</v>
       </c>
       <c r="H96" t="n">
-        <v>39.89</v>
+        <v>45</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4799,10 +4790,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.667</v>
+        <v>0.287</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.283</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4815,28 +4806,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>-0.0167</v>
+        <v>4.48</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1043700</v>
+        <v>1387100</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="H97" t="n">
-        <v>21.3</v>
+        <v>38.42</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4844,10 +4835,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.356</v>
+        <v>4.591</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.54</v>
+        <v>4.641</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4860,40 +4851,38 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.0263</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1037100</v>
+        <v>1383300</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="H98" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="I98" s="16" t="inlineStr">
+        <v>69.33</v>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="K98" s="9" t="n">
-        <v>0.384</v>
-      </c>
+        <v>0.331</v>
+      </c>
+      <c r="K98" s="9" t="n"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
     </row>
@@ -4905,28 +4894,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>-0.0058</v>
+        <v>0.44</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1022600</v>
+        <v>1344900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>34.28</v>
+        <v>25.69</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4934,10 +4923,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.761</v>
+        <v>0.495</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.874</v>
+        <v>0.653</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4950,39 +4939,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.545</v>
+        <v>0.245</v>
       </c>
       <c r="E100" s="15" t="n">
-        <v>0.0481</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1020000</v>
+        <v>1315500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.19</v>
+        <v>1.18</v>
       </c>
       <c r="H100" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.8</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.555</v>
+        <v>0.213</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.52</v>
+        <v>0.21</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4995,39 +4984,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0.0313</v>
+        <v>0.47</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>952300</v>
+        <v>1312700</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>0.16</v>
       </c>
       <c r="H101" t="n">
-        <v>57.54</v>
-      </c>
-      <c r="I101" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.3</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>6.233</v>
+        <v>0.5</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>5.95</v>
+        <v>0.521</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5040,39 +5029,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.635</v>
+        <v>0.62</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0248</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>940000</v>
+        <v>1273400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.45</v>
+        <v>0.14</v>
       </c>
       <c r="H102" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.89</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.636</v>
+        <v>0.667</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.625</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5085,39 +5074,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.97</v>
+        <v>0.235</v>
       </c>
       <c r="E103" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>922600</v>
+        <v>1268100</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.15</v>
+        <v>0.74</v>
       </c>
       <c r="H103" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.07</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.251</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.883</v>
+        <v>0.272</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5130,39 +5119,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>906300</v>
+        <v>1255900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>4.92</v>
+        <v>0.95</v>
       </c>
       <c r="H104" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="I104" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.12</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>2.078</v>
+        <v>0.749</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>2.083</v>
+        <v>0.721</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5190,10 +5179,10 @@
         <v>0.003</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>881600</v>
+        <v>1235300</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H105" t="n">
         <v>32.94</v>
@@ -5220,28 +5209,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="E106" s="15" t="n">
-        <v>0.0314</v>
+        <v>1.43</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>852100</v>
+        <v>1224300</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.33</v>
+        <v>0.1</v>
       </c>
       <c r="H106" t="n">
-        <v>44.65</v>
+        <v>21.69</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5249,10 +5238,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>2.082</v>
+        <v>1.645</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.993</v>
+        <v>1.918</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5265,39 +5254,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0</v>
+        <v>1.18</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>843200</v>
+        <v>1218500</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H107" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.3</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.926</v>
+        <v>1.356</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.951</v>
+        <v>1.54</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5310,39 +5299,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.77</v>
+        <v>0.64</v>
       </c>
       <c r="E108" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.0159</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>839000</v>
+        <v>1216600</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="H108" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.16</v>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.87</v>
+        <v>0.637</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>3.002</v>
+        <v>0.625</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5355,28 +5344,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>0.0488</v>
+        <v>1.18</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>816400</v>
+        <v>1207000</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H109" t="n">
-        <v>36.61</v>
+        <v>52.11</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5384,10 +5373,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.707</v>
+        <v>1.173</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.742</v>
+        <v>1.143</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5400,39 +5389,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>2.34</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>806300</v>
+        <v>1178400</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="H110" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.79</v>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>1.69</v>
+        <v>2.247</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>1.757</v>
+        <v>2.184</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5445,28 +5434,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>DESTINI</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>0.0192</v>
+        <v>0.23</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>795300</v>
+        <v>1160300</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.25</v>
+        <v>4.56</v>
       </c>
       <c r="H111" t="n">
-        <v>46.42</v>
+        <v>48.6</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5474,10 +5463,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>3.821</v>
+        <v>0.229</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>3.711</v>
+        <v>0.243</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5490,39 +5479,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2.14</v>
+        <v>0.545</v>
       </c>
       <c r="E112" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0481</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>754200</v>
+        <v>1145500</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.36</v>
+        <v>0.21</v>
       </c>
       <c r="H112" t="n">
-        <v>55.85</v>
-      </c>
-      <c r="I112" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.45</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2.113</v>
+        <v>0.555</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.07</v>
+        <v>0.52</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5535,28 +5524,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>746500</v>
+        <v>1144300</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="H113" t="n">
-        <v>33</v>
+        <v>46.18</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5564,10 +5553,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.839</v>
+        <v>2.599</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.859</v>
+        <v>2.61</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5580,28 +5569,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>0.0388</v>
+        <v>1.7</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>745200</v>
+        <v>1103600</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H114" t="n">
-        <v>50.18</v>
+        <v>34.28</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5609,10 +5598,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>7.306</v>
+        <v>1.761</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>6.915</v>
+        <v>1.874</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5625,39 +5614,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.47</v>
+        <v>6.53</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.0235</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>736500</v>
+        <v>1094800</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="H115" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.85</v>
+      </c>
+      <c r="I115" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.593</v>
+        <v>6.228</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>1.656</v>
+        <v>5.949</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5670,39 +5659,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>3.28</v>
+        <v>0.915</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>0.025</v>
+        <v>0.0167</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>726000</v>
+        <v>1075800</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.12</v>
+        <v>0.61</v>
       </c>
       <c r="H116" t="n">
-        <v>40.38</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.28</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>3.343</v>
+        <v>0.914</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>3.582</v>
+        <v>0.883</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5715,28 +5704,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.59</v>
+        <v>1.11</v>
       </c>
       <c r="E117" s="15" t="n">
-        <v>0.0442</v>
+        <v>0.0374</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>714100</v>
+        <v>1074900</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="H117" t="n">
-        <v>49.58</v>
+        <v>46.18</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5744,10 +5733,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.594</v>
+        <v>1.144</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.586</v>
+        <v>1.105</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5760,39 +5749,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.1</v>
+        <v>0.35</v>
       </c>
       <c r="E118" s="15" t="n">
-        <v>0.028</v>
+        <v>0.0145</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>697700</v>
+        <v>1057200</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.19</v>
+        <v>0.68</v>
       </c>
       <c r="H118" t="n">
-        <v>44.65</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.59</v>
+      </c>
+      <c r="I118" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.143</v>
+        <v>0.356</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.105</v>
+        <v>0.384</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5805,28 +5794,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>2.79</v>
+        <v>1.55</v>
       </c>
       <c r="E119" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>669400</v>
+        <v>1016600</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="H119" t="n">
-        <v>51.36</v>
+        <v>29.96</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5834,10 +5823,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>2.793</v>
+        <v>1.69</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.677</v>
+        <v>1.757</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5850,28 +5839,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>3.76</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.0301</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>656800</v>
+        <v>959800</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="H120" t="n">
-        <v>23.81</v>
+        <v>48.2</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5879,10 +5868,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.96</v>
+        <v>3.824</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.044</v>
+        <v>3.711</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5895,39 +5884,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0360</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SAG</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>-0.0234</v>
+        <v>1.97</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>0.0314</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>652200</v>
+        <v>952200</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>3.65</v>
+        <v>0.36</v>
       </c>
       <c r="H121" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.65</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.637</v>
+        <v>2.082</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.644</v>
+        <v>1.993</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5940,28 +5929,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>2.77</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>648100</v>
+        <v>946500</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="H122" t="n">
-        <v>28.87</v>
+        <v>40.89</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5969,10 +5958,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.219</v>
+        <v>2.87</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.306</v>
+        <v>3.002</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5985,39 +5974,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>7.5</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>0.0027</v>
+        <v>0.0224</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>647500</v>
+        <v>945500</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="H123" t="n">
-        <v>45.97</v>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.03</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>7.561</v>
+        <v>0.715</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>7.745</v>
+        <v>0.781</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6030,28 +6019,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>0.0311</v>
+        <v>7.67</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>639500</v>
+        <v>900700</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="H124" t="n">
-        <v>56.5</v>
+        <v>37.97</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6059,10 +6048,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>10.424</v>
+        <v>7.822</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>9.805</v>
+        <v>7.858</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6075,28 +6064,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0</v>
+        <v>7.23</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0.0388</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>625000</v>
+        <v>897000</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="H125" t="n">
-        <v>42.09</v>
+        <v>50.18</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6104,10 +6093,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.727</v>
+        <v>7.306</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.743</v>
+        <v>6.915</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6120,28 +6109,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>0.0121</v>
+        <v>1</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>622700</v>
+        <v>876600</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.19</v>
+        <v>0.76</v>
       </c>
       <c r="H126" t="n">
-        <v>33.02</v>
+        <v>35.9</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6149,10 +6138,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.883</v>
+        <v>1.042</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.945</v>
+        <v>1.134</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6165,28 +6154,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>5.67</v>
+        <v>1.48</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>0.0053</v>
+        <v>0.0137</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>583400</v>
+        <v>869600</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.08</v>
+        <v>0.47</v>
       </c>
       <c r="H127" t="n">
-        <v>34.2</v>
+        <v>35.83</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6194,10 +6183,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>5.859</v>
+        <v>1.594</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>6.145</v>
+        <v>1.656</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6210,28 +6199,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.785</v>
+        <v>0.645</v>
       </c>
       <c r="E128" s="15" t="n">
-        <v>0.0129</v>
+        <v>0.0488</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>577200</v>
+        <v>841600</v>
       </c>
       <c r="G128" s="12" t="n">
         <v>0.25</v>
       </c>
       <c r="H128" t="n">
-        <v>18.07</v>
+        <v>36.61</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6239,10 +6228,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.91</v>
+        <v>0.707</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.062</v>
+        <v>0.742</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6255,39 +6244,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E129" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.59</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>0.0442</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>575100</v>
+        <v>830100</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.52</v>
+        <v>0.19</v>
       </c>
       <c r="H129" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.58</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.633</v>
+        <v>0.594</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.631</v>
+        <v>0.586</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6300,39 +6289,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.19</v>
+        <v>3.28</v>
       </c>
       <c r="E130" s="15" t="n">
-        <v>0.0259</v>
+        <v>0.025</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>573500</v>
+        <v>820300</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="H130" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.38</v>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.228</v>
+        <v>3.343</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.085</v>
+        <v>3.582</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6345,39 +6334,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>-0.0048</v>
+        <v>2.8</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>544700</v>
+        <v>820100</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H131" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I131" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.91</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>2.103</v>
+        <v>2.794</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>2.103</v>
+        <v>2.677</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6390,28 +6379,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0.0208</v>
+        <v>0.915</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>536600</v>
+        <v>788400</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="H132" t="n">
-        <v>51.23</v>
+        <v>23.81</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6419,10 +6408,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.74</v>
+        <v>0.96</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>1.044</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6435,28 +6424,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.995</v>
+        <v>5.65</v>
       </c>
       <c r="E133" s="15" t="n">
-        <v>0.0258</v>
+        <v>0.0018</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>534300</v>
+        <v>787600</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H133" t="n">
-        <v>46.41</v>
+        <v>32.61</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6464,10 +6453,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.034</v>
+        <v>5.857</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.955</v>
+        <v>6.145</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6480,28 +6469,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>0.0317</v>
+        <v>3.9</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>530000</v>
+        <v>773200</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="H134" t="n">
-        <v>55.45</v>
+        <v>50.42</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6509,10 +6498,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.265</v>
+        <v>3.949</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.179</v>
+        <v>3.587</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6525,28 +6514,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0</v>
+        <v>0.835</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>524600</v>
+        <v>766300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="H135" t="n">
-        <v>41.69</v>
+        <v>33.02</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6554,10 +6543,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>2.11</v>
+        <v>0.883</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>2.265</v>
+        <v>0.945</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6570,28 +6559,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.915</v>
+        <v>10.58</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.0272</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>522200</v>
+        <v>756200</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H136" t="n">
-        <v>51.28</v>
+        <v>55.88</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6599,10 +6588,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.914</v>
+        <v>10.421</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.883</v>
+        <v>9.805</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6615,45 +6604,945 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>3.11</v>
+        <v>2.14</v>
       </c>
       <c r="E137" s="15" t="n">
-        <v>0.0032</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>503700</v>
+        <v>754200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H137" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.85</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>3.161</v>
+        <v>2.113</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>2.911</v>
+        <v>2.07</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>747400</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H138" t="n">
+        <v>33</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>724100</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H139" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>7.561</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>7.745</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H140" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>683400</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H141" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>678500</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H142" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0360</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SAG</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>652200</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H143" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="I143" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>646400</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H144" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>645100</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H145" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="I145" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>630000</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H146" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>623300</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H147" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>609200</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H148" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>606800</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H149" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="I149" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>605500</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H150" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>603600</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H151" t="n">
+        <v>51.29</v>
+      </c>
+      <c r="I151" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>4.374</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>4.431</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>582500</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H152" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E153" s="15" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>569600</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H153" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>1.178</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>543600</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H154" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>534500</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H155" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>506500</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H156" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>2.911</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>502900</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H157" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>4.373</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>4.681</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M137"/>
+  <autoFilter ref="A1:M157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,8 +97,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.012</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5975700</v>
+        <v>6478000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>58.95</v>
@@ -625,7 +625,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>57902200</v>
+        <v>58222600</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -655,19 +655,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.145</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>31840000</v>
+        <v>32068300</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>37.84</v>
+        <v>31.27</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.184</v>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>28607400</v>
+        <v>30693800</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>0.08</v>
@@ -736,28 +736,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>-0.05</v>
+        <v>0.16</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0.1429</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>25966400</v>
+        <v>30524300</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.22</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
-        <v>33.93</v>
+        <v>52.3</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.214</v>
+        <v>0.157</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.233</v>
+        <v>0.142</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,21 +790,21 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.915</v>
+        <v>0.92</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>25131900</v>
+        <v>27325100</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="H7" t="n">
-        <v>67.05</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -826,28 +826,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.195</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>23296800</v>
+        <v>26021700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.28</v>
+        <v>1.23</v>
       </c>
       <c r="H8" t="n">
-        <v>67.47</v>
+        <v>35.85</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.311</v>
+        <v>0.214</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.261</v>
+        <v>0.233</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -871,28 +871,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.155</v>
+        <v>0.35</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.1071</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>21626800</v>
+        <v>24556400</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H9" t="n">
-        <v>50.11</v>
+        <v>68.58</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.157</v>
+        <v>0.311</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.142</v>
+        <v>0.261</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -927,14 +927,14 @@
       <c r="D10" s="9" t="n">
         <v>0.175</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>-0.0278</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>18369800</v>
+        <v>19439200</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="H10" t="n">
         <v>41.19</v>
@@ -970,21 +970,21 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>13819200</v>
+        <v>19319200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>2.61</v>
+        <v>3.65</v>
       </c>
       <c r="H11" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
+        <v>64.81</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1006,39 +1006,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.0142</v>
+        <v>0.465</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>13418000</v>
+        <v>18671600</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="H12" t="n">
-        <v>81.19</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
+        <v>79.34</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.635</v>
+        <v>0.4</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.543</v>
+        <v>0.294</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,39 +1051,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1.3</v>
+        <v>0.715</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.0236</v>
+        <v>0.0142</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>11392600</v>
+        <v>13713300</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.78</v>
+        <v>0.54</v>
       </c>
       <c r="H13" t="n">
-        <v>63.96</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
+        <v>81.19</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.214</v>
+        <v>0.635</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.197</v>
+        <v>0.543</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.036</v>
+        <v>0.155</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>10454100</v>
+        <v>13294000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.51</v>
+        <v>0.38</v>
       </c>
       <c r="H14" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.42</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.572</v>
+        <v>0.155</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.544</v>
+        <v>0.156</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10249000</v>
+        <v>11684500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.64</v>
+        <v>1.83</v>
       </c>
       <c r="H15" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
+        <v>62.98</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.213</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.197</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,39 +1186,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>-0.0106</v>
+        <v>0.82</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10050000</v>
+        <v>11466800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.29</v>
+        <v>0.71</v>
       </c>
       <c r="H16" t="n">
-        <v>79.34</v>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
+        <v>55.6</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.4</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.294</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,39 +1231,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>-0.0667</v>
+        <v>0.57</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.027</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>9279300</v>
+        <v>11090500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>9.1</v>
+        <v>0.54</v>
       </c>
       <c r="H17" t="n">
-        <v>51.64</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.13</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.544</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,27 +1285,27 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.77</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>9259200</v>
+        <v>10333500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="H18" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
+        <v>46.5</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0.776</v>
@@ -1321,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.0112</v>
+        <v>0.305</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8940500</v>
+        <v>9755300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
-        <v>59.14</v>
+        <v>47.41</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.427</v>
+        <v>0.308</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.375</v>
+        <v>0.301</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,33 +1366,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.0204</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>-0.0667</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>8364800</v>
+        <v>9384500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
+        <v>9.210000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.06900000000000001</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
     </row>
@@ -1404,28 +1411,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TALAMT</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7528700</v>
+        <v>8988900</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>5.53</v>
+        <v>0.43</v>
       </c>
       <c r="H21" t="n">
-        <v>44.56</v>
+        <v>59.14</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1433,10 +1440,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.078</v>
+        <v>0.427</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.081</v>
+        <v>0.375</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1449,40 +1456,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6416300</v>
+        <v>8364800</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H22" t="n">
-        <v>47.41</v>
+        <v>0.37</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="9" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.301</v>
-      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1494,39 +1494,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0.0611</v>
+        <v>0.865</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6351300</v>
+        <v>8083400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1.23</v>
+        <v>0.4</v>
       </c>
       <c r="H23" t="n">
-        <v>35.27</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.09</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>2.728</v>
+        <v>0.868</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>2.868</v>
+        <v>0.869</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,28 +1539,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0361</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6273600</v>
+        <v>8083000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="H24" t="n">
-        <v>41.87</v>
+        <v>37.98</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.63</v>
+        <v>0.467</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.619</v>
+        <v>0.48</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,28 +1584,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>TALAMT</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>0.0361</v>
+        <v>0.075</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6261200</v>
+        <v>7550100</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.17</v>
+        <v>5.54</v>
       </c>
       <c r="H25" t="n">
-        <v>37.98</v>
+        <v>44.56</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.467</v>
+        <v>0.078</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.48</v>
+        <v>0.081</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,39 +1629,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>-0.0042</v>
+        <v>2.41</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.0524</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6171900</v>
+        <v>6879900</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.3</v>
+        <v>1.33</v>
       </c>
       <c r="H26" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.19</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>4.727</v>
+        <v>2.726</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>4.832</v>
+        <v>2.868</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,28 +1674,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0849</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5838800</v>
+        <v>6693100</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.45</v>
+        <v>0.72</v>
       </c>
       <c r="H27" t="n">
-        <v>28.46</v>
+        <v>40.99</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.229</v>
+        <v>0.63</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.279</v>
+        <v>0.619</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,28 +1719,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.93</v>
+        <v>0.115</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.0164</v>
+        <v>0.0455</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5813300</v>
+        <v>6563700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.39</v>
+        <v>0.34</v>
       </c>
       <c r="H28" t="n">
-        <v>59.5</v>
+        <v>34.73</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.856</v>
+        <v>0.138</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.599</v>
+        <v>0.148</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,39 +1764,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.275</v>
+        <v>0.51</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.0377</v>
+        <v>0.0968</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5636100</v>
+        <v>6526600</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.84</v>
+        <v>2.8</v>
       </c>
       <c r="H29" t="n">
-        <v>35.22</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.20999999999999</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.307</v>
+        <v>0.43</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.331</v>
+        <v>0.435</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,39 +1809,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>4.71</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5577600</v>
+        <v>6518500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="H30" t="n">
-        <v>32.87</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.91</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>7.44</v>
+        <v>4.727</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>7.66</v>
+        <v>4.832</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0</v>
+        <v>7.14</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5388100</v>
+        <v>6059000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H31" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.57</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.868</v>
+        <v>7.439</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.869</v>
+        <v>7.659</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0164</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5288100</v>
+        <v>6027100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="H32" t="n">
-        <v>66.59</v>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.5</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.101</v>
+        <v>0.856</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.091</v>
+        <v>0.599</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,28 +1944,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.175</v>
+        <v>0.205</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4943800</v>
+        <v>6003200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.88</v>
+        <v>0.46</v>
       </c>
       <c r="H33" t="n">
-        <v>48.63</v>
+        <v>28.46</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.174</v>
+        <v>0.229</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.181</v>
+        <v>0.279</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,39 +1989,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>AIZO</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>-0.0313</v>
+        <v>0.04</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.3333</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4915900</v>
+        <v>5933000</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.14</v>
+        <v>3.91</v>
       </c>
       <c r="H34" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
+        <v>64.33</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.155</v>
+        <v>0.034</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.156</v>
+        <v>0.036</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.0566</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4834800</v>
+        <v>5773800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.48</v>
+        <v>0.86</v>
       </c>
       <c r="H35" t="n">
-        <v>38.25</v>
+        <v>37.59</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.292</v>
+        <v>0.307</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.28</v>
+        <v>0.331</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2088,30 +2088,30 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>0.0354</v>
+        <v>0.0404</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4808300</v>
+        <v>5446100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H36" t="n">
-        <v>59.42</v>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
+        <v>59.89</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.948</v>
+        <v>1.949</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.765</v>
+        <v>1.766</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2135,19 +2135,19 @@
       <c r="D37" s="9" t="n">
         <v>0.63</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>-0.007900000000000001</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4350500</v>
+        <v>5359900</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="H37" t="n">
         <v>58.13</v>
       </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="I37" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.0417</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4344600</v>
+        <v>5288200</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H38" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
+        <v>66.59</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.123</v>
+        <v>0.101</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.124</v>
+        <v>0.091</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,28 +2214,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0049</v>
+        <v>0.265</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4245000</v>
+        <v>4984800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="H39" t="n">
-        <v>48.15</v>
+        <v>38.25</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>2.043</v>
+        <v>0.292</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>2.068</v>
+        <v>0.28</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,39 +2259,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>0.0538</v>
+        <v>0.175</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4236800</v>
+        <v>4953800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.82</v>
+        <v>0.88</v>
       </c>
       <c r="H40" t="n">
-        <v>75.95</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.428</v>
+        <v>0.174</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.434</v>
+        <v>0.181</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,40 +2304,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.115</v>
+        <v>0.22</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.0732</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4171500</v>
+        <v>4889700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.21</v>
+        <v>0.51</v>
       </c>
       <c r="H41" t="n">
-        <v>34.73</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J41" s="9" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>0.148</v>
-      </c>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
     </row>
@@ -2349,28 +2345,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.61</v>
+        <v>5.34</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>0.08929999999999999</v>
+        <v>0.0075</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4051900</v>
+        <v>4876800</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.68</v>
+        <v>0.37</v>
       </c>
       <c r="H42" t="n">
-        <v>58.07</v>
+        <v>44.1</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2378,10 +2374,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.573</v>
+        <v>5.474</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.476</v>
+        <v>5.484</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,33 +2390,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>-0.08699999999999999</v>
+        <v>2.57</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3926000</v>
+        <v>4486500</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
+      </c>
+      <c r="H43" t="n">
+        <v>46.99</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
+      <c r="J43" s="9" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>2.56</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
     </row>
@@ -2432,39 +2435,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>4462600</v>
+      </c>
+      <c r="G44" s="12" t="n">
         <v>0.38</v>
       </c>
-      <c r="E44" s="15" t="n">
-        <v>0.0133</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>3870500</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>0.54</v>
-      </c>
       <c r="H44" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="I44" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.35</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.372</v>
+        <v>2.447</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.37</v>
+        <v>2.399</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,28 +2480,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>2.02</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3855100</v>
+        <v>4421600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="H45" t="n">
-        <v>49.15</v>
+        <v>44.19</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2506,10 +2509,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.295</v>
+        <v>2.041</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.295</v>
+        <v>2.068</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2533,14 +2536,14 @@
       <c r="D46" s="9" t="n">
         <v>0.39</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>-0.025</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3828900</v>
+        <v>4408200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H46" t="n">
         <v>27.8</v>
@@ -2567,28 +2570,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.44</v>
+        <v>2.05</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.0602</v>
+        <v>0.0149</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3790600</v>
+        <v>4345000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="H47" t="n">
-        <v>54.38</v>
+        <v>37.82</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2596,10 +2599,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.425</v>
+        <v>2.127</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.417</v>
+        <v>2.235</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,39 +2615,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.56</v>
+        <v>0.125</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>0.0039</v>
+        <v>0.0417</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3750100</v>
+        <v>4344600</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.21</v>
+        <v>1.2</v>
       </c>
       <c r="H48" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.628</v>
+        <v>0.123</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.559</v>
+        <v>0.124</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2660,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.09820000000000001</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3657100</v>
+        <v>4230100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="H49" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I49" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.6</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.618</v>
+        <v>0.574</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.607</v>
+        <v>0.477</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,28 +2705,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.03</v>
+        <v>0.445</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>0.005</v>
+        <v>0.0723</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3622800</v>
+        <v>4180900</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.31</v>
+        <v>0.59</v>
       </c>
       <c r="H50" t="n">
-        <v>34.81</v>
+        <v>55.39</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2731,10 +2734,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.125</v>
+        <v>0.426</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.235</v>
+        <v>0.417</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2750,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.165</v>
+        <v>0.44</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3613900</v>
+        <v>4155800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.65</v>
+        <v>0.21</v>
       </c>
       <c r="H51" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.69</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.175</v>
+        <v>0.495</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.195</v>
+        <v>0.653</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,40 +2795,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>-0.0038</v>
+        <v>0.105</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3576700</v>
+        <v>4112200</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H52" t="n">
-        <v>41.57</v>
+        <v>0.11</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J52" s="9" t="n">
-        <v>5.469</v>
-      </c>
-      <c r="K52" s="9" t="n">
-        <v>5.482</v>
-      </c>
+      <c r="J52" s="9" t="n"/>
+      <c r="K52" s="9" t="n"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
     </row>
@@ -2837,39 +2833,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.68</v>
+        <v>0.385</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.0075</v>
+        <v>0.0267</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3534700</v>
+        <v>4040100</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.746</v>
+        <v>0.373</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.743</v>
+        <v>0.37</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,39 +2878,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>7.34</v>
+        <v>0.63</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3472600</v>
+        <v>3984500</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.33</v>
+        <v>1.17</v>
       </c>
       <c r="H54" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
+        <v>75.14</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>7.43</v>
+        <v>0.619</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>7.894</v>
+        <v>0.608</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,39 +2923,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.026</v>
+        <v>7.3</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3471500</v>
+        <v>3975200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1.31</v>
+        <v>0.38</v>
       </c>
       <c r="H55" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="I55" s="17" t="inlineStr">
+        <v>37.78</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.744</v>
+        <v>7.426</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.707</v>
+        <v>7.893</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,28 +2968,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.125</v>
+        <v>0.295</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3313200</v>
+        <v>3855100</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>2.21</v>
+        <v>1.15</v>
       </c>
       <c r="H56" t="n">
-        <v>41.39</v>
+        <v>49.15</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3001,10 +2997,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.129</v>
+        <v>0.295</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.13</v>
+        <v>0.295</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,36 +3013,40 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.215</v>
+        <v>0.675</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>0.0488</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3233400</v>
+        <v>3835900</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="H57" t="n">
-        <v>87.13</v>
+        <v>41.05</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J57" s="9" t="n"/>
-      <c r="K57" s="9" t="n"/>
+      <c r="J57" s="9" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>0.722</v>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
     </row>
@@ -3058,39 +3058,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0.0105</v>
+        <v>0.165</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3206000</v>
+        <v>3735500</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.13</v>
+        <v>0.67</v>
       </c>
       <c r="H58" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>4.88</v>
+        <v>0.175</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>4.741</v>
+        <v>0.195</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3103,28 +3103,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.465</v>
+        <v>0.83</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.022</v>
+        <v>0.0184</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3179800</v>
+        <v>3708000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.31</v>
+        <v>1.05</v>
       </c>
       <c r="H59" t="n">
-        <v>43.04</v>
+        <v>52.36</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.508</v>
+        <v>0.826</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.465</v>
+        <v>0.789</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3148,39 +3148,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.765</v>
+        <v>0.79</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.026</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3121400</v>
+        <v>3669900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.38</v>
+        <v>1.39</v>
       </c>
       <c r="H60" t="n">
-        <v>48.57</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.75</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.769</v>
+        <v>0.744</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.771</v>
+        <v>0.707</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3193,28 +3193,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>0.0698</v>
+        <v>0.011</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3109000</v>
+        <v>3568600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="H61" t="n">
-        <v>43.48</v>
+        <v>42.02</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.734</v>
+        <v>0.508</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.723</v>
+        <v>0.465</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3238,28 +3238,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.83</v>
+        <v>2.68</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>0.0184</v>
+        <v>0.0075</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2962900</v>
+        <v>3553700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.84</v>
+        <v>0.29</v>
       </c>
       <c r="H62" t="n">
-        <v>52.36</v>
+        <v>44.61</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.826</v>
+        <v>2.746</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.789</v>
+        <v>2.743</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3283,28 +3283,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.97</v>
+        <v>4.81</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0319</v>
+        <v>0.0126</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2385100</v>
+        <v>3456500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.28</v>
+        <v>0.14</v>
       </c>
       <c r="H63" t="n">
-        <v>42.7</v>
+        <v>47.25</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.032</v>
+        <v>4.881</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.969</v>
+        <v>4.742</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3328,28 +3328,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>-0.018</v>
+        <v>0.125</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2320000</v>
+        <v>3313200</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.29</v>
+        <v>2.21</v>
       </c>
       <c r="H64" t="n">
-        <v>57.48</v>
+        <v>41.39</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>3.689</v>
+        <v>0.129</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>3.103</v>
+        <v>0.13</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3373,28 +3373,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.335</v>
+        <v>0.765</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0.0308</v>
+        <v>0.0132</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2187300</v>
+        <v>3222600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="H65" t="n">
-        <v>47.84</v>
+        <v>48.57</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.343</v>
+        <v>0.769</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.335</v>
+        <v>0.771</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3418,39 +3418,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0</v>
+        <v>1.96</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2173000</v>
+        <v>3078500</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.19</v>
+        <v>0.51</v>
       </c>
       <c r="H66" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.29</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.449</v>
+        <v>1.927</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.399</v>
+        <v>1.951</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3463,28 +3463,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>0.0551</v>
+        <v>6.21</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2151800</v>
+        <v>2922200</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="H67" t="n">
-        <v>41.18</v>
+        <v>37.8</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.741</v>
+        <v>6.358</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>6.709</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3508,39 +3508,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>9.98</v>
+        <v>5.1</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>0.003</v>
+        <v>0.0303</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2119700</v>
+        <v>2726400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.17</v>
+        <v>0.67</v>
       </c>
       <c r="H68" t="n">
-        <v>47</v>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.39</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>9.994999999999999</v>
+        <v>5.053</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>10.129</v>
+        <v>5.049</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3553,28 +3553,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>-0.0097</v>
+        <v>1.24</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2108700</v>
+        <v>2715300</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.77</v>
+        <v>0.32</v>
       </c>
       <c r="H69" t="n">
-        <v>31.45</v>
+        <v>41.31</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.537</v>
+        <v>1.286</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>1.315</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3598,39 +3598,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.255</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E70" s="15" t="n">
-        <v>0.02</v>
+        <v>0.002</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2099700</v>
+        <v>2710800</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="H70" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.34</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.27</v>
+        <v>9.994</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.29</v>
+        <v>10.129</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3643,39 +3643,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.0245</v>
+        <v>0.255</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2062400</v>
+        <v>2648900</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="H71" t="n">
-        <v>87.79000000000001</v>
-      </c>
-      <c r="I71" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.73</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.916</v>
+        <v>0.272</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.485</v>
+        <v>0.298</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3688,33 +3688,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.77</v>
+        <v>5.66</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0035</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2031000</v>
+        <v>2633800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.04</v>
+        <v>0.34</v>
+      </c>
+      <c r="H72" t="n">
+        <v>33.42</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J72" s="9" t="n"/>
-      <c r="K72" s="9" t="n"/>
+      <c r="J72" s="9" t="n">
+        <v>5.858</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>6.145</v>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
     </row>
@@ -3726,28 +3733,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>5.1</v>
+        <v>0.97</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.0319</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1999100</v>
+        <v>2577000</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="H73" t="n">
-        <v>53.39</v>
+        <v>42.7</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3755,10 +3762,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>5.053</v>
+        <v>1.032</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>5.049</v>
+        <v>0.969</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3771,39 +3778,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0</v>
+        <v>3.85</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1989400</v>
+        <v>2556900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="H74" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.51</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.626</v>
+        <v>3.692</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.686</v>
+        <v>3.104</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3816,28 +3823,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.275</v>
+        <v>0.455</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>0.0377</v>
+        <v>0.0111</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1952500</v>
+        <v>2405000</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0.32</v>
       </c>
       <c r="H75" t="n">
-        <v>25.26</v>
+        <v>30.55</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3845,10 +3852,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.321</v>
+        <v>0.489</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.366</v>
+        <v>0.548</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3861,28 +3868,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>1.23</v>
+        <v>0.865</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1924000</v>
+        <v>2340500</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.22</v>
+        <v>0.73</v>
       </c>
       <c r="H76" t="n">
-        <v>39.47</v>
+        <v>32.77</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3890,10 +3897,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.285</v>
+        <v>0.904</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.315</v>
+        <v>0.967</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3906,28 +3913,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.13</v>
+        <v>0.335</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.0308</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1874400</v>
+        <v>2266300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="H77" t="n">
-        <v>60.5</v>
+        <v>47.84</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3935,10 +3942,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.068</v>
+        <v>0.343</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3951,40 +3958,33 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.0111</v>
+        <v>0.765</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1866900</v>
+        <v>2208900</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H78" t="n">
-        <v>30.55</v>
+        <v>0.04</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J78" s="9" t="n">
-        <v>0.489</v>
-      </c>
-      <c r="K78" s="9" t="n">
-        <v>0.548</v>
-      </c>
+      <c r="J78" s="9" t="n"/>
+      <c r="K78" s="9" t="n"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
     </row>
@@ -3996,28 +3996,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.405</v>
+        <v>0.67</v>
       </c>
       <c r="E79" s="15" t="n">
-        <v>0.0385</v>
+        <v>0.0551</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1844500</v>
+        <v>2205700</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="H79" t="n">
-        <v>54.26</v>
+        <v>41.18</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.393</v>
+        <v>0.741</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.363</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4041,28 +4041,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.0246</v>
+        <v>0.51</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1805600</v>
+        <v>2179800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="H80" t="n">
-        <v>48.41</v>
+        <v>31.45</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1.278</v>
+        <v>0.537</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.23</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4086,39 +4086,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.235</v>
+        <v>0.405</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0.0444</v>
+        <v>0.0385</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1802400</v>
+        <v>2173100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>5.18</v>
+        <v>0.37</v>
       </c>
       <c r="H81" t="n">
-        <v>73.31</v>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.26</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.226</v>
+        <v>0.393</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.225</v>
+        <v>0.363</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4131,28 +4131,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.26</v>
+        <v>0.255</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.0196</v>
+        <v>0.02</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1766600</v>
+        <v>2147700</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H82" t="n">
-        <v>33.79</v>
+        <v>41.5</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.273</v>
+        <v>0.27</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.298</v>
+        <v>0.29</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,39 +4176,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0</v>
+        <v>3.34</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0245</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1720600</v>
+        <v>2146100</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.22</v>
+        <v>0.67</v>
       </c>
       <c r="H83" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I83" s="17" t="inlineStr">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.222</v>
+        <v>2.916</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.31</v>
+        <v>2.485</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4221,28 +4221,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.355</v>
+        <v>1.28</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0441</v>
+        <v>0.0492</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1658700</v>
+        <v>2028500</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="H84" t="n">
-        <v>52.77</v>
+        <v>50.75</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.353</v>
+        <v>1.281</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.328</v>
+        <v>1.231</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4266,39 +4266,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0.0174</v>
+        <v>1.64</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1643500</v>
+        <v>2023200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="H85" t="n">
-        <v>65.97</v>
-      </c>
-      <c r="I85" s="17" t="inlineStr">
+        <v>50.4</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.523</v>
+        <v>1.626</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.475</v>
+        <v>1.686</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,39 +4311,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1634900</v>
+        <v>2002900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="H86" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="I86" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.5</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.068</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.883</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,39 +4356,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.96</v>
+        <v>0.275</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>0.0051</v>
+        <v>0.0377</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1626600</v>
+        <v>1956400</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H87" t="n">
-        <v>54.29</v>
-      </c>
-      <c r="I87" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.26</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.927</v>
+        <v>0.321</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.951</v>
+        <v>0.366</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4401,28 +4401,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>0.0241</v>
+        <v>4.46</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1604800</v>
+        <v>1886000</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="H88" t="n">
-        <v>26.29</v>
+        <v>36.71</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.902</v>
+        <v>4.589</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.967</v>
+        <v>4.64</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,39 +4446,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>-0.018</v>
+        <v>0.585</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.0174</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1596000</v>
+        <v>1882900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>1.18</v>
+        <v>0.45</v>
       </c>
       <c r="H89" t="n">
-        <v>67.76000000000001</v>
-      </c>
-      <c r="I89" s="17" t="inlineStr">
+        <v>65.97</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>2.627</v>
+        <v>0.523</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>2.452</v>
+        <v>0.475</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,28 +4491,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>-0.0016</v>
+        <v>0.925</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1536500</v>
+        <v>1873600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="H90" t="n">
-        <v>37.39</v>
+        <v>29.55</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>6.357</v>
+        <v>0.961</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>6.709</v>
+        <v>1.044</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,39 +4536,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>-0.009000000000000001</v>
+        <v>1.17</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1534900</v>
+        <v>1871100</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H91" t="n">
-        <v>53.75</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.42</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.083</v>
+        <v>1.222</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,39 +4581,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.82</v>
+        <v>0.235</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>0.0061</v>
+        <v>0.0444</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1455200</v>
+        <v>1802400</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.27</v>
+        <v>5.18</v>
       </c>
       <c r="H92" t="n">
-        <v>66.97</v>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
+        <v>73.31</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.798</v>
+        <v>0.226</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.774</v>
+        <v>0.225</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,39 +4626,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.07</v>
+        <v>1.43</v>
       </c>
       <c r="E93" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1408600</v>
+        <v>1785400</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>7.64</v>
+        <v>0.15</v>
       </c>
       <c r="H93" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.69</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.078</v>
+        <v>1.645</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>2.083</v>
+        <v>1.918</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,39 +4671,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.0366</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1400600</v>
+        <v>1761500</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="H94" t="n">
-        <v>42.57</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.911</v>
+        <v>0.797</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.853</v>
+        <v>0.774</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,39 +4716,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0.06519999999999999</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1400100</v>
+        <v>1741000</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.09</v>
+        <v>1.56</v>
       </c>
       <c r="H95" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I95" s="17" t="inlineStr">
+        <v>84.8</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>2.104</v>
+        <v>0.213</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>2.103</v>
+        <v>0.21</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,28 +4761,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.275</v>
+        <v>0.355</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>0.0185</v>
+        <v>0.0441</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1392800</v>
+        <v>1725000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="H96" t="n">
-        <v>45</v>
+        <v>52.77</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.287</v>
+        <v>0.353</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.283</v>
+        <v>0.328</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,39 +4806,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>4.48</v>
+        <v>0.975</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>0.0022</v>
+        <v>0.0052</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1387100</v>
+        <v>1690300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="H97" t="n">
-        <v>38.42</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.08</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>4.591</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>4.641</v>
+        <v>0.883</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,38 +4851,40 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>0.0263</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1383300</v>
+        <v>1669700</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="H98" t="n">
-        <v>69.33</v>
-      </c>
-      <c r="I98" s="17" t="inlineStr">
+        <v>48.49</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="K98" s="9" t="n"/>
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
     </row>
@@ -4894,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>2.72</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>-0.0216</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1344900</v>
+        <v>1648600</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="H99" t="n">
-        <v>25.69</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.27</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.495</v>
+        <v>2.626</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.653</v>
+        <v>2.451</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4939,39 +4941,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0.06519999999999999</v>
+        <v>1.11</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1315500</v>
+        <v>1629000</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.18</v>
+        <v>0.18</v>
       </c>
       <c r="H100" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="I100" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.46</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.213</v>
+        <v>1.084</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.21</v>
+        <v>1.05</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4984,28 +4986,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>6.77</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1312700</v>
+        <v>1602300</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H101" t="n">
-        <v>36.3</v>
+        <v>32.94</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5013,10 +5015,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.5</v>
+        <v>7.128</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.521</v>
+        <v>7.559</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5029,39 +5031,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>0.0248</v>
+        <v>0.0299</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1273400</v>
+        <v>1511200</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="H102" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.1</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.667</v>
+        <v>0.716</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5074,28 +5076,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0</v>
+        <v>0.84</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1268100</v>
+        <v>1479600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.74</v>
+        <v>0.21</v>
       </c>
       <c r="H103" t="n">
-        <v>36.07</v>
+        <v>41.09</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5103,10 +5105,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.251</v>
+        <v>0.91</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.272</v>
+        <v>0.852</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5119,40 +5121,38 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.765</v>
+        <v>0.39</v>
       </c>
       <c r="E104" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.0263</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1255900</v>
+        <v>1443400</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.95</v>
+        <v>0.26</v>
       </c>
       <c r="H104" t="n">
-        <v>60.12</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.33</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="K104" s="9" t="n">
-        <v>0.721</v>
-      </c>
+        <v>0.331</v>
+      </c>
+      <c r="K104" s="9" t="n"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
     </row>
@@ -5164,28 +5164,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>6.77</v>
+        <v>0.62</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>0.003</v>
+        <v>0.0248</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1235300</v>
+        <v>1425400</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="H105" t="n">
-        <v>32.94</v>
+        <v>39.89</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>7.128</v>
+        <v>0.667</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>7.559</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5209,39 +5209,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.43</v>
+        <v>2.09</v>
       </c>
       <c r="E106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1224300</v>
+        <v>1418500</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H106" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.56</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.645</v>
+        <v>2.104</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.918</v>
+        <v>2.103</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5254,39 +5254,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>-0.0167</v>
+        <v>2.07</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1218500</v>
+        <v>1409300</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.26</v>
+        <v>7.65</v>
       </c>
       <c r="H107" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.34</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.356</v>
+        <v>2.078</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.54</v>
+        <v>2.083</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5299,39 +5299,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.64</v>
+        <v>0.275</v>
       </c>
       <c r="E108" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.0185</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1216600</v>
+        <v>1408800</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.59</v>
+        <v>0.12</v>
       </c>
       <c r="H108" t="n">
-        <v>54.16</v>
-      </c>
-      <c r="I108" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.637</v>
+        <v>0.287</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.625</v>
+        <v>0.283</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5344,28 +5344,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
         <v>1.18</v>
       </c>
-      <c r="E109" s="16" t="n">
-        <v>-0.008399999999999999</v>
+      <c r="E109" s="17" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1207000</v>
+        <v>1383700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="H109" t="n">
-        <v>52.11</v>
+        <v>21.3</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.173</v>
+        <v>1.356</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.143</v>
+        <v>1.54</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5389,39 +5389,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E110" s="16" t="n">
-        <v>-0.0127</v>
+        <v>0.865</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1178400</v>
+        <v>1383500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="H110" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.48</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.247</v>
+        <v>0.865</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.184</v>
+        <v>0.86</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5434,28 +5434,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DESTINI</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.23</v>
+        <v>0.47</v>
       </c>
       <c r="E111" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1160300</v>
+        <v>1380700</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>4.56</v>
+        <v>0.16</v>
       </c>
       <c r="H111" t="n">
-        <v>48.6</v>
+        <v>36.3</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.229</v>
+        <v>0.5</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.243</v>
+        <v>0.521</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5479,39 +5479,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.545</v>
+        <v>0.64</v>
       </c>
       <c r="E112" s="15" t="n">
-        <v>0.0481</v>
+        <v>0.0159</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1145500</v>
+        <v>1311000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="H112" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.16</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.555</v>
+        <v>0.637</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.52</v>
+        <v>0.625</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5524,28 +5524,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>2.56</v>
+        <v>0.54</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>0.0039</v>
+        <v>0.0385</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1144300</v>
+        <v>1296300</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H113" t="n">
-        <v>46.18</v>
+        <v>48.35</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>2.599</v>
+        <v>0.555</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>2.61</v>
+        <v>0.52</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5569,28 +5569,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>-0.0058</v>
+        <v>0.765</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1103600</v>
+        <v>1278400</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.19</v>
+        <v>0.97</v>
       </c>
       <c r="H114" t="n">
-        <v>34.28</v>
+        <v>60.12</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.761</v>
+        <v>0.749</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1.874</v>
+        <v>0.721</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5614,39 +5614,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>0.0235</v>
+        <v>0.235</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1094800</v>
+        <v>1268100</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.19</v>
+        <v>0.74</v>
       </c>
       <c r="H115" t="n">
-        <v>56.85</v>
-      </c>
-      <c r="I115" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.07</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>6.228</v>
+        <v>0.251</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>5.949</v>
+        <v>0.272</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5659,28 +5659,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.915</v>
+        <v>0.66</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.0394</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1075800</v>
+        <v>1252300</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.61</v>
+        <v>1.8</v>
       </c>
       <c r="H116" t="n">
-        <v>51.28</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.914</v>
+        <v>0.623</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.883</v>
+        <v>0.609</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5704,25 +5704,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.11</v>
+        <v>2.56</v>
       </c>
       <c r="E117" s="15" t="n">
-        <v>0.0374</v>
+        <v>0.0039</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1074900</v>
+        <v>1250200</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="H117" t="n">
         <v>46.18</v>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>1.144</v>
+        <v>2.599</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>1.105</v>
+        <v>2.61</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5749,39 +5749,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>0.0145</v>
+        <v>2.34</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1057200</v>
+        <v>1246000</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="H118" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="I118" s="17" t="inlineStr">
+        <v>59.79</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.356</v>
+        <v>2.247</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.384</v>
+        <v>2.184</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5794,28 +5794,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E119" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>1.18</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1016600</v>
+        <v>1223300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H119" t="n">
-        <v>29.96</v>
+        <v>52.11</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5823,10 +5823,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.69</v>
+        <v>1.173</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.757</v>
+        <v>1.143</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5839,39 +5839,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>3.76</v>
+        <v>3.29</v>
       </c>
       <c r="E120" s="15" t="n">
-        <v>0.0301</v>
+        <v>0.0281</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>959800</v>
+        <v>1217300</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H120" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.33</v>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>3.824</v>
+        <v>3.344</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>3.711</v>
+        <v>3.583</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5884,39 +5884,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.97</v>
+        <v>6.56</v>
       </c>
       <c r="E121" s="15" t="n">
-        <v>0.0314</v>
+        <v>0.0282</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>952200</v>
+        <v>1183000</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="H121" t="n">
-        <v>44.65</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.27</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.082</v>
+        <v>6.231</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.993</v>
+        <v>5.95</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5929,28 +5929,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v>0.0109</v>
+        <v>1.7</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>946500</v>
+        <v>1167700</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H122" t="n">
-        <v>40.89</v>
+        <v>34.28</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.87</v>
+        <v>1.761</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>3.002</v>
+        <v>1.874</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5974,28 +5974,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>DESTINI</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E123" s="15" t="n">
-        <v>0.0224</v>
+        <v>0.23</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>945500</v>
+        <v>1160300</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.14</v>
+        <v>4.56</v>
       </c>
       <c r="H123" t="n">
-        <v>34.03</v>
+        <v>48.6</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.715</v>
+        <v>0.229</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.781</v>
+        <v>0.243</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6019,28 +6019,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>-0.0039</v>
+        <v>3.92</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>900700</v>
+        <v>1145100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.31</v>
+        <v>0.12</v>
       </c>
       <c r="H124" t="n">
-        <v>37.97</v>
+        <v>51.13</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>7.822</v>
+        <v>3.951</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>7.858</v>
+        <v>3.587</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6064,28 +6064,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>7.23</v>
+        <v>1.1</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>0.0388</v>
+        <v>0.028</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>897000</v>
+        <v>1137500</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="H125" t="n">
-        <v>50.18</v>
+        <v>44.65</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>7.306</v>
+        <v>1.143</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>6.915</v>
+        <v>1.105</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6109,28 +6109,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="16" t="n">
-        <v>-0.0196</v>
+        <v>7.68</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>876600</v>
+        <v>1091100</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.76</v>
+        <v>0.38</v>
       </c>
       <c r="H126" t="n">
-        <v>35.9</v>
+        <v>38.5</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.042</v>
+        <v>7.823</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.134</v>
+        <v>7.858</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6154,28 +6154,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>1.48</v>
+        <v>2.77</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>0.0137</v>
+        <v>0.0109</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>869600</v>
+        <v>1077200</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="H127" t="n">
-        <v>35.83</v>
+        <v>40.89</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>1.594</v>
+        <v>2.87</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.656</v>
+        <v>3.002</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6199,28 +6199,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.645</v>
+        <v>0.915</v>
       </c>
       <c r="E128" s="15" t="n">
-        <v>0.0488</v>
+        <v>0.0167</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>841600</v>
+        <v>1075800</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="H128" t="n">
-        <v>36.61</v>
+        <v>51.28</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.707</v>
+        <v>0.914</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.742</v>
+        <v>0.883</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6244,28 +6244,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="E129" s="15" t="n">
-        <v>0.0442</v>
+        <v>0.0123</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>830100</v>
+        <v>1075600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="H129" t="n">
-        <v>49.58</v>
+        <v>42.99</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.594</v>
+        <v>0.432</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.586</v>
+        <v>0.437</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6289,39 +6289,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>0.025</v>
+        <v>0.345</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>820300</v>
+        <v>1057400</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.14</v>
+        <v>0.68</v>
       </c>
       <c r="H130" t="n">
-        <v>40.38</v>
-      </c>
-      <c r="I130" s="17" t="inlineStr">
+        <v>40.21</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>3.343</v>
+        <v>0.356</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>3.582</v>
+        <v>0.383</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6334,28 +6334,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>0.0145</v>
+        <v>1.54</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>820100</v>
+        <v>1052300</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H131" t="n">
-        <v>51.91</v>
+        <v>28.25</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>2.794</v>
+        <v>1.689</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>2.677</v>
+        <v>1.756</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6379,39 +6379,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>0</v>
+        <v>7.51</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.004</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>788400</v>
+        <v>1043600</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.19</v>
+        <v>0.41</v>
       </c>
       <c r="H132" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.44</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.96</v>
+        <v>7.562</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.044</v>
+        <v>7.745</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6424,28 +6424,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>5.65</v>
+        <v>3.75</v>
       </c>
       <c r="E133" s="15" t="n">
-        <v>0.0018</v>
+        <v>0.0274</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>787600</v>
+        <v>1033300</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="H133" t="n">
-        <v>32.61</v>
+        <v>47.77</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>5.857</v>
+        <v>3.823</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>6.145</v>
+        <v>3.711</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6469,28 +6469,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>0</v>
+        <v>1.48</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>773200</v>
+        <v>1018900</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.08</v>
+        <v>0.55</v>
       </c>
       <c r="H134" t="n">
-        <v>50.42</v>
+        <v>35.83</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>3.949</v>
+        <v>1.594</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>3.587</v>
+        <v>1.656</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6514,28 +6514,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.835</v>
+        <v>7.23</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>0.0121</v>
+        <v>0.0388</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>766300</v>
+        <v>1017600</v>
       </c>
       <c r="G135" s="12" t="n">
         <v>0.23</v>
       </c>
       <c r="H135" t="n">
-        <v>33.02</v>
+        <v>50.18</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.883</v>
+        <v>7.306</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.945</v>
+        <v>6.915</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6559,28 +6559,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>10.58</v>
+        <v>1.97</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>0.0272</v>
+        <v>0.0314</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>756200</v>
+        <v>1017400</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="H136" t="n">
-        <v>55.88</v>
+        <v>44.65</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>10.421</v>
+        <v>2.082</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>9.805</v>
+        <v>1.993</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6604,39 +6604,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>2.14</v>
+        <v>0.835</v>
       </c>
       <c r="E137" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0121</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>754200</v>
+        <v>985300</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="H137" t="n">
-        <v>55.85</v>
-      </c>
-      <c r="I137" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.02</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>2.113</v>
+        <v>0.883</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>2.07</v>
+        <v>0.945</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6649,28 +6649,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>0</v>
+        <v>2.81</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0.0181</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>747400</v>
+        <v>947800</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="H138" t="n">
-        <v>33</v>
+        <v>52.45</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.839</v>
+        <v>2.795</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.859</v>
+        <v>2.677</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6694,39 +6694,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E139" s="15" t="n">
-        <v>0.0027</v>
+        <v>6.73</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>724100</v>
+        <v>932500</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H139" t="n">
-        <v>45.97</v>
-      </c>
-      <c r="I139" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.72</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>7.561</v>
+        <v>6.753</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>7.745</v>
+        <v>6.819</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6739,39 +6739,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0.0442</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>700000</v>
+        <v>921200</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="H140" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="I140" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.58</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.594</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.586</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6784,28 +6784,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.64</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>0.0407</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>683400</v>
+        <v>911800</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H141" t="n">
-        <v>28.87</v>
+        <v>35.5</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.219</v>
+        <v>0.707</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.306</v>
+        <v>0.742</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6829,28 +6829,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>0.0236</v>
+        <v>1</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>678500</v>
+        <v>909400</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="H142" t="n">
-        <v>62.98</v>
+        <v>35.9</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.622</v>
+        <v>1.042</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.609</v>
+        <v>1.134</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6874,39 +6874,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0360</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SAG</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E143" s="16" t="n">
-        <v>-0.0234</v>
+        <v>10.64</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>0.033</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>652200</v>
+        <v>894000</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>3.65</v>
+        <v>0.26</v>
       </c>
       <c r="H143" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="I143" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.81</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.637</v>
+        <v>10.426</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.644</v>
+        <v>9.805999999999999</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6928,19 +6928,19 @@
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0.0258</v>
+        <v>0.0206</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>646400</v>
+        <v>889200</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H144" t="n">
-        <v>46.41</v>
+        <v>45.65</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>1.034</v>
+        <v>1.033</v>
       </c>
       <c r="K144" s="9" t="n">
         <v>0.955</v>
@@ -6964,39 +6964,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E145" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>2.13</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>645100</v>
+        <v>859700</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.58</v>
+        <v>0.41</v>
       </c>
       <c r="H145" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I145" s="17" t="inlineStr">
+        <v>54.56</v>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.633</v>
+        <v>2.113</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.631</v>
+        <v>2.07</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7009,39 +7009,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.71</v>
+        <v>0.655</v>
       </c>
       <c r="E146" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>630000</v>
+        <v>853600</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="H146" t="n">
-        <v>42.09</v>
-      </c>
-      <c r="I146" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.76</v>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.727</v>
+        <v>0.648</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.743</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7054,39 +7054,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.66</v>
+        <v>0.795</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>0.0076</v>
+        <v>0.0258</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>623300</v>
+        <v>824200</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="H147" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="I147" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.98</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.648</v>
+        <v>0.911</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.063</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7099,28 +7099,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E148" s="15" t="n">
-        <v>0.0194</v>
+        <v>1.14</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>609200</v>
+        <v>815100</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="H148" t="n">
-        <v>19.55</v>
+        <v>28.87</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.91</v>
+        <v>1.219</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>1.063</v>
+        <v>1.306</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7159,15 +7159,15 @@
         <v>0.0388</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>606800</v>
+        <v>750900</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="H149" t="n">
         <v>48.23</v>
       </c>
-      <c r="I149" s="17" t="inlineStr">
+      <c r="I149" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7189,28 +7189,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>6.75</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E150" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>605500</v>
+        <v>747400</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.14</v>
+        <v>0.42</v>
       </c>
       <c r="H150" t="n">
-        <v>49.35</v>
+        <v>33</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>6.755</v>
+        <v>0.839</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>6.82</v>
+        <v>0.859</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7243,27 +7243,27 @@
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>-0.0156</v>
+        <v>4.41</v>
+      </c>
+      <c r="E151" s="17" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>603600</v>
+        <v>707100</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H151" t="n">
-        <v>51.29</v>
-      </c>
-      <c r="I151" s="17" t="inlineStr">
+        <v>50.9</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>4.374</v>
+        <v>4.373</v>
       </c>
       <c r="K151" s="9" t="n">
         <v>4.431</v>
@@ -7279,39 +7279,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0360</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SAG</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E152" s="15" t="n">
-        <v>0.0259</v>
+        <v>0.625</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>582500</v>
+        <v>652200</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.18</v>
+        <v>3.65</v>
       </c>
       <c r="H152" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.91</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>1.228</v>
+        <v>0.637</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>1.085</v>
+        <v>0.644</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7324,28 +7324,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="E153" s="15" t="n">
-        <v>0.0238</v>
+        <v>0.0345</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>569600</v>
+        <v>648000</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H153" t="n">
-        <v>54.64</v>
+        <v>49.82</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>1.264</v>
+        <v>1.229</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.178</v>
+        <v>1.085</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7369,39 +7369,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E154" s="15" t="n">
-        <v>0.0208</v>
+        <v>0.635</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>543600</v>
+        <v>645100</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.09</v>
+        <v>0.58</v>
       </c>
       <c r="H154" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="I154" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.02</v>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.74</v>
+        <v>0.633</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.631</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7414,28 +7414,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E155" s="15" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>534500</v>
+        <v>636900</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.43</v>
+        <v>0.26</v>
       </c>
       <c r="H155" t="n">
-        <v>41.69</v>
+        <v>54.64</v>
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>2.11</v>
+        <v>1.264</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>2.265</v>
+        <v>1.178</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7459,28 +7459,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>3.1</v>
+        <v>0.71</v>
       </c>
       <c r="E156" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>506500</v>
+        <v>630000</v>
       </c>
       <c r="G156" s="12" t="n">
         <v>0.33</v>
       </c>
       <c r="H156" t="n">
-        <v>49.07</v>
+        <v>42.09</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>3.16</v>
+        <v>0.727</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>2.911</v>
+        <v>0.743</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7513,19 +7513,19 @@
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>0</v>
+        <v>4.2</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>502900</v>
+        <v>599700</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H157" t="n">
-        <v>35.35</v>
+        <v>34.48</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7533,16 +7533,511 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>4.373</v>
+        <v>4.371</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>4.681</v>
+        <v>4.68</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="E158" s="15" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>595100</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H158" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>8.587</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>8.679</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>584400</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H159" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>551900</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H160" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>545800</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H161" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>1.359</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>534700</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H162" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>529400</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H163" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>13.023</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>13.371</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>529000</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H164" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="I164" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>7.954</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="E165" s="15" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>525900</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H165" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>5.443</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>5.778</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>525700</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H166" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>3.161</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>2.911</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>520000</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H167" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>517000</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H168" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M157"/>
+  <autoFilter ref="A1:M168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.42</v>
+        <v>0.425</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.012</v>
+        <v>0.0241</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>6478000</v>
+        <v>6791400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>58.95</v>
+        <v>60.15</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.38</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 58.95未超买，现价高于50日均线约10.5%，技术面信号较为可靠。</t>
+          <t>SAR转多，RSI 60.15未超买，现价高于50日均线约11.8%，技术面信号偏可靠。</t>
         </is>
       </c>
     </row>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.235</v>
+        <v>0.23</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>58222600</v>
+        <v>59970300</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -646,28 +646,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0.1429</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32068300</v>
+        <v>33937400</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>2.36</v>
+        <v>0.55</v>
       </c>
       <c r="H4" t="n">
-        <v>31.27</v>
+        <v>52.3</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.154</v>
+        <v>0.157</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.184</v>
+        <v>0.142</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -706,10 +706,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>30693800</v>
+        <v>33925900</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H5" t="n">
         <v>24.46</v>
@@ -736,28 +736,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.1429</v>
+        <v>0.145</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>30524300</v>
+        <v>32396100</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.5</v>
+        <v>2.39</v>
       </c>
       <c r="H6" t="n">
-        <v>52.3</v>
+        <v>31.27</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.157</v>
+        <v>0.154</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.142</v>
+        <v>0.184</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -781,28 +781,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.011</v>
+        <v>0.47</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>27325100</v>
+        <v>32162900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.38</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>67.59999999999999</v>
+        <v>81.92</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.843</v>
+        <v>0.4</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.748</v>
+        <v>0.294</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.195</v>
+        <v>0.19</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>-0.025</v>
+        <v>-0.05</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>26021700</v>
+        <v>30140100</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="H8" t="n">
-        <v>35.85</v>
+        <v>33.93</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -871,39 +871,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.35</v>
+        <v>0.915</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>24556400</v>
+        <v>28505100</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="H9" t="n">
-        <v>68.58</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.05</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.311</v>
+        <v>0.843</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.261</v>
+        <v>0.748</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -916,28 +916,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>-0.0278</v>
+        <v>0.35</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.06059999999999999</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>19439200</v>
+        <v>26479500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.91</v>
+        <v>0.32</v>
       </c>
       <c r="H10" t="n">
-        <v>41.19</v>
+        <v>68.58</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.187</v>
+        <v>0.311</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.186</v>
+        <v>0.261</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,39 +961,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.2</v>
+        <v>0.175</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>19319200</v>
+        <v>19526600</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>3.65</v>
+        <v>0.91</v>
       </c>
       <c r="H11" t="n">
-        <v>64.81</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.19</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.048</v>
+        <v>0.187</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.047</v>
+        <v>0.186</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.0106</v>
+        <v>0.06</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.2</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>18671600</v>
+        <v>19522200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.54</v>
+        <v>3.68</v>
       </c>
       <c r="H12" t="n">
-        <v>79.34</v>
+        <v>64.81</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.4</v>
+        <v>0.048</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.294</v>
+        <v>0.047</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,28 +1051,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.0142</v>
+        <v>0.155</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13713300</v>
+        <v>18815900</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="H13" t="n">
-        <v>81.19</v>
+        <v>48.42</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.635</v>
+        <v>0.155</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.543</v>
+        <v>0.156</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,28 +1096,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>-0.0313</v>
+        <v>0.71</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13294000</v>
+        <v>14183300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>48.42</v>
+        <v>80.62</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.155</v>
+        <v>0.634</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.156</v>
+        <v>0.543</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.0157</v>
+        <v>0.305</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>11684500</v>
+        <v>13243300</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.83</v>
+        <v>0.68</v>
       </c>
       <c r="H15" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.41</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.213</v>
+        <v>0.308</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.197</v>
+        <v>0.301</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11466800</v>
+        <v>12589400</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="H16" t="n">
         <v>55.6</v>
@@ -1231,39 +1231,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.027</v>
+        <v>0.77</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>11090500</v>
+        <v>12160300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.54</v>
+        <v>0.79</v>
       </c>
       <c r="H17" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.5</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.571</v>
+        <v>0.774</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.544</v>
+        <v>0.776</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,28 +1276,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>10333500</v>
+        <v>11985200</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.67</v>
+        <v>1.88</v>
       </c>
       <c r="H18" t="n">
-        <v>46.5</v>
+        <v>62.98</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.774</v>
+        <v>1.213</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.776</v>
+        <v>1.197</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1321,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.036</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>9755300</v>
+        <v>11883300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="H19" t="n">
-        <v>47.41</v>
+        <v>52.07</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.308</v>
+        <v>0.572</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.301</v>
+        <v>0.544</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,28 +1366,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>-0.0667</v>
+        <v>0.865</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>9384500</v>
+        <v>10562700</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>9.210000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="H20" t="n">
-        <v>51.64</v>
+        <v>46.09</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.868</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.869</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1411,39 +1411,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.0112</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>-0.0667</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8988900</v>
+        <v>9384500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.43</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>59.14</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.64</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.427</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.375</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,33 +1456,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>9126900</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="E22" s="15" t="n">
-        <v>0.0204</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>8364800</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>0.37</v>
+      <c r="H22" t="n">
+        <v>39.67</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="J22" s="9" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.48</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1494,39 +1501,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.865</v>
+        <v>0.445</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8083400</v>
+        <v>9113700</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="H23" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.07</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.868</v>
+        <v>0.427</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.869</v>
+        <v>0.375</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,40 +1546,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.0361</v>
+        <v>0.0204</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>8083000</v>
+        <v>8373900</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H24" t="n">
-        <v>37.98</v>
+        <v>0.37</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J24" s="9" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>0.48</v>
-      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1629,28 +1629,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2.41</v>
+        <v>0.575</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>0.0524</v>
+        <v>0.0849</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6879900</v>
+        <v>7433900</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="H26" t="n">
-        <v>34.19</v>
+        <v>40.99</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.726</v>
+        <v>0.63</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.868</v>
+        <v>0.619</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1674,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.575</v>
+        <v>2.08</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>0.0849</v>
+        <v>0.0505</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6693100</v>
+        <v>7285700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.72</v>
+        <v>0.26</v>
       </c>
       <c r="H27" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.8</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.63</v>
+        <v>1.95</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.619</v>
+        <v>1.766</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,28 +1719,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.115</v>
+        <v>2.41</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.0524</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6563700</v>
+        <v>7152400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.34</v>
+        <v>1.39</v>
       </c>
       <c r="H28" t="n">
-        <v>34.73</v>
+        <v>34.19</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.138</v>
+        <v>2.726</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.148</v>
+        <v>2.868</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,39 +1764,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.0968</v>
+        <v>0.385</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6526600</v>
+        <v>7141800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>2.8</v>
+        <v>0.72</v>
       </c>
       <c r="H29" t="n">
-        <v>79.20999999999999</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.46</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.43</v>
+        <v>0.395</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.435</v>
+        <v>0.406</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1824,10 +1824,10 @@
         <v>-0.0042</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6518500</v>
+        <v>6951200</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H30" t="n">
         <v>46.91</v>
@@ -1854,28 +1854,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>-0.0014</v>
+        <v>0.115</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6059000</v>
+        <v>6903800</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="H31" t="n">
-        <v>32.57</v>
+        <v>34.73</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>7.439</v>
+        <v>0.138</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>7.659</v>
+        <v>0.148</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.93</v>
+        <v>0.505</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>0.0164</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6027100</v>
+        <v>6766000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.44</v>
+        <v>2.91</v>
       </c>
       <c r="H32" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.48</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.856</v>
+        <v>0.429</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.599</v>
+        <v>0.434</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,28 +1944,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0</v>
+        <v>7.14</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6003200</v>
+        <v>6508900</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="H33" t="n">
-        <v>28.46</v>
+        <v>32.57</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.229</v>
+        <v>7.439</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.279</v>
+        <v>7.659</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,39 +1989,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AIZO</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.04</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.3333</v>
+        <v>0.0219</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5933000</v>
+        <v>6115800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>3.91</v>
+        <v>1.46</v>
       </c>
       <c r="H34" t="n">
-        <v>64.33</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.76</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.034</v>
+        <v>0.856</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.036</v>
+        <v>0.599</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.0566</v>
+        <v>0.205</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5773800</v>
+        <v>6085300</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.86</v>
+        <v>0.46</v>
       </c>
       <c r="H35" t="n">
-        <v>37.59</v>
+        <v>28.46</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.307</v>
+        <v>0.229</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.331</v>
+        <v>0.279</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,28 +2079,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>AIZO</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>2.06</v>
+        <v>0.04</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>0.0404</v>
+        <v>0.3333</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5446100</v>
+        <v>5933000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.19</v>
+        <v>3.91</v>
       </c>
       <c r="H36" t="n">
-        <v>59.89</v>
+        <v>64.33</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.949</v>
+        <v>0.034</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.766</v>
+        <v>0.036</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,28 +2124,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>7.31</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.0014</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5359900</v>
+        <v>5910500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="H37" t="n">
-        <v>58.13</v>
+        <v>38.43</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.62</v>
+        <v>7.427</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.616</v>
+        <v>7.893</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.12</v>
+        <v>0.275</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0377</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5288200</v>
+        <v>5778800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.21</v>
+        <v>0.86</v>
       </c>
       <c r="H38" t="n">
-        <v>66.59</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.22</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.101</v>
+        <v>0.307</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.091</v>
+        <v>0.331</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,40 +2214,36 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4984800</v>
+        <v>5760800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H39" t="n">
-        <v>38.25</v>
+        <v>87.13</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J39" s="9" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>0.28</v>
-      </c>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
     </row>
@@ -2259,28 +2255,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
+        <v>2.57</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4953800</v>
+        <v>5598300</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="H40" t="n">
-        <v>48.63</v>
+        <v>46.99</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2288,10 +2284,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.174</v>
+        <v>2.629</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.181</v>
+        <v>2.56</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,36 +2300,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.22</v>
+        <v>0.115</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.0732</v>
+        <v>0.0455</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4889700</v>
+        <v>5568200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.51</v>
+        <v>1.27</v>
       </c>
       <c r="H41" t="n">
-        <v>87.48999999999999</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
+        <v>64.04000000000001</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.091</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
     </row>
@@ -2345,28 +2345,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>0.0075</v>
+        <v>2.43</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4876800</v>
+        <v>5546500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.37</v>
+        <v>0.48</v>
       </c>
       <c r="H42" t="n">
-        <v>44.1</v>
+        <v>49.05</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>5.474</v>
+        <v>2.446</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>5.484</v>
+        <v>2.399</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2390,39 +2390,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.63</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4486500</v>
+        <v>5405900</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H43" t="n">
-        <v>46.99</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.629</v>
+        <v>0.62</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.56</v>
+        <v>0.616</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2435,28 +2435,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>-0.008100000000000001</v>
+        <v>5.32</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4462600</v>
+        <v>5348700</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="H44" t="n">
-        <v>50.35</v>
+        <v>43.19</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>2.447</v>
+        <v>5.472</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.399</v>
+        <v>5.483</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2480,28 +2480,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0049</v>
+        <v>0.265</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4421600</v>
+        <v>5034000</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.35</v>
+        <v>0.5</v>
       </c>
       <c r="H45" t="n">
-        <v>44.19</v>
+        <v>38.25</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>2.041</v>
+        <v>0.292</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>2.068</v>
+        <v>0.28</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2525,28 +2525,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.39</v>
+        <v>4.44</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>-0.025</v>
+        <v>-0.0067</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4408200</v>
+        <v>5000000</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.42</v>
+        <v>0.61</v>
       </c>
       <c r="H46" t="n">
-        <v>27.8</v>
+        <v>35.49</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.499</v>
+        <v>4.587</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.601</v>
+        <v>4.64</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2570,39 +2570,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2.05</v>
+        <v>0.125</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.0149</v>
+        <v>0.0417</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4345000</v>
+        <v>4971600</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.37</v>
+        <v>1.37</v>
       </c>
       <c r="H47" t="n">
-        <v>37.82</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2.127</v>
+        <v>0.123</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2.235</v>
+        <v>0.124</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2615,39 +2615,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.0417</v>
+        <v>0.175</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4344600</v>
+        <v>4963800</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="H48" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.123</v>
+        <v>0.174</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.124</v>
+        <v>0.181</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2660,28 +2660,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>-0.0375</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4230100</v>
+        <v>4945200</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.71</v>
+        <v>0.48</v>
       </c>
       <c r="H49" t="n">
-        <v>58.6</v>
+        <v>27.37</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.574</v>
+        <v>0.498</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.477</v>
+        <v>0.601</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2705,28 +2705,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.445</v>
+        <v>0.945</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>0.0723</v>
+        <v>0.0053</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4180900</v>
+        <v>4919400</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H50" t="n">
-        <v>55.39</v>
+        <v>38.86</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.426</v>
+        <v>1.03</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.417</v>
+        <v>0.968</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2750,28 +2750,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4155800</v>
+        <v>4703000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="H51" t="n">
-        <v>25.69</v>
+        <v>36.35</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.495</v>
+        <v>2.126</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.653</v>
+        <v>2.235</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2810,10 +2810,10 @@
         <v>-0.08699999999999999</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4112200</v>
+        <v>4636100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2842,19 +2842,19 @@
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.385</v>
+        <v>0.38</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.0267</v>
+        <v>0.0133</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4040100</v>
+        <v>4606100</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H53" t="n">
-        <v>64.98</v>
+        <v>60.97</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0.37</v>
@@ -2878,39 +2878,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0.008</v>
+        <v>2.02</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3984500</v>
+        <v>4504700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="H54" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.19</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.619</v>
+        <v>2.041</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.608</v>
+        <v>2.068</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2923,39 +2923,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0602</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3975200</v>
+        <v>4345000</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="H55" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.38</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>7.426</v>
+        <v>0.425</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>7.893</v>
+        <v>0.417</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2968,28 +2968,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.295</v>
+        <v>0.44</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3855100</v>
+        <v>4313300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1.15</v>
+        <v>0.22</v>
       </c>
       <c r="H56" t="n">
-        <v>49.15</v>
+        <v>25.69</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.295</v>
+        <v>0.495</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.295</v>
+        <v>0.653</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3013,28 +3013,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.675</v>
+        <v>0.61</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3835900</v>
+        <v>4242300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.26</v>
+        <v>0.72</v>
       </c>
       <c r="H57" t="n">
-        <v>41.05</v>
+        <v>58.07</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.733</v>
+        <v>0.573</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.722</v>
+        <v>0.476</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3058,39 +3058,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>2.68</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3735500</v>
+        <v>4077100</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H58" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.61</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.175</v>
+        <v>2.746</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.195</v>
+        <v>2.743</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3103,28 +3103,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.0184</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3708000</v>
+        <v>4031800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>1.05</v>
+        <v>0.27</v>
       </c>
       <c r="H59" t="n">
-        <v>52.36</v>
+        <v>41.88</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.826</v>
+        <v>0.733</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.789</v>
+        <v>0.722</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3148,39 +3148,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.79</v>
+        <v>0.835</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>0.026</v>
+        <v>0.0245</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3669900</v>
+        <v>4023600</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="H60" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.18</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.744</v>
+        <v>0.826</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.707</v>
+        <v>0.789</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3193,39 +3193,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3568600</v>
+        <v>3984500</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.35</v>
+        <v>1.17</v>
       </c>
       <c r="H61" t="n">
-        <v>42.02</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.14</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.508</v>
+        <v>0.619</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.465</v>
+        <v>0.608</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3238,39 +3238,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0.0075</v>
+        <v>0.165</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3553700</v>
+        <v>3884500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.29</v>
+        <v>0.7</v>
       </c>
       <c r="H62" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>2.746</v>
+        <v>0.175</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>2.743</v>
+        <v>0.195</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0126</v>
+        <v>0.0147</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3456500</v>
+        <v>3872700</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H63" t="n">
-        <v>47.25</v>
+        <v>47.8</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>4.881</v>
+        <v>4.882</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>4.742</v>
@@ -3328,28 +3328,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.125</v>
+        <v>0.295</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3313200</v>
+        <v>3855100</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>2.21</v>
+        <v>1.15</v>
       </c>
       <c r="H64" t="n">
-        <v>41.39</v>
+        <v>49.15</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.129</v>
+        <v>0.295</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.13</v>
+        <v>0.295</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3373,39 +3373,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.765</v>
+        <v>0.79</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.026</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3222600</v>
+        <v>3779600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.4</v>
+        <v>1.43</v>
       </c>
       <c r="H65" t="n">
-        <v>48.57</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.75</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.769</v>
+        <v>0.744</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.771</v>
+        <v>0.707</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3418,39 +3418,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.96</v>
+        <v>0.465</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0.0051</v>
+        <v>0.022</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3078500</v>
+        <v>3715000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="H66" t="n">
-        <v>54.29</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.04</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.927</v>
+        <v>0.508</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.951</v>
+        <v>0.465</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3463,28 +3463,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>6.21</v>
+        <v>0.755</v>
       </c>
       <c r="E67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2922200</v>
+        <v>3711300</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H67" t="n">
-        <v>37.8</v>
+        <v>45.85</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>6.358</v>
+        <v>0.768</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>6.709</v>
+        <v>0.771</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3508,39 +3508,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>5.1</v>
+        <v>0.13</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.04</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2726400</v>
+        <v>3591500</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.67</v>
+        <v>26.87</v>
       </c>
       <c r="H68" t="n">
-        <v>53.39</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.8</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>5.053</v>
+        <v>0.127</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>5.049</v>
+        <v>0.129</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3553,28 +3553,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.24</v>
+        <v>5.67</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>0.0164</v>
+        <v>0.0053</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2715300</v>
+        <v>3508200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="H69" t="n">
-        <v>41.31</v>
+        <v>34.2</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.286</v>
+        <v>5.859</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.315</v>
+        <v>6.145</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3598,28 +3598,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>0.002</v>
+        <v>1.95</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2710800</v>
+        <v>3482000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.21</v>
+        <v>0.58</v>
       </c>
       <c r="H70" t="n">
-        <v>46.34</v>
+        <v>52.97</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>9.994</v>
+        <v>1.926</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>10.129</v>
+        <v>1.951</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3643,28 +3643,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.255</v>
+        <v>0.125</v>
       </c>
       <c r="E71" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2648900</v>
+        <v>3313200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.33</v>
+        <v>2.21</v>
       </c>
       <c r="H71" t="n">
-        <v>27.73</v>
+        <v>41.39</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.272</v>
+        <v>0.129</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.298</v>
+        <v>0.13</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3688,28 +3688,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0.0035</v>
+        <v>6.2</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2633800</v>
+        <v>3252600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="H72" t="n">
-        <v>33.42</v>
+        <v>37.39</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>5.858</v>
+        <v>6.357</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>6.145</v>
+        <v>6.709</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3733,39 +3733,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.97</v>
+        <v>0.975</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>0.0319</v>
+        <v>0.0052</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2577000</v>
+        <v>3195300</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.3</v>
+        <v>0.53</v>
       </c>
       <c r="H73" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.08</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.032</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.969</v>
+        <v>0.883</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>-0.0103</v>
+        <v>0.185</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2556900</v>
+        <v>3188300</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="H74" t="n">
-        <v>58.51</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.31999999999999</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>3.692</v>
+        <v>0.165</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>3.104</v>
+        <v>0.166</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3823,28 +3823,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.455</v>
+        <v>5.1</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>0.0111</v>
+        <v>0.0303</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2405000</v>
+        <v>3059000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.32</v>
+        <v>0.75</v>
       </c>
       <c r="H75" t="n">
-        <v>30.55</v>
+        <v>53.39</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.489</v>
+        <v>5.053</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.548</v>
+        <v>5.049</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3868,39 +3868,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.865</v>
+        <v>9.98</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.04219999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2340500</v>
+        <v>3029700</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.73</v>
+        <v>0.24</v>
       </c>
       <c r="H76" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.904</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.967</v>
+        <v>10.129</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3913,28 +3913,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.335</v>
+        <v>0.275</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>0.0308</v>
+        <v>0.0377</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2266300</v>
+        <v>3024500</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="H77" t="n">
-        <v>47.84</v>
+        <v>25.26</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.343</v>
+        <v>0.321</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.335</v>
+        <v>0.366</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3958,33 +3958,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2208900</v>
+        <v>3018600</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.04</v>
+        <v>0.35</v>
+      </c>
+      <c r="H78" t="n">
+        <v>43.04</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J78" s="9" t="n"/>
-      <c r="K78" s="9" t="n"/>
+      <c r="J78" s="9" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>1.315</v>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
     </row>
@@ -3996,28 +4003,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.0551</v>
+        <v>0.255</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2205700</v>
+        <v>2971700</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="H79" t="n">
-        <v>41.18</v>
+        <v>27.73</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4025,10 +4032,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.741</v>
+        <v>0.272</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.298</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4041,28 +4048,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>-0.0097</v>
+        <v>0.86</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2179800</v>
+        <v>2820900</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="H80" t="n">
-        <v>31.45</v>
+        <v>30.74</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4070,10 +4077,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.537</v>
+        <v>0.903</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.967</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4086,40 +4093,33 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.0385</v>
+        <v>0.765</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2173100</v>
+        <v>2731300</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H81" t="n">
-        <v>54.26</v>
+        <v>0.05</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J81" s="9" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="K81" s="9" t="n">
-        <v>0.363</v>
-      </c>
+      <c r="J81" s="9" t="n"/>
+      <c r="K81" s="9" t="n"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
     </row>
@@ -4131,28 +4131,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.255</v>
+        <v>0.455</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.02</v>
+        <v>0.0111</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2147700</v>
+        <v>2730300</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="H82" t="n">
-        <v>41.5</v>
+        <v>30.55</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.27</v>
+        <v>0.489</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.29</v>
+        <v>0.548</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,28 +4176,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>3.34</v>
+        <v>0.585</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>0.0245</v>
+        <v>0.0174</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2146100</v>
+        <v>2727800</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H83" t="n">
-        <v>87.79000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>2.916</v>
+        <v>0.523</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>2.485</v>
+        <v>0.475</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4221,28 +4221,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>0.0492</v>
+        <v>3.84</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2028500</v>
+        <v>2686200</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
       <c r="H84" t="n">
-        <v>50.75</v>
+        <v>58.16</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>1.281</v>
+        <v>3.691</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.231</v>
+        <v>3.104</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4266,28 +4266,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2023200</v>
+        <v>2584700</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.26</v>
+        <v>1.27</v>
       </c>
       <c r="H85" t="n">
-        <v>50.4</v>
+        <v>51.76</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.626</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.686</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,39 +4311,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>0.0089</v>
+        <v>1.64</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2002900</v>
+        <v>2499000</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="H86" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.4</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.068</v>
+        <v>1.626</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.686</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,28 +4356,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.275</v>
+        <v>0.36</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>0.0377</v>
+        <v>0.0588</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1956400</v>
+        <v>2474700</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>0.32</v>
       </c>
       <c r="H87" t="n">
-        <v>25.26</v>
+        <v>54.66</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.321</v>
+        <v>0.353</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.366</v>
+        <v>0.329</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4401,28 +4401,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>-0.0022</v>
+        <v>0.255</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0.02</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1886000</v>
+        <v>2473800</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H88" t="n">
-        <v>36.71</v>
+        <v>41.5</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>4.589</v>
+        <v>0.27</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>4.64</v>
+        <v>0.29</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,39 +4446,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.585</v>
+        <v>1.29</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.0174</v>
+        <v>0.0574</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1882900</v>
+        <v>2467500</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="H89" t="n">
-        <v>65.97</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.48</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.523</v>
+        <v>1.282</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.475</v>
+        <v>1.231</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,39 +4491,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.925</v>
+        <v>0.82</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.0061</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1873600</v>
+        <v>2424400</v>
       </c>
       <c r="G90" s="12" t="n">
         <v>0.45</v>
       </c>
       <c r="H90" t="n">
-        <v>29.55</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.97</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.961</v>
+        <v>0.798</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>1.044</v>
+        <v>0.774</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,39 +4536,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1871100</v>
+        <v>2402600</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0.24</v>
       </c>
       <c r="H91" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.84</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.222</v>
+        <v>0.343</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.31</v>
+        <v>0.335</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,39 +4581,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.235</v>
+        <v>0.41</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>0.0444</v>
+        <v>0.0513</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1802400</v>
+        <v>2362000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>5.18</v>
+        <v>0.4</v>
       </c>
       <c r="H92" t="n">
-        <v>73.31</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.11</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.226</v>
+        <v>0.393</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.225</v>
+        <v>0.363</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,28 +4626,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
+        <v>0.51</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1785400</v>
+        <v>2340600</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.15</v>
+        <v>0.86</v>
       </c>
       <c r="H93" t="n">
-        <v>21.69</v>
+        <v>31.45</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.645</v>
+        <v>0.537</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.918</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,39 +4671,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0</v>
+        <v>0.67</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.0551</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1761500</v>
+        <v>2251100</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="H94" t="n">
-        <v>65</v>
-      </c>
-      <c r="I94" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.18</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.797</v>
+        <v>0.741</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.774</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,39 +4716,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.245</v>
+        <v>1.15</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0268</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1741000</v>
+        <v>2188600</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.56</v>
+        <v>0.48</v>
       </c>
       <c r="H95" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.11</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.213</v>
+        <v>1.07</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.21</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,39 +4761,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.355</v>
+        <v>3.34</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>0.0441</v>
+        <v>0.0245</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1725000</v>
+        <v>2148900</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.22</v>
+        <v>0.67</v>
       </c>
       <c r="H96" t="n">
-        <v>52.77</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>87.79000000000001</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.353</v>
+        <v>2.916</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.328</v>
+        <v>2.485</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,28 +4806,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0.0052</v>
+        <v>1.17</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1690300</v>
+        <v>2140300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H97" t="n">
-        <v>67.08</v>
+        <v>36.42</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.222</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.883</v>
+        <v>1.31</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,28 +4851,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0</v>
+        <v>3.3</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0312</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1669700</v>
+        <v>2138200</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.82</v>
+        <v>0.35</v>
       </c>
       <c r="H98" t="n">
-        <v>48.49</v>
+        <v>42.25</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>3.345</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>3.583</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>-0.0216</v>
+        <v>0.915</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1648600</v>
+        <v>2047800</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>1.22</v>
+        <v>0.49</v>
       </c>
       <c r="H99" t="n">
-        <v>66.27</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.81</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>2.626</v>
+        <v>0.96</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2.451</v>
+        <v>1.044</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,28 +4941,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0</v>
+        <v>6.81</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1629000</v>
+        <v>1997800</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H100" t="n">
-        <v>55.46</v>
+        <v>34.75</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.084</v>
+        <v>7.131</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.05</v>
+        <v>7.56</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,39 +4986,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>6.77</v>
+        <v>0.245</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>0.003</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1602300</v>
+        <v>1963500</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.15</v>
+        <v>1.75</v>
       </c>
       <c r="H101" t="n">
-        <v>32.94</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.8</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>7.128</v>
+        <v>0.213</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>7.559</v>
+        <v>0.21</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,39 +5031,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>0.0299</v>
+        <v>1.43</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1511200</v>
+        <v>1905200</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H102" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.69</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.716</v>
+        <v>1.645</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.781</v>
+        <v>1.918</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,28 +5076,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>0.0244</v>
+        <v>1.1</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1479600</v>
+        <v>1900200</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H103" t="n">
-        <v>41.09</v>
+        <v>53.75</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.91</v>
+        <v>1.083</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.852</v>
+        <v>1.05</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,38 +5121,40 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.39</v>
+        <v>1.57</v>
       </c>
       <c r="E104" s="15" t="n">
-        <v>0.0263</v>
+        <v>0.0195</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1443400</v>
+        <v>1832100</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H104" t="n">
-        <v>69.33</v>
-      </c>
-      <c r="I104" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.14</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="K104" s="9" t="n"/>
+        <v>1.692</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>1.757</v>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
     </row>
@@ -5164,28 +5166,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>0.0248</v>
+        <v>7.68</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1425400</v>
+        <v>1809200</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.16</v>
+        <v>0.63</v>
       </c>
       <c r="H105" t="n">
-        <v>39.89</v>
+        <v>38.5</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5193,10 +5195,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.667</v>
+        <v>7.823</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>7.858</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5209,39 +5211,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1418500</v>
+        <v>1806500</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.09</v>
+        <v>0.39</v>
       </c>
       <c r="H106" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I106" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.84</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>2.104</v>
+        <v>1.357</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>2.103</v>
+        <v>1.54</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5254,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1409300</v>
+        <v>1802400</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>7.65</v>
+        <v>5.18</v>
       </c>
       <c r="H107" t="n">
-        <v>45.34</v>
+        <v>73.31</v>
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
@@ -5283,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.078</v>
+        <v>0.226</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.083</v>
+        <v>0.225</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5299,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0.0185</v>
+        <v>0.865</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1408800</v>
+        <v>1683500</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H108" t="n">
-        <v>45</v>
+        <v>51.48</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5328,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.287</v>
+        <v>0.865</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.283</v>
+        <v>0.86</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5344,39 +5346,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.18</v>
+        <v>2.73</v>
       </c>
       <c r="E109" s="17" t="n">
-        <v>-0.0167</v>
+        <v>-0.018</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1383700</v>
+        <v>1672500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.3</v>
+        <v>1.24</v>
       </c>
       <c r="H109" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.356</v>
+        <v>2.627</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.54</v>
+        <v>2.452</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5389,28 +5391,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0</v>
+        <v>3.96</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1383500</v>
+        <v>1643500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
       <c r="H110" t="n">
-        <v>51.48</v>
+        <v>52.48</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5418,10 +5420,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.865</v>
+        <v>3.955</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.86</v>
+        <v>3.588</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5434,39 +5436,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E111" s="10" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1380700</v>
+        <v>1626900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H111" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.1</v>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.5</v>
+        <v>0.716</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.521</v>
+        <v>0.781</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5479,39 +5481,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="E112" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.0248</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1311000</v>
+        <v>1606000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.63</v>
+        <v>0.18</v>
       </c>
       <c r="H112" t="n">
-        <v>54.16</v>
-      </c>
-      <c r="I112" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.89</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.637</v>
+        <v>0.667</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.625</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5524,28 +5526,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E113" s="15" t="n">
-        <v>0.0385</v>
+        <v>0.27</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1296300</v>
+        <v>1559500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="H113" t="n">
-        <v>48.35</v>
+        <v>42.76</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5553,10 +5555,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.555</v>
+        <v>0.287</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.52</v>
+        <v>0.283</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5569,28 +5571,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.765</v>
+        <v>0.84</v>
       </c>
       <c r="E114" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.0244</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1278400</v>
+        <v>1552600</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.97</v>
+        <v>0.22</v>
       </c>
       <c r="H114" t="n">
-        <v>60.12</v>
+        <v>41.09</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5598,10 +5600,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.749</v>
+        <v>0.91</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.721</v>
+        <v>0.852</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5614,39 +5616,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.235</v>
+        <v>2.09</v>
       </c>
       <c r="E115" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1268100</v>
+        <v>1525000</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.74</v>
+        <v>0.1</v>
       </c>
       <c r="H115" t="n">
-        <v>36.07</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.56</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.251</v>
+        <v>2.104</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.272</v>
+        <v>2.103</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5659,40 +5661,38 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.66</v>
+        <v>0.39</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>0.0394</v>
+        <v>0.0263</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1252300</v>
+        <v>1511100</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>1.8</v>
+        <v>0.27</v>
       </c>
       <c r="H116" t="n">
-        <v>65.76000000000001</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.33</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="K116" s="9" t="n">
-        <v>0.609</v>
-      </c>
+        <v>0.331</v>
+      </c>
+      <c r="K116" s="9" t="n"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
     </row>
@@ -5704,39 +5704,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>2.56</v>
+        <v>6.59</v>
       </c>
       <c r="E117" s="15" t="n">
-        <v>0.0039</v>
+        <v>0.0329</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1250200</v>
+        <v>1487200</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H117" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.67</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.599</v>
+        <v>6.234</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.61</v>
+        <v>5.951</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5749,39 +5749,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>-0.0127</v>
+        <v>0.545</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0.0481</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1246000</v>
+        <v>1456300</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="H118" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.45</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>2.247</v>
+        <v>0.555</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>2.184</v>
+        <v>0.52</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5794,28 +5794,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="E119" s="17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0058</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1223300</v>
+        <v>1431700</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="H119" t="n">
-        <v>52.11</v>
+        <v>34.28</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5823,10 +5823,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.173</v>
+        <v>1.761</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.143</v>
+        <v>1.874</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5839,39 +5839,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>0.0281</v>
+        <v>0.47</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1217300</v>
+        <v>1431100</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="H120" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.3</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>3.344</v>
+        <v>0.5</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>3.583</v>
+        <v>0.521</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5884,28 +5884,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>0.0282</v>
+        <v>2.06</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1183000</v>
+        <v>1412100</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.2</v>
+        <v>7.66</v>
       </c>
       <c r="H121" t="n">
-        <v>57.27</v>
+        <v>41.44</v>
       </c>
       <c r="I121" s="16" t="inlineStr">
         <is>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>6.231</v>
+        <v>2.078</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>5.95</v>
+        <v>2.083</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5929,39 +5929,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="E122" s="17" t="n">
-        <v>-0.0058</v>
+        <v>-0.0127</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1167700</v>
+        <v>1375400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H122" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.79</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.761</v>
+        <v>2.247</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.874</v>
+        <v>2.184</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5974,39 +5974,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DESTINI</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1160300</v>
+        <v>1320200</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>4.56</v>
+        <v>0.64</v>
       </c>
       <c r="H123" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.16</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.229</v>
+        <v>0.637</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.243</v>
+        <v>0.625</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6019,28 +6019,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>0.0051</v>
+        <v>0.235</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1145100</v>
+        <v>1317400</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.12</v>
+        <v>0.77</v>
       </c>
       <c r="H124" t="n">
-        <v>51.13</v>
+        <v>36.07</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>3.951</v>
+        <v>0.251</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>3.587</v>
+        <v>0.272</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6064,28 +6064,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.1</v>
+        <v>2.79</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>0.028</v>
+        <v>0.0109</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1137500</v>
+        <v>1313000</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="H125" t="n">
-        <v>44.65</v>
+        <v>51.36</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>1.143</v>
+        <v>2.793</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>1.105</v>
+        <v>2.677</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6109,28 +6109,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>-0.0026</v>
+        <v>2.56</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1091100</v>
+        <v>1306300</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="H126" t="n">
-        <v>38.5</v>
+        <v>46.18</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>7.823</v>
+        <v>2.599</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>7.858</v>
+        <v>2.61</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6154,28 +6154,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2.77</v>
+        <v>0.765</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.0132</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1077200</v>
+        <v>1297900</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.29</v>
+        <v>0.98</v>
       </c>
       <c r="H127" t="n">
-        <v>40.89</v>
+        <v>60.12</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>2.87</v>
+        <v>0.749</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>3.002</v>
+        <v>0.721</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6199,28 +6199,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0.0167</v>
+        <v>1.01</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1075800</v>
+        <v>1281200</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.61</v>
+        <v>1.11</v>
       </c>
       <c r="H128" t="n">
-        <v>51.28</v>
+        <v>37.58</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.914</v>
+        <v>1.043</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.883</v>
+        <v>1.134</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6244,28 +6244,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.41</v>
+        <v>0.655</v>
       </c>
       <c r="E129" s="15" t="n">
-        <v>0.0123</v>
+        <v>0.0315</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1075600</v>
+        <v>1268000</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.12</v>
+        <v>1.82</v>
       </c>
       <c r="H129" t="n">
-        <v>42.99</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.432</v>
+        <v>0.623</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.437</v>
+        <v>0.609</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6289,39 +6289,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0.028</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1057400</v>
+        <v>1266700</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
       <c r="H130" t="n">
-        <v>40.21</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.65</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.356</v>
+        <v>1.143</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.383</v>
+        <v>1.105</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6334,28 +6334,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.54</v>
+        <v>1.19</v>
       </c>
       <c r="E131" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1052300</v>
+        <v>1264500</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H131" t="n">
-        <v>28.25</v>
+        <v>53.66</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.689</v>
+        <v>1.173</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.756</v>
+        <v>1.143</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6379,39 +6379,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>7.51</v>
+        <v>0.84</v>
       </c>
       <c r="E132" s="15" t="n">
-        <v>0.004</v>
+        <v>0.0182</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1043600</v>
+        <v>1245100</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H132" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.76</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>7.562</v>
+        <v>0.884</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>7.745</v>
+        <v>0.945</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6424,39 +6424,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>3.75</v>
+        <v>7.51</v>
       </c>
       <c r="E133" s="15" t="n">
-        <v>0.0274</v>
+        <v>0.004</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1033300</v>
+        <v>1227400</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="H133" t="n">
-        <v>47.77</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.44</v>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>3.823</v>
+        <v>7.562</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>3.711</v>
+        <v>7.745</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6469,28 +6469,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="E134" s="15" t="n">
-        <v>0.0137</v>
+        <v>0.0262</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1018900</v>
+        <v>1196200</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="H134" t="n">
-        <v>35.83</v>
+        <v>44.06</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.594</v>
+        <v>2.081</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.656</v>
+        <v>1.993</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6514,39 +6514,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="E135" s="15" t="n">
-        <v>0.0388</v>
+        <v>7.91</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1017600</v>
+        <v>1186800</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="H135" t="n">
-        <v>50.18</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.59</v>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>7.306</v>
+        <v>7.91</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>6.915</v>
+        <v>7.954</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6559,28 +6559,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.97</v>
+        <v>0.41</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>0.0314</v>
+        <v>0.0123</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1017400</v>
+        <v>1164300</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.39</v>
+        <v>0.13</v>
       </c>
       <c r="H136" t="n">
-        <v>44.65</v>
+        <v>42.99</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>2.082</v>
+        <v>0.432</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.993</v>
+        <v>0.437</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6604,28 +6604,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>DESTINI</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E137" s="15" t="n">
-        <v>0.0121</v>
+        <v>0.22</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>985300</v>
+        <v>1160800</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.3</v>
+        <v>4.57</v>
       </c>
       <c r="H137" t="n">
-        <v>33.02</v>
+        <v>40.95</v>
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.883</v>
+        <v>0.228</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.945</v>
+        <v>0.243</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6649,28 +6649,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HOCKSOON</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>0.0181</v>
+        <v>0.22</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>-0.0638</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>947800</v>
+        <v>1155200</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.1</v>
+        <v>1.78</v>
       </c>
       <c r="H138" t="n">
-        <v>52.45</v>
+        <v>33.23</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>2.795</v>
+        <v>0.238</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>2.677</v>
+        <v>0.276</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6694,28 +6694,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>-0.003</v>
+        <v>3.75</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>932500</v>
+        <v>1154700</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.22</v>
+        <v>0.37</v>
       </c>
       <c r="H139" t="n">
-        <v>47.72</v>
+        <v>47.77</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>6.753</v>
+        <v>3.823</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>6.819</v>
+        <v>3.711</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6739,28 +6739,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.59</v>
+        <v>2.77</v>
       </c>
       <c r="E140" s="15" t="n">
-        <v>0.0442</v>
+        <v>0.0109</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>921200</v>
+        <v>1151700</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="H140" t="n">
-        <v>49.58</v>
+        <v>40.89</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.594</v>
+        <v>2.87</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.586</v>
+        <v>3.002</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6784,39 +6784,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E141" s="15" t="n">
-        <v>0.0407</v>
+        <v>4.42</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>911800</v>
+        <v>1138500</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="H141" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.29</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.707</v>
+        <v>4.374</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.742</v>
+        <v>4.431</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6829,28 +6829,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" s="17" t="n">
-        <v>-0.0196</v>
+        <v>10.62</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0.0311</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>909400</v>
+        <v>1137400</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.79</v>
+        <v>0.33</v>
       </c>
       <c r="H142" t="n">
-        <v>35.9</v>
+        <v>56.5</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>1.042</v>
+        <v>10.424</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1.134</v>
+        <v>9.805</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6874,28 +6874,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>0.033</v>
+        <v>6.74</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>-0.0015</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>894000</v>
+        <v>1134000</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H143" t="n">
-        <v>56.81</v>
+        <v>48.52</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>10.426</v>
+        <v>6.754</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>9.805999999999999</v>
+        <v>6.82</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6919,28 +6919,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.99</v>
+        <v>7.22</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0.0206</v>
+        <v>0.0374</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>889200</v>
+        <v>1129800</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H144" t="n">
-        <v>45.65</v>
+        <v>49.98</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>1.033</v>
+        <v>7.305</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.955</v>
+        <v>6.915</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6964,39 +6964,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E145" s="15" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.27</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>859700</v>
+        <v>1116200</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H145" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="I145" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.16</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>2.113</v>
+        <v>0.266</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>2.07</v>
+        <v>0.257</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7009,39 +7009,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0.0206</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>853600</v>
+        <v>1101800</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="H146" t="n">
-        <v>55.76</v>
-      </c>
-      <c r="I146" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.65</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.648</v>
+        <v>1.033</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.955</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7054,28 +7054,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.795</v>
+        <v>1.48</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>0.0258</v>
+        <v>0.0137</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>824200</v>
+        <v>1098300</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="H147" t="n">
-        <v>20.98</v>
+        <v>35.83</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.911</v>
+        <v>1.594</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.063</v>
+        <v>1.656</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7099,28 +7099,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E148" s="17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.915</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>815100</v>
+        <v>1075800</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.35</v>
+        <v>0.61</v>
       </c>
       <c r="H148" t="n">
-        <v>28.87</v>
+        <v>51.28</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>1.219</v>
+        <v>0.914</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>1.306</v>
+        <v>0.883</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7144,28 +7144,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E149" s="15" t="n">
-        <v>0.0388</v>
+        <v>0.345</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>750900</v>
+        <v>1057400</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="H149" t="n">
-        <v>48.23</v>
+        <v>40.21</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>1.084</v>
+        <v>0.356</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>1.096</v>
+        <v>0.383</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7189,39 +7189,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="E150" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>747400</v>
+        <v>975800</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="H150" t="n">
-        <v>33</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.76</v>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.839</v>
+        <v>0.648</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.859</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7234,39 +7234,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="E151" s="17" t="n">
-        <v>-0.0178</v>
+        <v>0.82</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>707100</v>
+        <v>972900</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.14</v>
+        <v>0.54</v>
       </c>
       <c r="H151" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I151" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.49</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>4.373</v>
+        <v>0.839</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>4.431</v>
+        <v>0.859</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7279,39 +7279,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0360</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SAG</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E152" s="17" t="n">
-        <v>-0.0234</v>
+        <v>0.64</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0.0407</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>652200</v>
+        <v>972000</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>3.65</v>
+        <v>0.29</v>
       </c>
       <c r="H152" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.5</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.637</v>
+        <v>0.707</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.644</v>
+        <v>0.742</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7324,28 +7324,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1.2</v>
+        <v>0.59</v>
       </c>
       <c r="E153" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.0442</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>648000</v>
+        <v>960600</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H153" t="n">
-        <v>49.82</v>
+        <v>49.58</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>1.229</v>
+        <v>0.594</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.085</v>
+        <v>0.586</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7369,39 +7369,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E154" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.795</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>0.0258</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>645100</v>
+        <v>899600</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.58</v>
+        <v>0.39</v>
       </c>
       <c r="H154" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I154" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.98</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.633</v>
+        <v>0.911</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.631</v>
+        <v>1.063</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7414,28 +7414,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E155" s="15" t="n">
-        <v>0.0238</v>
+        <v>1.02</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>636900</v>
+        <v>872200</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.26</v>
+        <v>0.64</v>
       </c>
       <c r="H155" t="n">
-        <v>54.64</v>
+        <v>32.98</v>
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.264</v>
+        <v>1.074</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.178</v>
+        <v>1.126</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7459,28 +7459,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.71</v>
+        <v>1.15</v>
       </c>
       <c r="E156" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>630000</v>
+        <v>867500</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="H156" t="n">
-        <v>42.09</v>
+        <v>30.05</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.727</v>
+        <v>1.22</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.743</v>
+        <v>1.306</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7504,39 +7504,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E157" s="17" t="n">
-        <v>-0.004699999999999999</v>
+        <v>2.13</v>
+      </c>
+      <c r="E157" s="15" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>599700</v>
+        <v>859700</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.14</v>
+        <v>0.41</v>
       </c>
       <c r="H157" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.56</v>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>4.371</v>
+        <v>2.113</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>4.68</v>
+        <v>2.07</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7549,28 +7549,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>8.41</v>
+        <v>5.4</v>
       </c>
       <c r="E158" s="15" t="n">
-        <v>0.0072</v>
+        <v>0.0286</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>595100</v>
+        <v>800900</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="H158" t="n">
-        <v>44.5</v>
+        <v>48.66</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>8.587</v>
+        <v>5.479</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>8.679</v>
+        <v>5.383</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7594,28 +7594,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E159" s="10" t="n">
-        <v>0</v>
+        <v>0.745</v>
+      </c>
+      <c r="E159" s="15" t="n">
+        <v>0.0347</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>584400</v>
+        <v>790100</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.43</v>
+        <v>0.13</v>
       </c>
       <c r="H159" t="n">
-        <v>32.98</v>
+        <v>52.81</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -7623,10 +7623,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.074</v>
+        <v>0.741</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.126</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7639,28 +7639,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.735</v>
+        <v>4.09</v>
       </c>
       <c r="E160" s="15" t="n">
-        <v>0.0208</v>
+        <v>0.0276</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>551900</v>
+        <v>789300</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.09</v>
+        <v>0.32</v>
       </c>
       <c r="H160" t="n">
-        <v>51.23</v>
+        <v>43.78</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.74</v>
+        <v>4.24</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>4.308</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7684,39 +7684,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>0</v>
+        <v>1.06</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.0291</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>545800</v>
+        <v>788800</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="H161" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="I161" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.11</v>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>1.359</v>
+        <v>1.083</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>1.341</v>
+        <v>1.096</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7729,28 +7729,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
+        <v>8.43</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>534700</v>
+        <v>729800</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="H162" t="n">
-        <v>41.69</v>
+        <v>45.08</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>2.11</v>
+        <v>8.589</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.265</v>
+        <v>8.68</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7774,39 +7774,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>0</v>
+        <v>4.21</v>
+      </c>
+      <c r="E163" s="17" t="n">
+        <v>-0.0024</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>529400</v>
+        <v>713400</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="H163" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="I163" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.91</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>13.023</v>
+        <v>4.372</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>13.371</v>
+        <v>4.68</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7819,39 +7819,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="E164" s="10" t="n">
-        <v>0</v>
+        <v>1.18</v>
+      </c>
+      <c r="E164" s="15" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>529000</v>
+        <v>702800</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="H164" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="I164" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>7.91</v>
+        <v>1.227</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>7.954</v>
+        <v>1.085</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7864,28 +7864,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>5.27</v>
+        <v>1.3</v>
       </c>
       <c r="E165" s="15" t="n">
-        <v>0.0135</v>
+        <v>0.0317</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>525900</v>
+        <v>699700</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="H165" t="n">
-        <v>36.13</v>
+        <v>55.45</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>5.443</v>
+        <v>1.265</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>5.778</v>
+        <v>1.179</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7909,39 +7909,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0360</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>SAG</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="E166" s="15" t="n">
-        <v>0.0032</v>
+        <v>0.625</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>525700</v>
+        <v>652200</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.34</v>
+        <v>3.65</v>
       </c>
       <c r="H166" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="I166" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.91</v>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>3.161</v>
+        <v>0.637</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>2.911</v>
+        <v>0.644</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7954,28 +7954,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>1.02</v>
+        <v>0.635</v>
       </c>
       <c r="E167" s="17" t="n">
-        <v>-0.0097</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>520000</v>
+        <v>645100</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="H167" t="n">
-        <v>57.62</v>
+        <v>55.02</v>
       </c>
       <c r="I167" s="16" t="inlineStr">
         <is>
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>1.008</v>
+        <v>0.633</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.986</v>
+        <v>0.631</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7999,28 +7999,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E168" s="15" t="n">
-        <v>0.0338</v>
+        <v>0.71</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>517000</v>
+        <v>639200</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H168" t="n">
-        <v>48.95</v>
+        <v>42.09</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8028,16 +8028,691 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.771</v>
+        <v>0.727</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.771</v>
+        <v>0.743</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E169" s="15" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>623600</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H169" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>5.442</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>5.778</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>620600</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H170" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>13.023</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>13.371</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E171" s="15" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>594000</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H171" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>3.163</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>2.911</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>7235</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SUPERLN</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E172" s="15" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>588300</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H172" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E173" s="17" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>577000</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H173" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>548800</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H174" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>1.359</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E175" s="15" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>538300</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H175" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E176" s="15" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>536100</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H176" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>528600</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H177" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>2.027</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>524400</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H178" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E179" s="17" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>522400</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H179" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="I179" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>520000</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H180" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="I180" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>513200</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H181" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>1.454</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E182" s="15" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>512500</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H182" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E183" s="15" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>510700</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H183" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>2.266</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M168"/>
+  <autoFilter ref="A1:M183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,9 +96,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M183"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.425</v>
+        <v>0.42</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0241</v>
+        <v>0.012</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>6791400</v>
+        <v>6797400</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>0.57</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>60.15</v>
+        <v>58.95</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.397</v>
+        <v>0.396</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.38</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，RSI 60.15未超买，现价高于50日均线约11.8%，技术面信号偏可靠。</t>
+          <t>SAR转多信号，现价0.42高于50日均线0.38，RSI 58.95处中性偏上区间，未超买，信号技术面尚属可靠。</t>
         </is>
       </c>
     </row>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.23</v>
+        <v>0.235</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>59970300</v>
+        <v>60388400</v>
       </c>
       <c r="G3" s="12" t="n"/>
       <c r="I3" s="13" t="inlineStr">
@@ -646,28 +646,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.1429</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>33937400</v>
+        <v>36971400</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>52.3</v>
+        <v>23.84</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.157</v>
+        <v>0.11</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.142</v>
+        <v>0.297</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -691,28 +691,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.1429</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>33925900</v>
+        <v>35914000</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.09</v>
+        <v>0.59</v>
       </c>
       <c r="H5" t="n">
-        <v>24.46</v>
+        <v>52.3</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.111</v>
+        <v>0.157</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.297</v>
+        <v>0.142</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -736,39 +736,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>32396100</v>
+        <v>32947900</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>2.39</v>
+        <v>0.96</v>
       </c>
       <c r="H6" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.34</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.154</v>
+        <v>0.4</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.184</v>
+        <v>0.294</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -781,39 +781,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.47</v>
+        <v>0.145</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>32162900</v>
+        <v>32396100</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.39</v>
       </c>
       <c r="H7" t="n">
-        <v>81.92</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.27</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.4</v>
+        <v>0.154</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.294</v>
+        <v>0.184</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>-0.05</v>
+        <v>0.185</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.075</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>30140100</v>
+        <v>30158500</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>1.42</v>
       </c>
       <c r="H8" t="n">
-        <v>33.93</v>
+        <v>32.2</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.214</v>
+        <v>0.213</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0.233</v>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.92</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.011</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>28505100</v>
+        <v>28734100</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H9" t="n">
-        <v>67.05</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.345</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>26479500</v>
+        <v>26985800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H10" t="n">
-        <v>68.58</v>
+        <v>67.47</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -961,39 +961,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>-0.0278</v>
+        <v>0.06</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.2</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>19526600</v>
+        <v>21137900</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.91</v>
+        <v>3.99</v>
       </c>
       <c r="H11" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.81</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.187</v>
+        <v>0.048</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.186</v>
+        <v>0.047</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,39 +1006,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.06</v>
+        <v>0.175</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.2</v>
+        <v>-0.0278</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>19522200</v>
+        <v>20003900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>3.68</v>
+        <v>0.93</v>
       </c>
       <c r="H12" t="n">
-        <v>64.81</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.19</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.048</v>
+        <v>0.187</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.047</v>
+        <v>0.186</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,23 +1060,23 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>-0.0313</v>
+        <v>0.15</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>18815900</v>
+        <v>18816400</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0.53</v>
       </c>
       <c r="H13" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.02</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
@@ -1105,27 +1105,27 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.0071</v>
+        <v>0.715</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.0142</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>14183300</v>
+        <v>14201700</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>80.62</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
+        <v>81.19</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.634</v>
+        <v>0.635</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0.543</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>13243300</v>
+        <v>13376300</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>47.41</v>
@@ -1209,7 +1209,7 @@
       <c r="H16" t="n">
         <v>55.6</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>12160300</v>
+        <v>12160900</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0.79</v>
@@ -1254,7 +1254,7 @@
       <c r="H17" t="n">
         <v>46.5</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1276,39 +1276,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0157</v>
+        <v>0.575</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0.036</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11985200</v>
+        <v>12104700</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.88</v>
+        <v>0.59</v>
       </c>
       <c r="H18" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.07</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1.213</v>
+        <v>0.572</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.197</v>
+        <v>0.544</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1321,39 +1321,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.036</v>
+        <v>1.29</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>11883300</v>
+        <v>12066300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.58</v>
+        <v>1.89</v>
       </c>
       <c r="H19" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.98</v>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.572</v>
+        <v>1.213</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.544</v>
+        <v>1.197</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
       <c r="H20" t="n">
         <v>46.09</v>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1411,39 +1411,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>-0.0667</v>
+        <v>0.43</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9384500</v>
+        <v>9709100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>9.210000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H21" t="n">
-        <v>51.64</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.98</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.467</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,39 +1456,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.435</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.0482</v>
+        <v>-0.0667</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9126900</v>
+        <v>9384500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.25</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>39.67</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.64</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.468</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.48</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9113700</v>
+        <v>9153900</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0.44</v>
       </c>
       <c r="H23" t="n">
-        <v>58.07</v>
+        <v>59.14</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1557,11 +1557,11 @@
       <c r="D24" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="E24" s="15" t="n">
+      <c r="E24" s="16" t="n">
         <v>0.0204</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>8373900</v>
+        <v>8423900</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0.37</v>
@@ -1584,39 +1584,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TALAMT</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0</v>
+        <v>2.08</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0.0505</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7550100</v>
+        <v>7560200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>5.54</v>
+        <v>0.27</v>
       </c>
       <c r="H25" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.8</v>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.078</v>
+        <v>1.95</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.081</v>
+        <v>1.766</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,28 +1629,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>TALAMT</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.0849</v>
+        <v>0.075</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7433900</v>
+        <v>7550100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.8</v>
+        <v>5.54</v>
       </c>
       <c r="H26" t="n">
-        <v>40.99</v>
+        <v>44.56</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.63</v>
+        <v>0.078</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.619</v>
+        <v>0.081</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1674,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0505</v>
+        <v>0.575</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0.0849</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7285700</v>
+        <v>7439000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="H27" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.99</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1.95</v>
+        <v>0.63</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1.766</v>
+        <v>0.619</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,39 +1719,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0524</v>
+        <v>4.73</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>7152400</v>
+        <v>7419800</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.39</v>
+        <v>0.36</v>
       </c>
       <c r="H28" t="n">
-        <v>34.19</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.53</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>2.726</v>
+        <v>4.729</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>2.868</v>
+        <v>4.833</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,28 +1764,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.115</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>7141800</v>
+        <v>7361000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.72</v>
+        <v>0.38</v>
       </c>
       <c r="H29" t="n">
-        <v>28.46</v>
+        <v>34.73</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.395</v>
+        <v>0.138</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.406</v>
+        <v>0.148</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,39 +1809,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>-0.0042</v>
+        <v>0.38</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6951200</v>
+        <v>7270100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.34</v>
+        <v>0.74</v>
       </c>
       <c r="H30" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.32</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>4.727</v>
+        <v>0.394</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>4.832</v>
+        <v>0.405</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,28 +1854,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.115</v>
+        <v>7.14</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>0.0455</v>
+        <v>-0.0014</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6903800</v>
+        <v>7221500</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="H31" t="n">
-        <v>34.73</v>
+        <v>32.57</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.138</v>
+        <v>7.439</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.148</v>
+        <v>7.659</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>0.08599999999999999</v>
+        <v>2.41</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0.0524</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6766000</v>
+        <v>7161300</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>2.91</v>
+        <v>1.39</v>
       </c>
       <c r="H32" t="n">
-        <v>78.48</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.19</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.429</v>
+        <v>2.726</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.434</v>
+        <v>2.868</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>-0.0014</v>
+        <v>0.51</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>0.0968</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6508900</v>
+        <v>6935800</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.39</v>
+        <v>2.98</v>
       </c>
       <c r="H33" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.20999999999999</v>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7.439</v>
+        <v>0.43</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>7.659</v>
+        <v>0.435</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,28 +1989,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>0.0219</v>
+        <v>0.45</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.0843</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>6115800</v>
+        <v>6578700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.46</v>
+        <v>0.93</v>
       </c>
       <c r="H34" t="n">
-        <v>59.76</v>
+        <v>56.35</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.856</v>
+        <v>0.426</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.599</v>
+        <v>0.417</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0.0219</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6085300</v>
+        <v>6118700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.46</v>
+        <v>1.47</v>
       </c>
       <c r="H35" t="n">
-        <v>28.46</v>
+        <v>59.76</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.229</v>
+        <v>0.856</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.279</v>
+        <v>0.599</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,39 +2079,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AIZO</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.3333</v>
+        <v>0.21</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5933000</v>
+        <v>6095100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>3.91</v>
+        <v>0.47</v>
       </c>
       <c r="H36" t="n">
-        <v>64.33</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.4</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.034</v>
+        <v>0.23</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.036</v>
+        <v>0.279</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,39 +2124,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.0014</v>
+        <v>2.57</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5910500</v>
+        <v>6017500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="H37" t="n">
-        <v>38.43</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.99</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>7.427</v>
+        <v>2.629</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>7.893</v>
+        <v>2.56</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>0.0377</v>
+        <v>7.31</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0.0014</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5778800</v>
+        <v>5980800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="H38" t="n">
-        <v>35.22</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.43</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.307</v>
+        <v>7.427</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.331</v>
+        <v>7.893</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,36 +2214,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>AIZO</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0488</v>
+        <v>0.035</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0.1667</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5760800</v>
+        <v>5933100</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.6</v>
+        <v>3.91</v>
       </c>
       <c r="H39" t="n">
-        <v>87.13</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
+        <v>52.49</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.036</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
     </row>
@@ -2255,28 +2259,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5598300</v>
+        <v>5876700</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="H40" t="n">
-        <v>46.99</v>
+        <v>51.72</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2284,10 +2288,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.629</v>
+        <v>2.448</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.56</v>
+        <v>2.399</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2300,39 +2304,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.265</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5568200</v>
+        <v>5819300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1.27</v>
+        <v>0.58</v>
       </c>
       <c r="H41" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.25</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.1</v>
+        <v>0.292</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.091</v>
+        <v>0.28</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2345,39 +2349,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>-0.0122</v>
+        <v>0.115</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5546500</v>
+        <v>5814500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.48</v>
+        <v>1.33</v>
       </c>
       <c r="H42" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.04000000000001</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.446</v>
+        <v>0.1</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.399</v>
+        <v>0.091</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2390,39 +2394,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.28</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.0566</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5405900</v>
+        <v>5813800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="H43" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.59</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.62</v>
+        <v>0.307</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.616</v>
+        <v>0.331</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2435,40 +2439,36 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.0038</v>
+        <v>0.21</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5348700</v>
+        <v>5761800</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="H44" t="n">
-        <v>43.19</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J44" s="9" t="n">
-        <v>5.472</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>5.483</v>
-      </c>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2480,39 +2480,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5034000</v>
+        <v>5405900</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="H45" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.292</v>
+        <v>0.62</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.28</v>
+        <v>0.616</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2525,28 +2525,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>-0.0067</v>
+        <v>5.31</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0.0019</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5000000</v>
+        <v>5363600</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="H46" t="n">
-        <v>35.49</v>
+        <v>42.73</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>4.587</v>
+        <v>5.471</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>4.64</v>
+        <v>5.483</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2570,39 +2570,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>0.0417</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4971600</v>
+        <v>5150300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>1.37</v>
+        <v>0.6</v>
       </c>
       <c r="H47" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.03</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.123</v>
+        <v>1.03</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.124</v>
+        <v>0.968</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2624,27 +2624,27 @@
         </is>
       </c>
       <c r="D48" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>5031600</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H48" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
         <v>0.175</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="11" t="n">
-        <v>4963800</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H48" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="n">
-        <v>0.174</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0.181</v>
@@ -2660,28 +2660,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>-0.0375</v>
+        <v>4.46</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4945200</v>
+        <v>5006300</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="H49" t="n">
-        <v>27.37</v>
+        <v>36.71</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.498</v>
+        <v>4.589</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.601</v>
+        <v>4.64</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2705,39 +2705,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>0.0053</v>
+        <v>0.125</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4919400</v>
+        <v>4971900</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.57</v>
+        <v>1.37</v>
       </c>
       <c r="H50" t="n">
-        <v>38.86</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.03</v>
+        <v>0.123</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.968</v>
+        <v>0.124</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2750,28 +2750,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>2.04</v>
+        <v>0.39</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>0.009899999999999999</v>
+        <v>-0.025</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4703000</v>
+        <v>4946200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="H51" t="n">
-        <v>36.35</v>
+        <v>27.8</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.126</v>
+        <v>0.499</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.235</v>
+        <v>0.601</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2795,33 +2795,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.13</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>0.04</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4636100</v>
+        <v>4778900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J52" s="9" t="n"/>
-      <c r="K52" s="9" t="n"/>
+        <v>35.76</v>
+      </c>
+      <c r="H52" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.129</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
     </row>
@@ -2833,39 +2840,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>0.0133</v>
+        <v>2.05</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4606100</v>
+        <v>4726300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="H53" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.82</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.372</v>
+        <v>2.127</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.37</v>
+        <v>2.235</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2878,40 +2885,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>-0.0049</v>
+        <v>0.105</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4504700</v>
+        <v>4688500</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H54" t="n">
-        <v>44.19</v>
+        <v>0.13</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J54" s="9" t="n">
-        <v>2.041</v>
-      </c>
-      <c r="K54" s="9" t="n">
-        <v>2.068</v>
-      </c>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
     </row>
@@ -2923,39 +2923,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0602</v>
+        <v>0.38</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4345000</v>
+        <v>4610500</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H55" t="n">
-        <v>54.38</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.97</v>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.425</v>
+        <v>0.372</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.417</v>
+        <v>0.37</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2968,28 +2968,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0</v>
+        <v>2.02</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4313300</v>
+        <v>4590800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.22</v>
+        <v>1.4</v>
       </c>
       <c r="H56" t="n">
-        <v>25.69</v>
+        <v>44.19</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.495</v>
+        <v>2.041</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.653</v>
+        <v>2.068</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3013,28 +3013,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.08929999999999999</v>
+        <v>0.44</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4242300</v>
+        <v>4466800</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
       <c r="H57" t="n">
-        <v>58.07</v>
+        <v>25.69</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.573</v>
+        <v>0.495</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.476</v>
+        <v>0.653</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3058,28 +3058,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0.0075</v>
+        <v>0.61</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0.08929999999999999</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4077100</v>
+        <v>4244500</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.33</v>
+        <v>0.72</v>
       </c>
       <c r="H58" t="n">
-        <v>44.61</v>
+        <v>58.07</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>2.746</v>
+        <v>0.573</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>2.743</v>
+        <v>0.476</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3103,28 +3103,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.05429999999999999</v>
+        <v>2.68</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4031800</v>
+        <v>4080400</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H59" t="n">
-        <v>41.88</v>
+        <v>44.61</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.733</v>
+        <v>2.746</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.722</v>
+        <v>2.743</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3148,28 +3148,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.0245</v>
+        <v>0.675</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4023600</v>
+        <v>4058800</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.14</v>
+        <v>0.27</v>
       </c>
       <c r="H60" t="n">
-        <v>53.18</v>
+        <v>41.05</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.826</v>
+        <v>0.733</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.789</v>
+        <v>0.722</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3193,39 +3193,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.008</v>
+        <v>0.83</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3984500</v>
+        <v>4034900</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="H61" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.36</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.619</v>
+        <v>0.826</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.608</v>
+        <v>0.789</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3238,39 +3238,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0.008</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3884500</v>
+        <v>3984500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.7</v>
+        <v>1.17</v>
       </c>
       <c r="H62" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
+        <v>75.14</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.175</v>
+        <v>0.619</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.195</v>
+        <v>0.608</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3283,39 +3283,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>0.0147</v>
+        <v>0.165</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3872700</v>
+        <v>3964600</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.15</v>
+        <v>0.71</v>
       </c>
       <c r="H63" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>4.882</v>
+        <v>0.175</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>4.742</v>
+        <v>0.195</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3328,28 +3328,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>4.8</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3855100</v>
+        <v>3909000</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>1.15</v>
+        <v>0.16</v>
       </c>
       <c r="H64" t="n">
-        <v>49.15</v>
+        <v>46.7</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.295</v>
+        <v>4.88</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.295</v>
+        <v>4.741</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3373,39 +3373,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0.026</v>
+        <v>-0.0169</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3779600</v>
+        <v>3860900</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="H65" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.78</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.744</v>
+        <v>0.295</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.707</v>
+        <v>0.295</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3418,28 +3418,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0.022</v>
+        <v>0.755</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3715000</v>
+        <v>3791300</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="H66" t="n">
-        <v>43.04</v>
+        <v>45.85</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.508</v>
+        <v>0.768</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.465</v>
+        <v>0.771</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3463,39 +3463,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>0.79</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>0.026</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3711300</v>
+        <v>3780300</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.46</v>
+        <v>1.43</v>
       </c>
       <c r="H67" t="n">
-        <v>45.85</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.75</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.768</v>
+        <v>0.744</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.771</v>
+        <v>0.707</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3508,39 +3508,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>0.04</v>
+        <v>0.47</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>0.033</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3591500</v>
+        <v>3776200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>26.87</v>
+        <v>0.37</v>
       </c>
       <c r="H68" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.03</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.127</v>
+        <v>0.509</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.129</v>
+        <v>0.465</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3553,39 +3553,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0.0053</v>
+        <v>1.96</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3508200</v>
+        <v>3662600</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="H69" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.29</v>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>5.859</v>
+        <v>1.927</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>6.145</v>
+        <v>1.951</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3598,39 +3598,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>5.68</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3482000</v>
+        <v>3661700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="H70" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.97</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.926</v>
+        <v>5.86</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.951</v>
+        <v>6.145</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3643,28 +3643,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0</v>
+        <v>0.275</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0.0377</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3313200</v>
+        <v>3324500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>2.21</v>
+        <v>0.55</v>
       </c>
       <c r="H71" t="n">
-        <v>41.39</v>
+        <v>25.26</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.129</v>
+        <v>0.321</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.13</v>
+        <v>0.366</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3688,28 +3688,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>-0.0016</v>
+        <v>0.125</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3252600</v>
+        <v>3313200</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.5</v>
+        <v>2.21</v>
       </c>
       <c r="H72" t="n">
-        <v>37.39</v>
+        <v>41.39</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>6.357</v>
+        <v>0.129</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>6.709</v>
+        <v>0.13</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3733,39 +3733,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E73" s="15" t="n">
-        <v>0.0052</v>
+        <v>6.21</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3195300</v>
+        <v>3269600</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="H73" t="n">
-        <v>67.08</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.8</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>6.358</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.883</v>
+        <v>6.709</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.0571</v>
+        <v>0.975</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3188300</v>
+        <v>3214900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="H74" t="n">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
+        <v>67.08</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.165</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.166</v>
+        <v>0.883</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3823,39 +3823,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0.0303</v>
+        <v>9.99</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>0.004</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3059000</v>
+        <v>3209600</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="H75" t="n">
-        <v>53.39</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.64</v>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>5.053</v>
+        <v>9.996</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>5.049</v>
+        <v>10.13</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3868,39 +3868,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.003</v>
+        <v>0.185</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>3029700</v>
+        <v>3188300</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.24</v>
+        <v>0.59</v>
       </c>
       <c r="H76" t="n">
-        <v>47</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
+        <v>65.31999999999999</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>9.994999999999999</v>
+        <v>0.165</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>10.129</v>
+        <v>0.166</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3913,28 +3913,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0.0377</v>
+        <v>5.11</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3024500</v>
+        <v>3093700</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="H77" t="n">
-        <v>25.26</v>
+        <v>53.94</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.321</v>
+        <v>5.054</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.366</v>
+        <v>5.049</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.0246</v>
+        <v>1.24</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>3018600</v>
+        <v>3066500</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H78" t="n">
-        <v>43.04</v>
+        <v>41.31</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.287</v>
+        <v>1.286</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>1.315</v>
@@ -4018,10 +4018,10 @@
         <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2971700</v>
+        <v>3014200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H79" t="n">
         <v>27.73</v>
@@ -4048,40 +4048,33 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.0361</v>
+        <v>0.765</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2820900</v>
+        <v>2833700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="H80" t="n">
-        <v>30.74</v>
+        <v>0.05</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J80" s="9" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="K80" s="9" t="n">
-        <v>0.967</v>
-      </c>
+      <c r="J80" s="9" t="n"/>
+      <c r="K80" s="9" t="n"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
     </row>
@@ -4093,33 +4086,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2731300</v>
+        <v>2825700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.05</v>
+        <v>0.88</v>
+      </c>
+      <c r="H81" t="n">
+        <v>30.74</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J81" s="9" t="n"/>
-      <c r="K81" s="9" t="n"/>
+      <c r="J81" s="9" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>0.967</v>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
     </row>
@@ -4131,39 +4131,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>0.0111</v>
+        <v>0.58</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2730300</v>
+        <v>2778900</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="H82" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.3</v>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.489</v>
+        <v>0.523</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.548</v>
+        <v>0.475</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,39 +4176,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>0.0174</v>
+        <v>0.455</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2727800</v>
+        <v>2738600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="H83" t="n">
-        <v>65.97</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.55</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.523</v>
+        <v>0.489</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.475</v>
+        <v>0.548</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4232,11 +4232,11 @@
       <c r="D84" s="9" t="n">
         <v>3.84</v>
       </c>
-      <c r="E84" s="17" t="n">
+      <c r="E84" s="15" t="n">
         <v>-0.0129</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2686200</v>
+        <v>2691900</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0.33</v>
@@ -4266,39 +4266,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.0089</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2584700</v>
+        <v>2669300</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>1.27</v>
+        <v>0.23</v>
       </c>
       <c r="H85" t="n">
-        <v>51.76</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.29</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.644</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.918</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,39 +4311,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>0.0574</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2499000</v>
+        <v>2601700</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.32</v>
+        <v>0.85</v>
       </c>
       <c r="H86" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.48</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.626</v>
+        <v>1.282</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.686</v>
+        <v>1.231</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,39 +4356,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2474700</v>
+        <v>2584700</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.32</v>
+        <v>1.27</v>
       </c>
       <c r="H87" t="n">
-        <v>54.66</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.76</v>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.353</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.329</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4412,14 +4412,14 @@
       <c r="D88" s="9" t="n">
         <v>0.255</v>
       </c>
-      <c r="E88" s="15" t="n">
+      <c r="E88" s="16" t="n">
         <v>0.02</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2473800</v>
+        <v>2554700</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H88" t="n">
         <v>41.5</v>
@@ -4446,39 +4446,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.0574</v>
+        <v>-0.0061</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2467500</v>
+        <v>2506200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.8</v>
+        <v>0.32</v>
       </c>
       <c r="H89" t="n">
-        <v>51.48</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.12</v>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.282</v>
+        <v>1.625</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.231</v>
+        <v>1.686</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,39 +4491,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>0.0061</v>
+        <v>0.36</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2424400</v>
+        <v>2496000</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="H90" t="n">
-        <v>66.97</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.66</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.798</v>
+        <v>0.353</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.774</v>
+        <v>0.329</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,28 +4536,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>0.0308</v>
+        <v>0.68</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0.0709</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2402600</v>
+        <v>2489200</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.24</v>
+        <v>0.47</v>
       </c>
       <c r="H91" t="n">
-        <v>47.84</v>
+        <v>42.69</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.343</v>
+        <v>0.742</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.335</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,28 +4581,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E92" s="15" t="n">
-        <v>0.0513</v>
+        <v>0.33</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2362000</v>
+        <v>2481400</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H92" t="n">
-        <v>55.11</v>
+        <v>45.85</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.393</v>
+        <v>0.343</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.363</v>
+        <v>0.335</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,39 +4626,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>-0.0097</v>
+        <v>0.82</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2340600</v>
+        <v>2424400</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.86</v>
+        <v>0.45</v>
       </c>
       <c r="H93" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.97</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.537</v>
+        <v>0.798</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,28 +4671,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.0551</v>
+        <v>0.41</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2251100</v>
+        <v>2372100</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="H94" t="n">
-        <v>41.18</v>
+        <v>55.11</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.741</v>
+        <v>0.393</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.363</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,28 +4716,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.15</v>
+        <v>0.51</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>0.0268</v>
+        <v>-0.0097</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2188600</v>
+        <v>2358700</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.48</v>
+        <v>0.87</v>
       </c>
       <c r="H95" t="n">
-        <v>62.11</v>
+        <v>31.45</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.07</v>
+        <v>0.537</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,39 +4761,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>0.0245</v>
+        <v>3.32</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>0.0375</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2148900</v>
+        <v>2263100</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.67</v>
+        <v>0.37</v>
       </c>
       <c r="H96" t="n">
-        <v>87.79000000000001</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
+        <v>44.01</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>2.916</v>
+        <v>3.347</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.485</v>
+        <v>3.583</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,39 +4806,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>0.0268</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2140300</v>
+        <v>2216300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
       <c r="H97" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.11</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.222</v>
+        <v>1.07</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.31</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,39 +4851,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>0.0312</v>
+        <v>1.17</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2138200</v>
+        <v>2202600</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="H98" t="n">
-        <v>42.25</v>
-      </c>
-      <c r="I98" s="16" t="inlineStr">
+        <v>36.42</v>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>3.345</v>
+        <v>1.222</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>3.583</v>
+        <v>1.31</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>3.35</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0.0276</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2047800</v>
+        <v>2158900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="H99" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>87.95</v>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.96</v>
+        <v>2.917</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.044</v>
+        <v>2.485</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,28 +4941,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.92</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1997800</v>
+        <v>2050300</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.19</v>
+        <v>0.49</v>
       </c>
       <c r="H100" t="n">
-        <v>34.75</v>
+        <v>26.79</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>7.131</v>
+        <v>0.961</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>7.56</v>
+        <v>1.044</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,39 +4986,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0.06519999999999999</v>
+        <v>6.81</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1963500</v>
+        <v>2028000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>1.75</v>
+        <v>0.19</v>
       </c>
       <c r="H101" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="I101" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.75</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.213</v>
+        <v>7.131</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.21</v>
+        <v>7.56</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,39 +5031,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0.06519999999999999</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1905200</v>
+        <v>1979300</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.16</v>
+        <v>1.77</v>
       </c>
       <c r="H102" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.8</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.645</v>
+        <v>0.213</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.918</v>
+        <v>0.21</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5087,11 +5087,11 @@
       <c r="D103" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E103" s="17" t="n">
+      <c r="E103" s="15" t="n">
         <v>-0.009000000000000001</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1900200</v>
+        <v>1902700</v>
       </c>
       <c r="G103" s="12" t="n">
         <v>0.2</v>
@@ -5121,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="E104" s="15" t="n">
-        <v>0.0195</v>
+        <v>-0.0167</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1832100</v>
+        <v>1888900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="H104" t="n">
-        <v>33.14</v>
+        <v>21.3</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.692</v>
+        <v>1.356</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.757</v>
+        <v>1.54</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,28 +5166,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>-0.0026</v>
+        <v>1.56</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>0.013</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1809200</v>
+        <v>1874600</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.63</v>
+        <v>0.31</v>
       </c>
       <c r="H105" t="n">
-        <v>38.5</v>
+        <v>31.59</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>7.823</v>
+        <v>1.691</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>7.858</v>
+        <v>1.757</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>-0.0083</v>
+        <v>7.67</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1806500</v>
+        <v>1810700</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="H106" t="n">
-        <v>21.84</v>
+        <v>37.97</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.357</v>
+        <v>7.822</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.54</v>
+        <v>7.858</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5267,7 +5267,7 @@
       <c r="D107" s="9" t="n">
         <v>0.235</v>
       </c>
-      <c r="E107" s="15" t="n">
+      <c r="E107" s="16" t="n">
         <v>0.0444</v>
       </c>
       <c r="F107" s="11" t="n">
@@ -5279,7 +5279,7 @@
       <c r="H107" t="n">
         <v>73.31</v>
       </c>
-      <c r="I107" s="16" t="inlineStr">
+      <c r="I107" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5301,39 +5301,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>6.64</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>0.0408</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1683500</v>
+        <v>1736800</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="H108" t="n">
-        <v>51.48</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.34</v>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.865</v>
+        <v>6.239</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.86</v>
+        <v>5.952</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,39 +5346,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>-0.018</v>
+        <v>0.865</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1672500</v>
+        <v>1683500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>1.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>67.76000000000001</v>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.48</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>2.627</v>
+        <v>0.865</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>2.452</v>
+        <v>0.86</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,39 +5391,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>3.96</v>
+        <v>2.73</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>0.0154</v>
+        <v>-0.018</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1643500</v>
+        <v>1677500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.17</v>
+        <v>1.24</v>
       </c>
       <c r="H110" t="n">
-        <v>52.48</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>3.955</v>
+        <v>2.627</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>3.588</v>
+        <v>2.452</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,39 +5436,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>0.0299</v>
+        <v>0.615</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0.0165</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1626900</v>
+        <v>1654100</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="H111" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="I111" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.74</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.716</v>
+        <v>0.666</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.781</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>0.0248</v>
+        <v>3.96</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1606000</v>
+        <v>1652400</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H112" t="n">
-        <v>39.89</v>
+        <v>52.48</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.667</v>
+        <v>3.955</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>3.588</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0</v>
+        <v>0.695</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.0373</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1559500</v>
+        <v>1629500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="H113" t="n">
-        <v>42.76</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.04</v>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.287</v>
+        <v>0.716</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.283</v>
+        <v>0.781</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5582,11 +5582,11 @@
       <c r="D114" s="9" t="n">
         <v>0.84</v>
       </c>
-      <c r="E114" s="15" t="n">
+      <c r="E114" s="16" t="n">
         <v>0.0244</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1552600</v>
+        <v>1582500</v>
       </c>
       <c r="G114" s="12" t="n">
         <v>0.22</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1525000</v>
+        <v>1543000</v>
       </c>
       <c r="G115" s="12" t="n">
         <v>0.1</v>
@@ -5639,7 +5639,7 @@
       <c r="H115" t="n">
         <v>47.56</v>
       </c>
-      <c r="I115" s="16" t="inlineStr">
+      <c r="I115" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5661,38 +5661,40 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>0.0263</v>
+        <v>0.27</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1511100</v>
+        <v>1539400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="H116" t="n">
-        <v>69.33</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.76</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="K116" s="9" t="n"/>
+        <v>0.287</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>0.283</v>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
     </row>
@@ -5704,40 +5706,38 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>0.0329</v>
+        <v>0.39</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1487200</v>
+        <v>1537100</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="H117" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
+        <v>69.33</v>
+      </c>
+      <c r="I117" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>6.234</v>
-      </c>
-      <c r="K117" s="9" t="n">
-        <v>5.951</v>
-      </c>
+        <v>0.331</v>
+      </c>
+      <c r="K117" s="9" t="n"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
     </row>
@@ -5749,28 +5749,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>0.0481</v>
+        <v>6.76</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>0.0015</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1456300</v>
+        <v>1532900</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="H118" t="n">
-        <v>49.45</v>
+        <v>50.2</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5778,10 +5778,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.555</v>
+        <v>6.756</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.52</v>
+        <v>6.82</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5794,39 +5794,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>-0.0058</v>
+        <v>0.64</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1431700</v>
+        <v>1512700</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.25</v>
+        <v>0.73</v>
       </c>
       <c r="H119" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.16</v>
+      </c>
+      <c r="I119" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.761</v>
+        <v>0.637</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.874</v>
+        <v>0.625</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5839,28 +5839,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>0.0481</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1431100</v>
+        <v>1456300</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="H120" t="n">
-        <v>36.3</v>
+        <v>49.45</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.5</v>
+        <v>0.555</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.521</v>
+        <v>0.52</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5884,39 +5884,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>-0.0048</v>
+        <v>1.7</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1412100</v>
+        <v>1446700</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>7.66</v>
+        <v>0.25</v>
       </c>
       <c r="H121" t="n">
-        <v>41.44</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.28</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.078</v>
+        <v>1.761</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.083</v>
+        <v>1.874</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5929,39 +5929,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>-0.0127</v>
+        <v>0.47</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1375400</v>
+        <v>1433000</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="H122" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I122" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.3</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.247</v>
+        <v>0.5</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>2.184</v>
+        <v>0.521</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5974,39 +5974,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E123" s="15" t="n">
-        <v>0.0159</v>
+        <v>2.07</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1320200</v>
+        <v>1414400</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.64</v>
+        <v>7.68</v>
       </c>
       <c r="H123" t="n">
-        <v>54.16</v>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
+        <v>45.34</v>
+      </c>
+      <c r="I123" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.637</v>
+        <v>2.078</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.625</v>
+        <v>2.083</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6019,28 +6019,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>0</v>
+        <v>2.79</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1317400</v>
+        <v>1407800</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.77</v>
+        <v>0.15</v>
       </c>
       <c r="H124" t="n">
-        <v>36.07</v>
+        <v>51.36</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.251</v>
+        <v>2.793</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.272</v>
+        <v>2.677</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6064,39 +6064,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>2.79</v>
+        <v>2.34</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>0.0109</v>
+        <v>-0.0127</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1313000</v>
+        <v>1376400</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="H125" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.79</v>
+      </c>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>2.793</v>
+        <v>2.247</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>2.677</v>
+        <v>2.184</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6109,28 +6109,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="E126" s="15" t="n">
-        <v>0.0039</v>
+        <v>-0.0098</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1306300</v>
+        <v>1353500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.22</v>
+        <v>1.17</v>
       </c>
       <c r="H126" t="n">
-        <v>46.18</v>
+        <v>37.58</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>2.599</v>
+        <v>1.043</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>2.61</v>
+        <v>1.134</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6154,28 +6154,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.835</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1297900</v>
+        <v>1326000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="H127" t="n">
-        <v>60.12</v>
+        <v>33.02</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.749</v>
+        <v>0.883</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.721</v>
+        <v>0.945</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6199,28 +6199,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>-0.0098</v>
+        <v>0.235</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1281200</v>
+        <v>1317400</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>1.11</v>
+        <v>0.77</v>
       </c>
       <c r="H128" t="n">
-        <v>37.58</v>
+        <v>36.07</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.043</v>
+        <v>0.251</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.134</v>
+        <v>0.272</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6244,28 +6244,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E129" s="15" t="n">
-        <v>0.0315</v>
+        <v>2.56</v>
+      </c>
+      <c r="E129" s="16" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1268000</v>
+        <v>1313200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>1.82</v>
+        <v>0.22</v>
       </c>
       <c r="H129" t="n">
-        <v>64.43000000000001</v>
+        <v>46.18</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.623</v>
+        <v>2.599</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.609</v>
+        <v>2.61</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6289,28 +6289,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>0.028</v>
+        <v>0.765</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1266700</v>
+        <v>1297900</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.35</v>
+        <v>0.98</v>
       </c>
       <c r="H130" t="n">
-        <v>44.65</v>
+        <v>60.12</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6318,10 +6318,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.143</v>
+        <v>0.749</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.105</v>
+        <v>0.721</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6334,28 +6334,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>0.028</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1264500</v>
+        <v>1284400</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="H131" t="n">
-        <v>53.66</v>
+        <v>44.65</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.173</v>
+        <v>1.143</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.143</v>
+        <v>1.105</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6379,28 +6379,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0.0182</v>
+        <v>1.19</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1245100</v>
+        <v>1282900</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="H132" t="n">
-        <v>34.76</v>
+        <v>53.66</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6408,10 +6408,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.884</v>
+        <v>1.173</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.945</v>
+        <v>1.143</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6424,39 +6424,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="E133" s="15" t="n">
-        <v>0.004</v>
+        <v>0.66</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>0.0394</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1227400</v>
+        <v>1275800</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.48</v>
+        <v>1.83</v>
       </c>
       <c r="H133" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="I133" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.76000000000001</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>7.562</v>
+        <v>0.623</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>7.745</v>
+        <v>0.609</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6469,39 +6469,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>0.0262</v>
+        <v>7.52</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1196200</v>
+        <v>1270300</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="H134" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.9</v>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>2.081</v>
+        <v>7.563</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.993</v>
+        <v>7.745</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6514,39 +6514,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0</v>
+        <v>1.97</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>0.0314</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1186800</v>
+        <v>1208300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="H135" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="I135" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.65</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>7.91</v>
+        <v>2.082</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>7.954</v>
+        <v>1.993</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6559,28 +6559,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E136" s="15" t="n">
-        <v>0.0123</v>
+        <v>0.99</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>0.0206</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1164300</v>
+        <v>1197800</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="H136" t="n">
-        <v>42.99</v>
+        <v>45.65</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.432</v>
+        <v>1.033</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.437</v>
+        <v>0.955</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6604,39 +6604,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DESTINI</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>-0.0435</v>
+        <v>7.91</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1160800</v>
+        <v>1189800</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>4.57</v>
+        <v>0.35</v>
       </c>
       <c r="H137" t="n">
-        <v>40.95</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.59</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.228</v>
+        <v>7.91</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.243</v>
+        <v>7.954</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6649,28 +6649,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>HOCKSOON</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>-0.0638</v>
+        <v>3.74</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1155200</v>
+        <v>1187800</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>1.78</v>
+        <v>0.38</v>
       </c>
       <c r="H138" t="n">
-        <v>33.23</v>
+        <v>47.33</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.238</v>
+        <v>3.822</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.276</v>
+        <v>3.711</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6694,28 +6694,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E139" s="15" t="n">
-        <v>0.0274</v>
+        <v>10.64</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0.033</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1154700</v>
+        <v>1167200</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="H139" t="n">
-        <v>47.77</v>
+        <v>56.81</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>3.823</v>
+        <v>10.426</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>3.711</v>
+        <v>9.805999999999999</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6739,28 +6739,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E140" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.41</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1151700</v>
+        <v>1166300</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="H140" t="n">
-        <v>40.89</v>
+        <v>42.99</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>2.87</v>
+        <v>0.432</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>3.002</v>
+        <v>0.437</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6784,39 +6784,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>-0.0156</v>
+        <v>2.77</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1138500</v>
+        <v>1165500</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="H141" t="n">
-        <v>51.29</v>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.89</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>4.374</v>
+        <v>2.87</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>4.431</v>
+        <v>3.002</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6829,28 +6829,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>DESTINI</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>10.62</v>
+        <v>0.22</v>
       </c>
       <c r="E142" s="15" t="n">
-        <v>0.0311</v>
+        <v>-0.0435</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1137400</v>
+        <v>1160800</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.33</v>
+        <v>4.57</v>
       </c>
       <c r="H142" t="n">
-        <v>56.5</v>
+        <v>40.95</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>10.424</v>
+        <v>0.228</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>9.805</v>
+        <v>0.243</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6874,28 +6874,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>HOCKSOON</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>-0.0015</v>
+        <v>0.22</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>-0.0638</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1134000</v>
+        <v>1155200</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.27</v>
+        <v>1.78</v>
       </c>
       <c r="H143" t="n">
-        <v>48.52</v>
+        <v>33.23</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>6.754</v>
+        <v>0.238</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>6.82</v>
+        <v>0.276</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6919,39 +6919,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>7.22</v>
+        <v>4.41</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0.0374</v>
+        <v>-0.0178</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1129800</v>
+        <v>1139900</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H144" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.9</v>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>7.305</v>
+        <v>4.373</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>6.915</v>
+        <v>4.431</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6964,28 +6964,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>0</v>
+        <v>7.22</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1116200</v>
+        <v>1139800</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="H145" t="n">
-        <v>56.16</v>
+        <v>49.98</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.266</v>
+        <v>7.305</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.257</v>
+        <v>6.915</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7009,28 +7009,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v>0.0206</v>
+        <v>1.48</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1101800</v>
+        <v>1124500</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.27</v>
+        <v>0.61</v>
       </c>
       <c r="H146" t="n">
-        <v>45.65</v>
+        <v>35.83</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.033</v>
+        <v>1.594</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.955</v>
+        <v>1.656</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7054,28 +7054,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="E147" s="15" t="n">
-        <v>0.0137</v>
+        <v>0.27</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1098300</v>
+        <v>1118200</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H147" t="n">
-        <v>35.83</v>
+        <v>56.16</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.594</v>
+        <v>0.266</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.656</v>
+        <v>0.257</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7108,19 +7108,19 @@
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E148" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.9</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1075800</v>
+        <v>1086800</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H148" t="n">
-        <v>51.28</v>
+        <v>48.85</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.914</v>
+        <v>0.913</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.883</v>
+        <v>0.882</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7167,7 +7167,7 @@
       <c r="H149" t="n">
         <v>40.21</v>
       </c>
-      <c r="I149" s="16" t="inlineStr">
+      <c r="I149" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7204,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>975800</v>
+        <v>980600</v>
       </c>
       <c r="G150" s="12" t="n">
         <v>0.36</v>
@@ -7212,7 +7212,7 @@
       <c r="H150" t="n">
         <v>55.76</v>
       </c>
-      <c r="I150" s="16" t="inlineStr">
+      <c r="I150" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7245,7 +7245,7 @@
       <c r="D151" s="9" t="n">
         <v>0.82</v>
       </c>
-      <c r="E151" s="15" t="n">
+      <c r="E151" s="16" t="n">
         <v>0.0061</v>
       </c>
       <c r="F151" s="11" t="n">
@@ -7290,7 +7290,7 @@
       <c r="D152" s="9" t="n">
         <v>0.64</v>
       </c>
-      <c r="E152" s="15" t="n">
+      <c r="E152" s="16" t="n">
         <v>0.0407</v>
       </c>
       <c r="F152" s="11" t="n">
@@ -7335,11 +7335,11 @@
       <c r="D153" s="9" t="n">
         <v>0.59</v>
       </c>
-      <c r="E153" s="15" t="n">
+      <c r="E153" s="16" t="n">
         <v>0.0442</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>960600</v>
+        <v>966700</v>
       </c>
       <c r="G153" s="12" t="n">
         <v>0.22</v>
@@ -7369,28 +7369,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.795</v>
+        <v>1.01</v>
       </c>
       <c r="E154" s="15" t="n">
-        <v>0.0258</v>
+        <v>-0.0098</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>899600</v>
+        <v>929600</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.39</v>
+        <v>0.68</v>
       </c>
       <c r="H154" t="n">
-        <v>20.98</v>
+        <v>31.48</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.911</v>
+        <v>1.073</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.063</v>
+        <v>1.126</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7414,28 +7414,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0.0258</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>872200</v>
+        <v>910000</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="H155" t="n">
-        <v>32.98</v>
+        <v>20.98</v>
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.074</v>
+        <v>0.911</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.126</v>
+        <v>1.063</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7468,19 +7468,19 @@
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E156" s="10" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E156" s="15" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>867500</v>
+        <v>898500</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="H156" t="n">
-        <v>30.05</v>
+        <v>28.87</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>1.22</v>
+        <v>1.219</v>
       </c>
       <c r="K156" s="9" t="n">
         <v>1.306</v>
@@ -7515,7 +7515,7 @@
       <c r="D157" s="9" t="n">
         <v>2.13</v>
       </c>
-      <c r="E157" s="15" t="n">
+      <c r="E157" s="16" t="n">
         <v>0.004699999999999999</v>
       </c>
       <c r="F157" s="11" t="n">
@@ -7527,7 +7527,7 @@
       <c r="H157" t="n">
         <v>54.56</v>
       </c>
-      <c r="I157" s="16" t="inlineStr">
+      <c r="I157" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7558,19 +7558,19 @@
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="E158" s="15" t="n">
-        <v>0.0286</v>
+        <v>5.41</v>
+      </c>
+      <c r="E158" s="16" t="n">
+        <v>0.0305</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>800900</v>
+        <v>808200</v>
       </c>
       <c r="G158" s="12" t="n">
         <v>0.21</v>
       </c>
       <c r="H158" t="n">
-        <v>48.66</v>
+        <v>48.9</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>5.479</v>
+        <v>5.48</v>
       </c>
       <c r="K158" s="9" t="n">
         <v>5.383</v>
@@ -7594,39 +7594,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E159" s="15" t="n">
-        <v>0.0347</v>
+        <v>1.06</v>
+      </c>
+      <c r="E159" s="16" t="n">
+        <v>0.0291</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>790100</v>
+        <v>798900</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="H159" t="n">
-        <v>52.81</v>
-      </c>
-      <c r="I159" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.11</v>
+      </c>
+      <c r="I159" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.741</v>
+        <v>1.083</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>1.096</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7648,19 +7648,19 @@
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="E160" s="15" t="n">
-        <v>0.0276</v>
+        <v>4.1</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>0.0302</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>789300</v>
+        <v>797000</v>
       </c>
       <c r="G160" s="12" t="n">
         <v>0.32</v>
       </c>
       <c r="H160" t="n">
-        <v>43.78</v>
+        <v>44.15</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>4.24</v>
+        <v>4.241</v>
       </c>
       <c r="K160" s="9" t="n">
         <v>4.308</v>
@@ -7684,39 +7684,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E161" s="15" t="n">
-        <v>0.0291</v>
+        <v>4.23</v>
+      </c>
+      <c r="E161" s="16" t="n">
+        <v>0.0024</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>788800</v>
+        <v>795500</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="H161" t="n">
-        <v>47.11</v>
-      </c>
-      <c r="I161" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.16</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>1.083</v>
+        <v>4.374</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>1.096</v>
+        <v>4.681</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7729,28 +7729,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="E162" s="15" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.745</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>0.0347</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>729800</v>
+        <v>790100</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="H162" t="n">
-        <v>45.08</v>
+        <v>52.81</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>8.589</v>
+        <v>0.741</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>8.68</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7774,28 +7774,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="E163" s="17" t="n">
-        <v>-0.0024</v>
+        <v>1.98</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>713400</v>
+        <v>758200</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.17</v>
+        <v>0.96</v>
       </c>
       <c r="H163" t="n">
-        <v>34.91</v>
+        <v>30.83</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>4.372</v>
+        <v>2.027</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>4.68</v>
+        <v>2.075</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7819,28 +7819,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E164" s="15" t="n">
-        <v>0.0172</v>
+        <v>8.43</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>702800</v>
+        <v>748000</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="H164" t="n">
-        <v>47.73</v>
+        <v>45.08</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -7848,10 +7848,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>1.227</v>
+        <v>8.589</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>1.085</v>
+        <v>8.68</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7864,39 +7864,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.3</v>
+        <v>0.635</v>
       </c>
       <c r="E165" s="15" t="n">
-        <v>0.0317</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>699700</v>
+        <v>745100</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.29</v>
+        <v>0.67</v>
       </c>
       <c r="H165" t="n">
-        <v>55.45</v>
-      </c>
-      <c r="I165" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.02</v>
+      </c>
+      <c r="I165" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.265</v>
+        <v>0.633</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.179</v>
+        <v>0.631</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7909,39 +7909,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0360</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SAG</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E166" s="17" t="n">
-        <v>-0.0234</v>
+        <v>1.29</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>652200</v>
+        <v>739900</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>3.65</v>
+        <v>0.3</v>
       </c>
       <c r="H166" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="I166" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.64</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>0.637</v>
+        <v>1.264</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>0.644</v>
+        <v>1.178</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7954,39 +7954,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E167" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.68</v>
+      </c>
+      <c r="E167" s="15" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>645100</v>
+        <v>712100</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.58</v>
+        <v>0.9</v>
       </c>
       <c r="H167" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I167" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.16</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.633</v>
+        <v>1.749</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.631</v>
+        <v>1.786</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7999,28 +7999,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E168" s="10" t="n">
-        <v>0</v>
+        <v>1.18</v>
+      </c>
+      <c r="E168" s="16" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>639200</v>
+        <v>704100</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="H168" t="n">
-        <v>42.09</v>
+        <v>47.73</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.727</v>
+        <v>1.227</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.743</v>
+        <v>1.085</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8044,39 +8044,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="E169" s="15" t="n">
-        <v>0.0115</v>
+        <v>13.06</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>623600</v>
+        <v>675900</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
       <c r="H169" t="n">
-        <v>35.44</v>
-      </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.86</v>
+      </c>
+      <c r="I169" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>5.442</v>
+        <v>13.023</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>5.778</v>
+        <v>13.371</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8089,39 +8089,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>0</v>
+        <v>5.25</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>620600</v>
+        <v>653000</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.09</v>
+        <v>0.51</v>
       </c>
       <c r="H170" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="I170" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.72</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>13.023</v>
+        <v>5.441</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>13.371</v>
+        <v>5.778</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8134,39 +8134,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0360</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>SAG</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>3.13</v>
+        <v>0.625</v>
       </c>
       <c r="E171" s="15" t="n">
-        <v>0.0097</v>
+        <v>-0.0234</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>594000</v>
+        <v>652200</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.39</v>
+        <v>3.65</v>
       </c>
       <c r="H171" t="n">
-        <v>51.31</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.91</v>
+      </c>
+      <c r="I171" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>3.163</v>
+        <v>0.637</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>2.911</v>
+        <v>0.644</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8179,39 +8179,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SUPERLN</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E172" s="15" t="n">
-        <v>0.0161</v>
+        <v>0.71</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>588300</v>
+        <v>639300</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>1.44</v>
+        <v>0.33</v>
       </c>
       <c r="H172" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="I172" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.09</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>0.872</v>
+        <v>0.727</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>0.846</v>
+        <v>0.743</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8224,39 +8224,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>SUPERLN</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E173" s="17" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.945</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>577000</v>
+        <v>619700</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.34</v>
+        <v>1.52</v>
       </c>
       <c r="H173" t="n">
-        <v>46.03</v>
-      </c>
-      <c r="I173" s="16" t="inlineStr">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="I173" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>0.892</v>
+        <v>0.872</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>0.906</v>
+        <v>0.846</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8269,39 +8269,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E174" s="10" t="n">
-        <v>0</v>
+        <v>0.88</v>
+      </c>
+      <c r="E174" s="15" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>548800</v>
+        <v>614000</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H174" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.47</v>
+      </c>
+      <c r="I174" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.359</v>
+        <v>0.891</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.341</v>
+        <v>0.906</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8314,28 +8314,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E175" s="15" t="n">
-        <v>0.027</v>
+        <v>3.13</v>
+      </c>
+      <c r="E175" s="16" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>538300</v>
+        <v>594400</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.23</v>
+        <v>0.39</v>
       </c>
       <c r="H175" t="n">
-        <v>47.94</v>
+        <v>51.31</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>0.771</v>
+        <v>3.163</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>0.771</v>
+        <v>2.911</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8359,28 +8359,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>2.05</v>
+        <v>0.75</v>
       </c>
       <c r="E176" s="15" t="n">
-        <v>0.0049</v>
+        <v>-0.0066</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>536100</v>
+        <v>575500</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="H176" t="n">
-        <v>42.57</v>
+        <v>59.2</v>
       </c>
       <c r="I176" s="13" t="inlineStr">
         <is>
@@ -8388,10 +8388,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>2.111</v>
+        <v>0.734</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>2.265</v>
+        <v>0.656</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8404,28 +8404,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E177" s="17" t="n">
-        <v>-0.005</v>
+        <v>1.33</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>528600</v>
+        <v>548800</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.67</v>
+        <v>0.27</v>
       </c>
       <c r="H177" t="n">
-        <v>30.83</v>
+        <v>37.04</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>2.027</v>
+        <v>1.359</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>2.075</v>
+        <v>1.341</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8449,28 +8449,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>0</v>
+        <v>0.76</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>0.027</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>524400</v>
+        <v>538300</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="H178" t="n">
-        <v>41.25</v>
+        <v>47.94</v>
       </c>
       <c r="I178" s="13" t="inlineStr">
         <is>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>2.545</v>
+        <v>0.771</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>2.669</v>
+        <v>0.771</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8494,39 +8494,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E179" s="17" t="n">
-        <v>-0.0076</v>
+        <v>2.05</v>
+      </c>
+      <c r="E179" s="16" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>522400</v>
+        <v>537200</v>
       </c>
       <c r="G179" s="12" t="n">
         <v>0.44</v>
       </c>
       <c r="H179" t="n">
-        <v>73.12</v>
-      </c>
-      <c r="I179" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.57</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>0.593</v>
+        <v>2.111</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>0.535</v>
+        <v>2.265</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8539,39 +8539,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E180" s="17" t="n">
-        <v>-0.0097</v>
+        <v>2.48</v>
+      </c>
+      <c r="E180" s="15" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>520000</v>
+        <v>528000</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.75</v>
+        <v>0.18</v>
       </c>
       <c r="H180" t="n">
-        <v>57.62</v>
-      </c>
-      <c r="I180" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.41</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>1.008</v>
+        <v>2.543</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.986</v>
+        <v>2.669</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8593,19 +8593,19 @@
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E181" s="17" t="n">
-        <v>-0.0234</v>
+        <v>1.26</v>
+      </c>
+      <c r="E181" s="15" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>513200</v>
+        <v>527600</v>
       </c>
       <c r="G181" s="12" t="n">
         <v>0.27</v>
       </c>
       <c r="H181" t="n">
-        <v>21.18</v>
+        <v>21.98</v>
       </c>
       <c r="I181" s="13" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>1.377</v>
+        <v>1.378</v>
       </c>
       <c r="K181" s="9" t="n">
         <v>1.454</v>
@@ -8629,39 +8629,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E182" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.66</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>512500</v>
+        <v>526300</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.08</v>
+        <v>0.44</v>
       </c>
       <c r="H182" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I182" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.22</v>
+      </c>
+      <c r="I182" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>1.107</v>
+        <v>0.593</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>0.903</v>
+        <v>0.535</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8674,45 +8674,135 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>2.45</v>
+        <v>1.02</v>
       </c>
       <c r="E183" s="15" t="n">
-        <v>0.0381</v>
+        <v>-0.0097</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>510700</v>
+        <v>520000</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.28</v>
+        <v>0.75</v>
       </c>
       <c r="H183" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="I183" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.62</v>
+      </c>
+      <c r="I183" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>2.497</v>
+        <v>1.008</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>2.266</v>
+        <v>0.986</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E184" s="16" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>514500</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H184" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>2.266</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>514500</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H185" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M183"/>
+  <autoFilter ref="A1:M185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,8 +96,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,86 +557,103 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>10042400</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 59.82未超买，现价0.47高于50日均线0.417，技术面信号可靠性偏正面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>0262</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>SUNVIEW</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.012</v>
       </c>
-      <c r="F2" s="5" t="n">
-        <v>6797400</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H2" s="2" t="n">
+      <c r="F3" s="5" t="n">
+        <v>8007400</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>58.95</v>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.396</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号，现价0.42高于50日均线0.38，RSI 58.95处中性偏上区间，未超买，信号技术面尚属可靠。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0478</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nwe Resources Group Bhd</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>60388400</v>
-      </c>
-      <c r="G3" s="12" t="n"/>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 58.95未超买，现价高于50日均线约10.5%，技术面信号较为可靠。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -646,40 +663,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>Nwe Resources Group Bhd</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.195</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>36971400</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.84</v>
-      </c>
+        <v>94794700</v>
+      </c>
+      <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.297</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
     </row>
@@ -700,19 +708,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0.1429</v>
+        <v>0.17</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.2143</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>35914000</v>
+        <v>48328000</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="H5" t="n">
-        <v>52.3</v>
+        <v>56.15</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -720,7 +728,7 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.142</v>
@@ -736,39 +744,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-0.0106</v>
+        <v>0.19</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>32947900</v>
+        <v>41227700</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="H6" t="n">
-        <v>79.34</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.93</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.4</v>
+        <v>0.214</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.294</v>
+        <v>0.233</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -781,28 +789,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.145</v>
+        <v>0.055</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>32396100</v>
+        <v>41097600</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>2.39</v>
+        <v>0.11</v>
       </c>
       <c r="H7" t="n">
-        <v>31.27</v>
+        <v>24.46</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -810,10 +818,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.154</v>
+        <v>0.111</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.184</v>
+        <v>0.297</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -826,39 +834,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.075</v>
+        <v>0.47</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>30158500</v>
+        <v>37416500</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="H8" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.92</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.213</v>
+        <v>0.4</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.233</v>
+        <v>0.294</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -871,39 +879,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.011</v>
+        <v>0.345</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>28734100</v>
+        <v>35207000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H9" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.47</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.843</v>
+        <v>0.311</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.748</v>
+        <v>0.261</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -916,28 +924,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0.0455</v>
+        <v>0.145</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>26985800</v>
+        <v>32444900</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.33</v>
+        <v>2.39</v>
       </c>
       <c r="H10" t="n">
-        <v>67.47</v>
+        <v>31.27</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -945,10 +953,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.311</v>
+        <v>0.154</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.261</v>
+        <v>0.184</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,28 +969,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.2</v>
+        <v>0.92</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.011</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>21137900</v>
+        <v>31646200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>3.99</v>
+        <v>0.44</v>
       </c>
       <c r="H11" t="n">
-        <v>64.81</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
@@ -990,10 +998,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.048</v>
+        <v>0.843</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.047</v>
+        <v>0.748</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,19 +1023,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.0278</v>
+        <v>0.18</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>20003900</v>
+        <v>25018400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="H12" t="n">
-        <v>41.19</v>
+        <v>44.11</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1051,39 +1059,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.15</v>
+        <v>0.055</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>-0.0625</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>18816400</v>
+        <v>23094100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.53</v>
+        <v>4.36</v>
       </c>
       <c r="H13" t="n">
-        <v>40.02</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.49</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.155</v>
+        <v>0.048</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.156</v>
+        <v>0.047</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1104,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.715</v>
+        <v>0.155</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.0142</v>
+        <v>-0.0313</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>14201700</v>
+        <v>22300200</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H14" t="n">
-        <v>81.19</v>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.42</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.635</v>
+        <v>0.155</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.543</v>
+        <v>0.156</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,28 +1149,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.036</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>13376300</v>
+        <v>16152700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H15" t="n">
-        <v>47.41</v>
+        <v>52.07</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1170,10 +1178,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.308</v>
+        <v>0.572</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.301</v>
+        <v>0.544</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1201,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12589400</v>
+        <v>15449000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="H16" t="n">
         <v>55.6</v>
@@ -1231,28 +1239,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.0236</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>12160900</v>
+        <v>14540100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.79</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
-        <v>46.5</v>
+        <v>63.96</v>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
@@ -1260,10 +1268,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.774</v>
+        <v>1.214</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.776</v>
+        <v>1.197</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,39 +1284,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0.036</v>
+        <v>0.715</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0142</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>12104700</v>
+        <v>14427000</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H18" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.19</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.572</v>
+        <v>0.635</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.544</v>
+        <v>0.543</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1321,39 +1329,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0.0157</v>
+        <v>0.305</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>12066300</v>
+        <v>13721300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1.89</v>
+        <v>0.71</v>
       </c>
       <c r="H19" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.41</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.213</v>
+        <v>0.308</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1.197</v>
+        <v>0.301</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1381,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>10562700</v>
+        <v>13146600</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H20" t="n">
         <v>46.09</v>
@@ -1411,39 +1419,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0.0361</v>
+        <v>0.77</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9709100</v>
+        <v>13081300</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.26</v>
+        <v>0.85</v>
       </c>
       <c r="H21" t="n">
-        <v>37.98</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.5</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.467</v>
+        <v>0.774</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.48</v>
+        <v>0.776</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,39 +1464,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>-0.0667</v>
+        <v>0.0361</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9384500</v>
+        <v>11923200</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>9.210000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="H22" t="n">
-        <v>51.64</v>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.98</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.467</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,39 +1509,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.45</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.0112</v>
+        <v>-0.0667</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9153900</v>
+        <v>9384500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.44</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>59.14</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.64</v>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.427</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.375</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1546,33 +1554,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0.0204</v>
+        <v>0.445</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>8423900</v>
+        <v>9344000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
+      </c>
+      <c r="H24" t="n">
+        <v>58.07</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+      <c r="J24" s="9" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.375</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1584,28 +1599,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0.0505</v>
+        <v>0.505</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.08599999999999999</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7560200</v>
+        <v>9324000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.27</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>60.8</v>
+        <v>78.48</v>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
@@ -1613,10 +1628,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.95</v>
+        <v>0.429</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.766</v>
+        <v>0.434</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,39 +1644,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TALAMT</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>4.71</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7550100</v>
+        <v>9270200</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>5.54</v>
+        <v>0.45</v>
       </c>
       <c r="H26" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.91</v>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.078</v>
+        <v>4.727</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.081</v>
+        <v>4.832</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1689,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0.0849</v>
+        <v>2.06</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0404</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7439000</v>
+        <v>8440300</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H27" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.89</v>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.63</v>
+        <v>1.949</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.619</v>
+        <v>1.766</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,40 +1734,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>7419800</v>
+        <v>8425000</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H28" t="n">
-        <v>48.53</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>4.729</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <v>4.833</v>
-      </c>
+        <v>0.37</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1775,14 +1783,14 @@
       <c r="D29" s="9" t="n">
         <v>0.115</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="15" t="n">
         <v>0.0455</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>7361000</v>
+        <v>8392400</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="H29" t="n">
         <v>34.73</v>
@@ -1809,28 +1817,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>-0.013</v>
+        <v>0.39</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>7270100</v>
+        <v>8339900</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H30" t="n">
-        <v>24.32</v>
+        <v>27.8</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1838,10 +1846,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.394</v>
+        <v>0.499</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.405</v>
+        <v>0.601</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,28 +1862,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>7.14</v>
+        <v>2.45</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>-0.0014</v>
+        <v>0.0699</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7221500</v>
+        <v>8305300</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.43</v>
+        <v>1.61</v>
       </c>
       <c r="H31" t="n">
-        <v>32.57</v>
+        <v>36.32</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1883,10 +1891,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>7.439</v>
+        <v>2.73</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>7.659</v>
+        <v>2.869</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1907,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0.0524</v>
+        <v>7.31</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0014</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7161300</v>
+        <v>8278800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.39</v>
+        <v>0.8</v>
       </c>
       <c r="H32" t="n">
-        <v>34.19</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.43</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.726</v>
+        <v>7.427</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.868</v>
+        <v>7.893</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,39 +1952,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.51</v>
+        <v>7.14</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>0.0968</v>
+        <v>-0.0014</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6935800</v>
+        <v>7936200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>2.98</v>
+        <v>0.47</v>
       </c>
       <c r="H33" t="n">
-        <v>79.20999999999999</v>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.57</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.43</v>
+        <v>7.439</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.435</v>
+        <v>7.659</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,28 +1997,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>0.0843</v>
+        <v>0.575</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.0849</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>6578700</v>
+        <v>7739600</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="H34" t="n">
-        <v>56.35</v>
+        <v>40.99</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2018,10 +2026,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.426</v>
+        <v>0.63</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.417</v>
+        <v>0.619</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2042,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>0.0219</v>
+        <v>-0.013</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6118700</v>
+        <v>7695300</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.47</v>
+        <v>0.78</v>
       </c>
       <c r="H35" t="n">
-        <v>59.76</v>
+        <v>24.32</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2071,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.856</v>
+        <v>0.394</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.599</v>
+        <v>0.405</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,39 +2087,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.115</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6095100</v>
+        <v>7689500</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.47</v>
+        <v>1.75</v>
       </c>
       <c r="H36" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.04000000000001</v>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.279</v>
+        <v>0.091</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,28 +2132,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>TALAMT</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.075</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>6017500</v>
+        <v>7550100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.33</v>
+        <v>5.54</v>
       </c>
       <c r="H37" t="n">
-        <v>46.99</v>
+        <v>44.56</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2153,10 +2161,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.629</v>
+        <v>0.078</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.56</v>
+        <v>0.081</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,40 +2177,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>7.31</v>
+        <v>0.105</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>0.0014</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5980800</v>
+        <v>7523700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H38" t="n">
-        <v>38.43</v>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>7.427</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>7.893</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
     </row>
@@ -2214,39 +2215,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AIZO</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0.1667</v>
+        <v>2.46</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5933100</v>
+        <v>7510100</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>3.91</v>
+        <v>0.65</v>
       </c>
       <c r="H39" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.17</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.034</v>
+        <v>2.449</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.036</v>
+        <v>2.399</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,28 +2260,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>-0.004099999999999999</v>
+        <v>4.46</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5876700</v>
+        <v>7221600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.51</v>
+        <v>0.89</v>
       </c>
       <c r="H40" t="n">
-        <v>51.72</v>
+        <v>36.71</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2288,10 +2289,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.448</v>
+        <v>4.589</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.399</v>
+        <v>4.64</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2319,10 +2320,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5819300</v>
+        <v>7142700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H41" t="n">
         <v>38.25</v>
@@ -2349,39 +2350,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0.0455</v>
+        <v>0.965</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.0266</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5814500</v>
+        <v>6750500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.33</v>
+        <v>0.79</v>
       </c>
       <c r="H42" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="I42" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.97</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.1</v>
+        <v>1.032</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.091</v>
+        <v>0.969</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,28 +2395,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0.0566</v>
+        <v>2.56</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5813800</v>
+        <v>6710100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.86</v>
+        <v>0.37</v>
       </c>
       <c r="H43" t="n">
-        <v>37.59</v>
+        <v>46.33</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2423,10 +2424,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.307</v>
+        <v>2.628</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.331</v>
+        <v>2.559</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2448,19 +2449,19 @@
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.215</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5761800</v>
+        <v>6331200</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="H44" t="n">
-        <v>86.73999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2480,39 +2481,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>-0.007900000000000001</v>
+        <v>5.3</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5405900</v>
+        <v>6319100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="H45" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.25</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.62</v>
+        <v>5.471</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.616</v>
+        <v>5.483</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2525,28 +2526,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>0.0019</v>
+        <v>0.71</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.1008</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5363600</v>
+        <v>6305300</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="H46" t="n">
-        <v>42.73</v>
+        <v>46.42</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2554,10 +2555,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>5.471</v>
+        <v>0.736</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>5.483</v>
+        <v>0.723</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2570,28 +2571,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5150300</v>
+        <v>6304600</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="H47" t="n">
-        <v>38.03</v>
+        <v>28.46</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2599,10 +2600,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.03</v>
+        <v>0.229</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.968</v>
+        <v>0.279</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2615,28 +2616,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.0286</v>
+        <v>0.925</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5031600</v>
+        <v>6284700</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="H48" t="n">
-        <v>57.17</v>
+        <v>59.23</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2644,10 +2645,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.175</v>
+        <v>0.855</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.181</v>
+        <v>0.599</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2660,39 +2661,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>AIZO</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>4.46</v>
+        <v>0.035</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>-0.0022</v>
+        <v>0.1667</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5006300</v>
+        <v>5933100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.61</v>
+        <v>3.91</v>
       </c>
       <c r="H49" t="n">
-        <v>36.71</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.49</v>
+      </c>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>4.589</v>
+        <v>0.034</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>4.64</v>
+        <v>0.036</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2705,39 +2706,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0.0417</v>
+        <v>0.275</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.0377</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4971900</v>
+        <v>5840600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.37</v>
+        <v>0.87</v>
       </c>
       <c r="H50" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.22</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.123</v>
+        <v>0.307</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.124</v>
+        <v>0.331</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2750,39 +2751,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.39</v>
+        <v>0.385</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>-0.025</v>
+        <v>0.0267</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4946200</v>
+        <v>5755500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="H51" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.499</v>
+        <v>0.373</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.601</v>
+        <v>0.37</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2795,39 +2796,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0.04</v>
+        <v>2.04</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4778900</v>
+        <v>5594700</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>35.76</v>
+        <v>0.48</v>
       </c>
       <c r="H52" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.35</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.127</v>
+        <v>2.126</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.129</v>
+        <v>2.235</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2840,28 +2841,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>0.0149</v>
+        <v>0.845</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0368</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4726300</v>
+        <v>5569800</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.4</v>
+        <v>1.58</v>
       </c>
       <c r="H53" t="n">
-        <v>37.82</v>
+        <v>54.74</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2869,10 +2870,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.127</v>
+        <v>0.827</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.235</v>
+        <v>0.789</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2885,33 +2886,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.63</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4688500</v>
+        <v>5405900</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J54" s="9" t="n"/>
-      <c r="K54" s="9" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0.616</v>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
     </row>
@@ -2923,28 +2931,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.125</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4610500</v>
+        <v>5382800</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.64</v>
+        <v>40.28</v>
       </c>
       <c r="H55" t="n">
-        <v>60.97</v>
+        <v>43.51</v>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
@@ -2952,10 +2960,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.372</v>
+        <v>0.127</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.37</v>
+        <v>0.129</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2968,28 +2976,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.02</v>
+        <v>0.445</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>-0.0049</v>
+        <v>0.0114</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4590800</v>
+        <v>5373600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1.4</v>
+        <v>0.28</v>
       </c>
       <c r="H56" t="n">
-        <v>44.19</v>
+        <v>27.55</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -2997,10 +3005,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.041</v>
+        <v>0.495</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.068</v>
+        <v>0.654</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3013,28 +3021,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>5.7</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4466800</v>
+        <v>5118200</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.23</v>
+        <v>0.66</v>
       </c>
       <c r="H57" t="n">
-        <v>25.69</v>
+        <v>36.46</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3042,10 +3050,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.495</v>
+        <v>5.861</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.653</v>
+        <v>6.146</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3058,28 +3066,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.61</v>
+        <v>2.02</v>
       </c>
       <c r="E58" s="16" t="n">
-        <v>0.08929999999999999</v>
+        <v>-0.0049</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4244500</v>
+        <v>5101200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.72</v>
+        <v>1.56</v>
       </c>
       <c r="H58" t="n">
-        <v>58.07</v>
+        <v>44.19</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3087,10 +3095,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.573</v>
+        <v>2.041</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.476</v>
+        <v>2.068</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3103,28 +3111,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0.0075</v>
+        <v>0.175</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4080400</v>
+        <v>5041600</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.33</v>
+        <v>0.9</v>
       </c>
       <c r="H59" t="n">
-        <v>44.61</v>
+        <v>48.63</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3132,10 +3140,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>2.746</v>
+        <v>0.174</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.743</v>
+        <v>0.181</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3148,28 +3156,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.12</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4058800</v>
+        <v>4971900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.27</v>
+        <v>1.37</v>
       </c>
       <c r="H60" t="n">
-        <v>41.05</v>
+        <v>44.15</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3177,10 +3185,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.733</v>
+        <v>0.122</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.722</v>
+        <v>0.124</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3193,28 +3201,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0.0184</v>
+        <v>0.475</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.044</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>4034900</v>
+        <v>4898400</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.15</v>
+        <v>0.48</v>
       </c>
       <c r="H61" t="n">
-        <v>52.36</v>
+        <v>44.98</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3222,10 +3230,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.826</v>
+        <v>0.509</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.789</v>
+        <v>0.465</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3238,28 +3246,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0.008</v>
+        <v>9.98</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3984500</v>
+        <v>4862700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.17</v>
+        <v>0.38</v>
       </c>
       <c r="H62" t="n">
-        <v>75.14</v>
+        <v>47</v>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
@@ -3267,10 +3275,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.619</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.608</v>
+        <v>10.129</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3283,39 +3291,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0</v>
+        <v>4.81</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3964600</v>
+        <v>4772000</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.71</v>
+        <v>0.19</v>
       </c>
       <c r="H63" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I63" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.25</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.175</v>
+        <v>4.881</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.195</v>
+        <v>4.742</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3328,39 +3336,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>0.0105</v>
+        <v>0.18</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3909000</v>
+        <v>4726500</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.16</v>
+        <v>0.87</v>
       </c>
       <c r="H64" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.97</v>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>4.88</v>
+        <v>0.164</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>4.741</v>
+        <v>0.165</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3373,28 +3381,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.29</v>
+        <v>2.69</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>-0.0169</v>
+        <v>0.0113</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3860900</v>
+        <v>4639900</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1.15</v>
+        <v>0.37</v>
       </c>
       <c r="H65" t="n">
-        <v>25.78</v>
+        <v>45.46</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3402,10 +3410,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.295</v>
+        <v>2.747</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.295</v>
+        <v>2.743</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3418,28 +3426,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.09820000000000001</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3791300</v>
+        <v>4395300</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="H66" t="n">
-        <v>45.85</v>
+        <v>58.6</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3447,10 +3455,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.768</v>
+        <v>0.574</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.771</v>
+        <v>0.477</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3463,39 +3471,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.026</v>
+        <v>-0.0199</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3780300</v>
+        <v>4216100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.43</v>
+        <v>0.52</v>
       </c>
       <c r="H67" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.48</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.744</v>
+        <v>0.767</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.707</v>
+        <v>0.771</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3508,39 +3516,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>0.033</v>
+        <v>1.96</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3776200</v>
+        <v>4215800</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.37</v>
+        <v>0.7</v>
       </c>
       <c r="H68" t="n">
-        <v>44.03</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.29</v>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.509</v>
+        <v>1.927</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.465</v>
+        <v>1.951</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3553,28 +3561,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>0.0051</v>
+        <v>0.165</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3662600</v>
+        <v>4091600</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="H69" t="n">
-        <v>54.29</v>
+        <v>34.49</v>
       </c>
       <c r="I69" s="17" t="inlineStr">
         <is>
@@ -3582,10 +3590,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.927</v>
+        <v>0.175</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.951</v>
+        <v>0.195</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3598,39 +3606,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>0.0071</v>
+        <v>0.63</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.008</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3661700</v>
+        <v>3984500</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.47</v>
+        <v>1.17</v>
       </c>
       <c r="H70" t="n">
-        <v>34.97</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.14</v>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>5.86</v>
+        <v>0.619</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>6.145</v>
+        <v>0.608</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3643,39 +3651,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0.0377</v>
+        <v>0.79</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.026</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3324500</v>
+        <v>3944500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.55</v>
+        <v>1.49</v>
       </c>
       <c r="H71" t="n">
-        <v>25.26</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.75</v>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.321</v>
+        <v>0.744</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.366</v>
+        <v>0.707</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3688,28 +3696,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.125</v>
+        <v>6.75</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3313200</v>
+        <v>3887200</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>2.21</v>
+        <v>0.93</v>
       </c>
       <c r="H72" t="n">
-        <v>41.39</v>
+        <v>49.35</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3717,10 +3725,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.129</v>
+        <v>6.755</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.13</v>
+        <v>6.82</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3733,28 +3741,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3269600</v>
+        <v>3860900</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.5</v>
+        <v>1.15</v>
       </c>
       <c r="H73" t="n">
-        <v>37.8</v>
+        <v>25.78</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3762,10 +3770,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>6.358</v>
+        <v>0.295</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>6.709</v>
+        <v>0.295</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3778,39 +3786,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>0.0052</v>
+        <v>0.275</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0377</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3214900</v>
+        <v>3843300</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="H74" t="n">
-        <v>67.08</v>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.26</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.321</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.883</v>
+        <v>0.366</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3823,28 +3831,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>0.004</v>
+        <v>3.32</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.0375</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3209600</v>
+        <v>3791600</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.25</v>
+        <v>0.63</v>
       </c>
       <c r="H75" t="n">
-        <v>47.64</v>
+        <v>44.01</v>
       </c>
       <c r="I75" s="17" t="inlineStr">
         <is>
@@ -3852,10 +3860,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>9.996</v>
+        <v>3.347</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>10.13</v>
+        <v>3.583</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3868,40 +3876,33 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>0.0571</v>
+        <v>0.77</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>3188300</v>
+        <v>3666200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H76" t="n">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="I76" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="K76" s="9" t="n">
-        <v>0.166</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n"/>
+      <c r="K76" s="9" t="n"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
     </row>
@@ -3924,14 +3925,14 @@
       <c r="D77" s="9" t="n">
         <v>5.11</v>
       </c>
-      <c r="E77" s="16" t="n">
+      <c r="E77" s="15" t="n">
         <v>0.0323</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3093700</v>
+        <v>3646100</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="H77" t="n">
         <v>53.94</v>
@@ -3958,28 +3959,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0.0164</v>
+        <v>0.765</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>3066500</v>
+        <v>3633200</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.36</v>
+        <v>2.74</v>
       </c>
       <c r="H78" t="n">
-        <v>41.31</v>
+        <v>60.12</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3987,10 +3988,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.286</v>
+        <v>0.749</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.315</v>
+        <v>0.721</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4003,28 +4004,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0</v>
+        <v>6.2</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>3014200</v>
+        <v>3614100</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>27.73</v>
+        <v>37.39</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4032,10 +4033,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.272</v>
+        <v>6.357</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.298</v>
+        <v>6.709</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4048,33 +4049,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.0261</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2833700</v>
+        <v>3602900</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J80" s="9" t="n"/>
-      <c r="K80" s="9" t="n"/>
+        <v>0.87</v>
+      </c>
+      <c r="H80" t="n">
+        <v>66.63</v>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>0.475</v>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
     </row>
@@ -4086,28 +4094,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>0.0361</v>
+        <v>1.24</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2825700</v>
+        <v>3544500</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.88</v>
+        <v>0.41</v>
       </c>
       <c r="H81" t="n">
-        <v>30.74</v>
+        <v>41.31</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4115,10 +4123,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.903</v>
+        <v>1.286</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.967</v>
+        <v>1.315</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4131,39 +4139,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.415</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.0641</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2778900</v>
+        <v>3507900</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="H82" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.93</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.523</v>
+        <v>0.394</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.475</v>
+        <v>0.363</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,39 +4184,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>0.0111</v>
+        <v>0.65</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0317</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2738600</v>
+        <v>3386300</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.37</v>
+        <v>1.64</v>
       </c>
       <c r="H83" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.35</v>
+      </c>
+      <c r="I83" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.489</v>
+        <v>0.638</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.548</v>
+        <v>0.625</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4221,28 +4229,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>-0.0129</v>
+        <v>1.42</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2691900</v>
+        <v>3345600</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="H84" t="n">
-        <v>58.16</v>
+        <v>21.29</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4250,10 +4258,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>3.691</v>
+        <v>1.644</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>3.104</v>
+        <v>1.918</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4266,28 +4274,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.125</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2669300</v>
+        <v>3313200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.23</v>
+        <v>2.21</v>
       </c>
       <c r="H85" t="n">
-        <v>21.29</v>
+        <v>41.39</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4295,10 +4303,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.644</v>
+        <v>0.129</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.918</v>
+        <v>0.13</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,28 +4319,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.29</v>
+        <v>3.8</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>0.0574</v>
+        <v>-0.0231</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2601700</v>
+        <v>3275300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="H86" t="n">
-        <v>51.48</v>
+        <v>56.81</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4340,10 +4348,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.282</v>
+        <v>3.687</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.231</v>
+        <v>3.103</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,39 +4364,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0.0089</v>
+        <v>0.85</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2584700</v>
+        <v>3259600</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="H87" t="n">
-        <v>51.76</v>
-      </c>
-      <c r="I87" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.29</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.902</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.967</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4401,39 +4409,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>0.02</v>
+        <v>0.97</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2554700</v>
+        <v>3228400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.39</v>
+        <v>0.54</v>
       </c>
       <c r="H88" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.02</v>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.27</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.29</v>
+        <v>0.883</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,39 +4454,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.63</v>
+        <v>0.26</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>-0.0061</v>
+        <v>0.0196</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2506200</v>
+        <v>3016200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H89" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="I89" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.79</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.625</v>
+        <v>0.273</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.686</v>
+        <v>0.298</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,28 +4499,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>0.0588</v>
+        <v>0.455</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2496000</v>
+        <v>3004000</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="H90" t="n">
-        <v>54.66</v>
+        <v>30.55</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4520,10 +4528,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.353</v>
+        <v>0.489</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.329</v>
+        <v>0.548</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,39 +4544,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>0.0709</v>
+        <v>0.715</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0672</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2489200</v>
+        <v>2932000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="H91" t="n">
-        <v>42.69</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.76</v>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.742</v>
+        <v>0.718</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.782</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,28 +4589,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>0.0154</v>
+        <v>0.355</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>0.0441</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2481400</v>
+        <v>2897100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="H92" t="n">
-        <v>45.85</v>
+        <v>52.77</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4610,10 +4618,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.343</v>
+        <v>0.353</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.335</v>
+        <v>0.328</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4637,14 +4645,14 @@
       <c r="D93" s="9" t="n">
         <v>0.82</v>
       </c>
-      <c r="E93" s="16" t="n">
+      <c r="E93" s="15" t="n">
         <v>0.0061</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2424400</v>
+        <v>2890600</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="H93" t="n">
         <v>66.97</v>
@@ -4671,28 +4679,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>0.0513</v>
+        <v>1.3</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.06559999999999999</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2372100</v>
+        <v>2873600</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H94" t="n">
-        <v>55.11</v>
+        <v>52.2</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4700,10 +4708,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.393</v>
+        <v>1.283</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.363</v>
+        <v>1.231</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,28 +4724,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.51</v>
+        <v>0.335</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>-0.0097</v>
+        <v>0.0308</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2358700</v>
+        <v>2832400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.87</v>
+        <v>0.28</v>
       </c>
       <c r="H95" t="n">
-        <v>31.45</v>
+        <v>47.84</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4745,10 +4753,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.537</v>
+        <v>0.343</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.335</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,39 +4769,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>0.0375</v>
+        <v>1.15</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.0268</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2263100</v>
+        <v>2803000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="H96" t="n">
-        <v>44.01</v>
-      </c>
-      <c r="I96" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.11</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>3.347</v>
+        <v>1.07</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>3.583</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,28 +4814,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>0.0268</v>
+        <v>6.82</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2216300</v>
+        <v>2780500</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.48</v>
+        <v>0.26</v>
       </c>
       <c r="H97" t="n">
-        <v>62.11</v>
+        <v>35.19</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4835,10 +4843,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.07</v>
+        <v>7.132</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,39 +4859,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0709</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2202600</v>
+        <v>2760000</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.28</v>
+        <v>0.52</v>
       </c>
       <c r="H98" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I98" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.69</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.222</v>
+        <v>0.742</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.31</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,28 +4904,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="E99" s="16" t="n">
-        <v>0.0276</v>
+        <v>1.64</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2158900</v>
+        <v>2749400</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.67</v>
+        <v>0.35</v>
       </c>
       <c r="H99" t="n">
-        <v>87.95</v>
+        <v>50.4</v>
       </c>
       <c r="I99" s="17" t="inlineStr">
         <is>
@@ -4925,10 +4933,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>2.917</v>
+        <v>1.626</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2.485</v>
+        <v>1.686</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,39 +4949,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.245</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.06519999999999999</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2050300</v>
+        <v>2730000</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.49</v>
+        <v>2.44</v>
       </c>
       <c r="H100" t="n">
-        <v>26.79</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.8</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.961</v>
+        <v>0.213</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.044</v>
+        <v>0.21</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,39 +4994,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="E101" s="16" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E101" s="15" t="n">
         <v>0.0089</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2028000</v>
+        <v>2594800</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.19</v>
+        <v>1.28</v>
       </c>
       <c r="H101" t="n">
-        <v>34.75</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.76</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>7.131</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>7.56</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,39 +5039,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.255</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0.02</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1979300</v>
+        <v>2554700</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>1.77</v>
+        <v>0.39</v>
       </c>
       <c r="H102" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.5</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.213</v>
+        <v>0.27</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,28 +5084,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.51</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1902700</v>
+        <v>2547900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H103" t="n">
-        <v>53.75</v>
+        <v>31.45</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5105,10 +5113,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.083</v>
+        <v>0.537</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.05</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5132,14 +5140,14 @@
       <c r="D104" s="9" t="n">
         <v>1.18</v>
       </c>
-      <c r="E104" s="15" t="n">
+      <c r="E104" s="16" t="n">
         <v>-0.0167</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1888900</v>
+        <v>2534400</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="H104" t="n">
         <v>21.3</v>
@@ -5166,39 +5174,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E105" s="16" t="n">
-        <v>0.013</v>
+        <v>1.17</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1874600</v>
+        <v>2470400</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>0.31</v>
       </c>
       <c r="H105" t="n">
-        <v>31.59</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.42</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.691</v>
+        <v>1.222</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.757</v>
+        <v>1.31</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5220,19 +5228,19 @@
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="E106" s="15" t="n">
-        <v>-0.0039</v>
+        <v>7.69</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1810700</v>
+        <v>2426700</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.63</v>
+        <v>0.85</v>
       </c>
       <c r="H106" t="n">
-        <v>37.97</v>
+        <v>39.05</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5240,7 +5248,7 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>7.822</v>
+        <v>7.824</v>
       </c>
       <c r="K106" s="9" t="n">
         <v>7.858</v>
@@ -5256,28 +5264,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>0.0444</v>
+        <v>6.65</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>0.0423</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1802400</v>
+        <v>2271800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>5.18</v>
+        <v>0.39</v>
       </c>
       <c r="H107" t="n">
-        <v>73.31</v>
+        <v>58.47</v>
       </c>
       <c r="I107" s="17" t="inlineStr">
         <is>
@@ -5285,10 +5293,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.226</v>
+        <v>6.24</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.225</v>
+        <v>5.952</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,39 +5309,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="E108" s="16" t="n">
-        <v>0.0408</v>
+        <v>0.92</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1736800</v>
+        <v>2212800</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.3</v>
+        <v>0.53</v>
       </c>
       <c r="H108" t="n">
-        <v>58.34</v>
-      </c>
-      <c r="I108" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.79</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>6.239</v>
+        <v>0.961</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>5.952</v>
+        <v>1.044</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,39 +5354,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0</v>
+        <v>3.34</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.0245</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1683500</v>
+        <v>2182400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H109" t="n">
-        <v>51.48</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>87.79000000000001</v>
+      </c>
+      <c r="I109" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.865</v>
+        <v>2.916</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.86</v>
+        <v>2.485</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,39 +5399,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.73</v>
+        <v>3.96</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>-0.018</v>
+        <v>0.0154</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1677500</v>
+        <v>2173200</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1.24</v>
+        <v>0.22</v>
       </c>
       <c r="H110" t="n">
-        <v>67.76000000000001</v>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.48</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.627</v>
+        <v>3.955</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.452</v>
+        <v>3.588</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,39 +5444,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.615</v>
+        <v>2.73</v>
       </c>
       <c r="E111" s="16" t="n">
-        <v>0.0165</v>
+        <v>-0.018</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1654100</v>
+        <v>2172400</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.19</v>
+        <v>1.61</v>
       </c>
       <c r="H111" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.666</v>
+        <v>2.627</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>2.452</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,28 +5489,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="E112" s="16" t="n">
-        <v>0.0154</v>
+        <v>0.865</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1652400</v>
+        <v>2133500</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.17</v>
+        <v>0.7</v>
       </c>
       <c r="H112" t="n">
-        <v>52.48</v>
+        <v>51.48</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5510,10 +5518,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>3.955</v>
+        <v>0.865</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>3.588</v>
+        <v>0.86</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,39 +5534,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E113" s="16" t="n">
-        <v>0.0373</v>
+        <v>1.57</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1629500</v>
+        <v>2129200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H113" t="n">
-        <v>38.04</v>
-      </c>
-      <c r="I113" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.14</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.716</v>
+        <v>1.692</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.781</v>
+        <v>1.757</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,28 +5579,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.62</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0.0248</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1582500</v>
+        <v>2069600</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H114" t="n">
-        <v>41.09</v>
+        <v>39.89</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5600,10 +5608,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.91</v>
+        <v>0.667</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.852</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,39 +5624,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>0</v>
+        <v>0.55</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.05769999999999999</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1543000</v>
+        <v>2046500</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H115" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I115" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.5</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>2.104</v>
+        <v>0.556</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.103</v>
+        <v>0.521</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,28 +5669,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0.0206</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1539400</v>
+        <v>1970400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.13</v>
+        <v>0.49</v>
       </c>
       <c r="H116" t="n">
-        <v>42.76</v>
+        <v>45.65</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -5690,10 +5698,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.287</v>
+        <v>1.033</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.283</v>
+        <v>0.955</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,38 +5714,40 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E117" s="16" t="n">
-        <v>0.0263</v>
+        <v>2.8</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1537100</v>
+        <v>1958300</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="H117" t="n">
-        <v>69.33</v>
-      </c>
-      <c r="I117" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.91</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="K117" s="9" t="n"/>
+        <v>2.794</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>2.677</v>
+      </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
     </row>
@@ -5749,28 +5759,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>6.76</v>
+        <v>1.1</v>
       </c>
       <c r="E118" s="16" t="n">
-        <v>0.0015</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1532900</v>
+        <v>1952800</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="H118" t="n">
-        <v>50.2</v>
+        <v>53.75</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5778,10 +5788,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>6.756</v>
+        <v>1.083</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>6.82</v>
+        <v>1.05</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5794,28 +5804,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>0.0159</v>
+        <v>0.39</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1512700</v>
+        <v>1925000</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.73</v>
+        <v>0.35</v>
       </c>
       <c r="H119" t="n">
-        <v>54.16</v>
+        <v>69.33</v>
       </c>
       <c r="I119" s="17" t="inlineStr">
         <is>
@@ -5823,11 +5833,9 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="K119" s="9" t="n">
-        <v>0.625</v>
-      </c>
+        <v>0.331</v>
+      </c>
+      <c r="K119" s="9" t="n"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
     </row>
@@ -5839,39 +5847,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E120" s="16" t="n">
-        <v>0.0481</v>
+        <v>0.23</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1456300</v>
+        <v>1856400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.27</v>
+        <v>5.34</v>
       </c>
       <c r="H120" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.31</v>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.555</v>
+        <v>0.225</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.52</v>
+        <v>0.225</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5884,28 +5892,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.7</v>
+        <v>0.845</v>
       </c>
       <c r="E121" s="15" t="n">
-        <v>-0.0058</v>
+        <v>0.0305</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1446700</v>
+        <v>1817800</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H121" t="n">
-        <v>34.28</v>
+        <v>41.84</v>
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
@@ -5913,10 +5921,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.761</v>
+        <v>0.91</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.874</v>
+        <v>0.853</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5929,39 +5937,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>2.06</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1433000</v>
+        <v>1817100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.17</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H122" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.44</v>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.5</v>
+        <v>2.078</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.521</v>
+        <v>2.083</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5974,39 +5982,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1414400</v>
+        <v>1771300</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>7.68</v>
+        <v>0.21</v>
       </c>
       <c r="H123" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="I123" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.66</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>2.078</v>
+        <v>0.501</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>2.083</v>
+        <v>0.521</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6019,28 +6027,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>0.0109</v>
+        <v>1.09</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.0187</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1407800</v>
+        <v>1738200</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.15</v>
+        <v>0.48</v>
       </c>
       <c r="H124" t="n">
-        <v>51.36</v>
+        <v>43.04</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6048,10 +6056,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>2.793</v>
+        <v>1.142</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>2.677</v>
+        <v>1.105</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6064,28 +6072,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E125" s="15" t="n">
-        <v>-0.0127</v>
+        <v>2.09</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1376400</v>
+        <v>1676100</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.4</v>
+        <v>0.11</v>
       </c>
       <c r="H125" t="n">
-        <v>59.79</v>
+        <v>47.56</v>
       </c>
       <c r="I125" s="17" t="inlineStr">
         <is>
@@ -6093,10 +6101,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>2.247</v>
+        <v>2.104</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>2.184</v>
+        <v>2.103</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6109,28 +6117,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>-0.0098</v>
+        <v>0.27</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1353500</v>
+        <v>1667200</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>1.17</v>
+        <v>0.14</v>
       </c>
       <c r="H126" t="n">
-        <v>37.58</v>
+        <v>42.76</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6138,10 +6146,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.043</v>
+        <v>0.287</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.134</v>
+        <v>0.283</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6154,28 +6162,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E127" s="16" t="n">
-        <v>0.0121</v>
+        <v>3.76</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.0301</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1326000</v>
+        <v>1613700</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="H127" t="n">
-        <v>33.02</v>
+        <v>48.2</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6183,10 +6191,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.883</v>
+        <v>3.824</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.945</v>
+        <v>3.711</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6199,28 +6207,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0</v>
+        <v>0.755</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0.0486</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1317400</v>
+        <v>1602700</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.77</v>
+        <v>0.26</v>
       </c>
       <c r="H128" t="n">
-        <v>36.07</v>
+        <v>54.29</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6228,10 +6236,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.251</v>
+        <v>0.742</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.272</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6244,28 +6252,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>0.0039</v>
+        <v>1.71</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1313200</v>
+        <v>1596700</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="H129" t="n">
-        <v>46.18</v>
+        <v>35.52</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6273,10 +6281,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>2.599</v>
+        <v>1.762</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>2.61</v>
+        <v>1.874</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6289,28 +6297,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E130" s="16" t="n">
-        <v>0.0132</v>
+        <v>1.03</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1297900</v>
+        <v>1574000</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="H130" t="n">
-        <v>60.12</v>
+        <v>36.03</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6318,10 +6326,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.749</v>
+        <v>1.075</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.721</v>
+        <v>1.126</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6334,39 +6342,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E131" s="16" t="n">
-        <v>0.028</v>
+        <v>0.67</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0.0229</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1284400</v>
+        <v>1538200</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>44.65</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.73</v>
+      </c>
+      <c r="I131" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.143</v>
+        <v>0.649</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.105</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6379,39 +6387,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>0</v>
+        <v>7.51</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.004</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1282900</v>
+        <v>1537300</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.19</v>
+        <v>0.61</v>
       </c>
       <c r="H132" t="n">
-        <v>53.66</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.44</v>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.173</v>
+        <v>7.562</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.143</v>
+        <v>7.745</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6424,39 +6432,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.66</v>
+        <v>2.34</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>0.0394</v>
+        <v>-0.0127</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1275800</v>
+        <v>1524500</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>1.83</v>
+        <v>0.44</v>
       </c>
       <c r="H133" t="n">
-        <v>65.76000000000001</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.79</v>
+      </c>
+      <c r="I133" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.623</v>
+        <v>2.247</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.609</v>
+        <v>2.184</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6469,39 +6477,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="E134" s="16" t="n">
-        <v>0.0053</v>
+        <v>0.835</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1270300</v>
+        <v>1506500</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="H134" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="I134" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.02</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>7.563</v>
+        <v>0.883</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>7.745</v>
+        <v>0.945</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6514,39 +6522,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>1.97</v>
+        <v>4.41</v>
       </c>
       <c r="E135" s="16" t="n">
-        <v>0.0314</v>
+        <v>-0.0178</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1208300</v>
+        <v>1477900</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.46</v>
+        <v>0.29</v>
       </c>
       <c r="H135" t="n">
-        <v>44.65</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.9</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>2.082</v>
+        <v>4.373</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.993</v>
+        <v>4.431</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6559,28 +6567,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="E136" s="16" t="n">
-        <v>0.0206</v>
+        <v>-0.0196</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1197800</v>
+        <v>1473000</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.3</v>
+        <v>1.28</v>
       </c>
       <c r="H136" t="n">
-        <v>45.65</v>
+        <v>35.9</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6588,10 +6596,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.033</v>
+        <v>1.042</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.955</v>
+        <v>1.134</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6604,39 +6612,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0</v>
+        <v>0.805</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0.0387</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1189800</v>
+        <v>1423400</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="H137" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="I137" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.7</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>7.91</v>
+        <v>0.912</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>7.954</v>
+        <v>1.063</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6649,28 +6657,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="E138" s="16" t="n">
-        <v>0.0247</v>
+        <v>0.41</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1187800</v>
+        <v>1420300</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.38</v>
+        <v>0.15</v>
       </c>
       <c r="H138" t="n">
-        <v>47.33</v>
+        <v>42.99</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6678,10 +6686,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>3.822</v>
+        <v>0.432</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>3.711</v>
+        <v>0.437</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6694,28 +6702,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>HOCKSOON</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>10.64</v>
+        <v>0.215</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>0.033</v>
+        <v>-0.0851</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1167200</v>
+        <v>1411100</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.34</v>
+        <v>2.17</v>
       </c>
       <c r="H139" t="n">
-        <v>56.81</v>
+        <v>31.36</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -6723,10 +6731,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>10.426</v>
+        <v>0.238</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>9.805999999999999</v>
+        <v>0.276</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6739,28 +6747,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>0.0123</v>
+        <v>2.57</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1166300</v>
+        <v>1387700</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H140" t="n">
-        <v>42.99</v>
+        <v>47.18</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -6768,10 +6776,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.432</v>
+        <v>2.6</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.437</v>
+        <v>2.61</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6784,28 +6792,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>0.0109</v>
+        <v>10.64</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>0.033</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1165500</v>
+        <v>1384100</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="H141" t="n">
-        <v>40.89</v>
+        <v>56.81</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6813,10 +6821,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>2.87</v>
+        <v>10.426</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>3.002</v>
+        <v>9.805999999999999</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6829,39 +6837,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>DESTINI</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>-0.0435</v>
+        <v>7.91</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1160800</v>
+        <v>1382400</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>4.57</v>
+        <v>0.4</v>
       </c>
       <c r="H142" t="n">
-        <v>40.95</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.59</v>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.228</v>
+        <v>7.91</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.243</v>
+        <v>7.954</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6874,28 +6882,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HOCKSOON</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.22</v>
+        <v>7.23</v>
       </c>
       <c r="E143" s="15" t="n">
-        <v>-0.0638</v>
+        <v>0.0388</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1155200</v>
+        <v>1364900</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>1.78</v>
+        <v>0.3</v>
       </c>
       <c r="H143" t="n">
-        <v>33.23</v>
+        <v>50.18</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -6903,10 +6911,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.238</v>
+        <v>7.306</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.276</v>
+        <v>6.915</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6919,39 +6927,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>ABMB</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>4.41</v>
+        <v>4.52</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>-0.0178</v>
+        <v>0.0022</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1139900</v>
+        <v>1345700</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.22</v>
+        <v>1.21</v>
       </c>
       <c r="H144" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I144" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.03</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>4.373</v>
+        <v>4.621</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>4.431</v>
+        <v>4.766</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6964,28 +6972,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="E145" s="16" t="n">
-        <v>0.0374</v>
+        <v>0.235</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1139800</v>
+        <v>1333200</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.25</v>
+        <v>0.78</v>
       </c>
       <c r="H145" t="n">
-        <v>49.98</v>
+        <v>36.07</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -6993,10 +7001,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>7.305</v>
+        <v>0.251</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>6.915</v>
+        <v>0.272</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7009,28 +7017,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="E146" s="16" t="n">
-        <v>0.0137</v>
+        <v>1.97</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0.0314</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1124500</v>
+        <v>1317600</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="H146" t="n">
-        <v>35.83</v>
+        <v>44.65</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7038,10 +7046,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.594</v>
+        <v>2.082</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.656</v>
+        <v>1.993</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7054,28 +7062,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>0</v>
+        <v>1.18</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1118200</v>
+        <v>1305200</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H147" t="n">
-        <v>56.16</v>
+        <v>52.11</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7083,10 +7091,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.266</v>
+        <v>1.173</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.257</v>
+        <v>1.143</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7099,28 +7107,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0.0394</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1086800</v>
+        <v>1288800</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.62</v>
+        <v>1.85</v>
       </c>
       <c r="H148" t="n">
-        <v>48.85</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7128,10 +7136,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.913</v>
+        <v>0.623</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.882</v>
+        <v>0.609</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7144,39 +7152,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>0</v>
+        <v>1.48</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1057400</v>
+        <v>1241100</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H149" t="n">
-        <v>40.21</v>
-      </c>
-      <c r="I149" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.83</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.356</v>
+        <v>1.594</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.383</v>
+        <v>1.656</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7189,39 +7197,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>980600</v>
+        <v>1224600</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.36</v>
+        <v>0.7</v>
       </c>
       <c r="H150" t="n">
-        <v>55.76</v>
-      </c>
-      <c r="I150" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.29</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.648</v>
+        <v>0.912</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7234,39 +7242,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.82</v>
+        <v>0.23</v>
       </c>
       <c r="E151" s="16" t="n">
-        <v>0.0061</v>
+        <v>-0.0213</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>972900</v>
+        <v>1206500</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.54</v>
+        <v>1.09</v>
       </c>
       <c r="H151" t="n">
-        <v>36.49</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.44</v>
+      </c>
+      <c r="I151" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.839</v>
+        <v>0.23</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.859</v>
+        <v>0.238</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7279,28 +7287,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E152" s="16" t="n">
-        <v>0.0407</v>
+        <v>2.76</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0.0073</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>972000</v>
+        <v>1181600</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="H152" t="n">
-        <v>35.5</v>
+        <v>40.07</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -7308,10 +7316,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.707</v>
+        <v>2.869</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.742</v>
+        <v>3.002</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7324,28 +7332,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>DESTINI</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.59</v>
+        <v>0.22</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>0.0442</v>
+        <v>-0.0435</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>966700</v>
+        <v>1160800</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.22</v>
+        <v>4.57</v>
       </c>
       <c r="H153" t="n">
-        <v>49.58</v>
+        <v>40.95</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7353,10 +7361,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.594</v>
+        <v>0.228</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.586</v>
+        <v>0.243</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7369,28 +7377,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>1.01</v>
+        <v>5.44</v>
       </c>
       <c r="E154" s="15" t="n">
-        <v>-0.0098</v>
+        <v>0.0362</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>929600</v>
+        <v>1150500</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="H154" t="n">
-        <v>31.48</v>
+        <v>49.61</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7398,10 +7406,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.073</v>
+        <v>5.483</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.126</v>
+        <v>5.384</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7414,39 +7422,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.795</v>
+        <v>0.27</v>
       </c>
       <c r="E155" s="16" t="n">
-        <v>0.0258</v>
+        <v>-0.0182</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>910000</v>
+        <v>1120400</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.4</v>
+        <v>1.02</v>
       </c>
       <c r="H155" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.32</v>
+      </c>
+      <c r="I155" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.911</v>
+        <v>0.272</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.063</v>
+        <v>0.276</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7459,39 +7467,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>1.14</v>
+        <v>0.35</v>
       </c>
       <c r="E156" s="15" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0145</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>898500</v>
+        <v>1120100</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.39</v>
+        <v>0.72</v>
       </c>
       <c r="H156" t="n">
-        <v>28.87</v>
-      </c>
-      <c r="I156" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.59</v>
+      </c>
+      <c r="I156" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>1.219</v>
+        <v>0.356</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.306</v>
+        <v>0.384</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7504,39 +7512,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E157" s="16" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.27</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>859700</v>
+        <v>1118200</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H157" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="I157" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.16</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>2.113</v>
+        <v>0.266</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>2.07</v>
+        <v>0.257</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7549,39 +7557,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>5.41</v>
+        <v>13.02</v>
       </c>
       <c r="E158" s="16" t="n">
-        <v>0.0305</v>
+        <v>-0.0031</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>808200</v>
+        <v>1089800</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="H158" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="I158" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.76</v>
+      </c>
+      <c r="I158" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>5.48</v>
+        <v>13.02</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>5.383</v>
+        <v>13.37</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7594,39 +7602,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="E159" s="16" t="n">
-        <v>0.0291</v>
+        <v>-0.0156</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>798900</v>
+        <v>1065100</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H159" t="n">
-        <v>47.11</v>
-      </c>
-      <c r="I159" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.98</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.083</v>
+        <v>1.378</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.096</v>
+        <v>1.454</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7639,28 +7647,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E160" s="16" t="n">
-        <v>0.0302</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>797000</v>
+        <v>1047200</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.32</v>
+        <v>0.58</v>
       </c>
       <c r="H160" t="n">
-        <v>44.15</v>
+        <v>33</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -7668,10 +7676,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>4.241</v>
+        <v>0.839</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>4.308</v>
+        <v>0.859</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7684,28 +7692,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E161" s="16" t="n">
-        <v>0.0024</v>
+        <v>8.460000000000001</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>795500</v>
+        <v>1043000</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="H161" t="n">
-        <v>36.16</v>
+        <v>45.94</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7713,10 +7721,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>4.374</v>
+        <v>8.592000000000001</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>4.681</v>
+        <v>8.68</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7729,28 +7737,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E162" s="16" t="n">
-        <v>0.0347</v>
+        <v>0.335</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>790100</v>
+        <v>1016100</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.13</v>
+        <v>1.35</v>
       </c>
       <c r="H162" t="n">
-        <v>52.81</v>
+        <v>52.15</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7758,10 +7766,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.741</v>
+        <v>0.334</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.324</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7774,28 +7782,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.98</v>
+        <v>0.64</v>
       </c>
       <c r="E163" s="15" t="n">
-        <v>-0.005</v>
+        <v>0.0407</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>758200</v>
+        <v>1012200</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.96</v>
+        <v>0.3</v>
       </c>
       <c r="H163" t="n">
-        <v>30.83</v>
+        <v>35.5</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7803,10 +7811,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>2.027</v>
+        <v>0.707</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>2.075</v>
+        <v>0.742</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7819,28 +7827,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="E164" s="16" t="n">
-        <v>0.009599999999999999</v>
+        <v>4.24</v>
+      </c>
+      <c r="E164" s="15" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>748000</v>
+        <v>1005400</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="H164" t="n">
-        <v>45.08</v>
+        <v>36.95</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -7848,10 +7856,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>8.589</v>
+        <v>4.375</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>8.68</v>
+        <v>4.681</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7864,39 +7872,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E165" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.33</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>745100</v>
+        <v>984300</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.67</v>
+        <v>0.48</v>
       </c>
       <c r="H165" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I165" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.04</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.633</v>
+        <v>1.359</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>0.631</v>
+        <v>1.341</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7909,28 +7917,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E166" s="16" t="n">
-        <v>0.0238</v>
+        <v>5.28</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>739900</v>
+        <v>969900</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.3</v>
+        <v>0.76</v>
       </c>
       <c r="H166" t="n">
-        <v>54.64</v>
+        <v>36.82</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7938,10 +7946,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>1.264</v>
+        <v>5.444</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.178</v>
+        <v>5.778</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7954,28 +7962,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>1.68</v>
+        <v>0.595</v>
       </c>
       <c r="E167" s="15" t="n">
-        <v>-0.0059</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>712100</v>
+        <v>967800</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.9</v>
+        <v>0.22</v>
       </c>
       <c r="H167" t="n">
-        <v>34.16</v>
+        <v>50.6</v>
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
@@ -7983,10 +7991,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>1.749</v>
+        <v>0.595</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>1.786</v>
+        <v>0.586</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7999,28 +8007,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E168" s="16" t="n">
-        <v>0.0172</v>
+        <v>1.15</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>704100</v>
+        <v>939400</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="H168" t="n">
-        <v>47.73</v>
+        <v>30.05</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8028,10 +8036,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>1.227</v>
+        <v>1.22</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.085</v>
+        <v>1.306</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8044,39 +8052,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="E169" s="10" t="n">
-        <v>0</v>
+        <v>4.14</v>
+      </c>
+      <c r="E169" s="15" t="n">
+        <v>0.04019999999999999</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>675900</v>
+        <v>924700</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="H169" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="I169" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.57</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>13.023</v>
+        <v>4.245</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>13.371</v>
+        <v>4.309</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8089,39 +8097,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E170" s="16" t="n">
-        <v>0.009599999999999999</v>
+        <v>1.07</v>
+      </c>
+      <c r="E170" s="15" t="n">
+        <v>0.0388</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>653000</v>
+        <v>890500</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="H170" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="I170" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.23</v>
+      </c>
+      <c r="I170" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>5.441</v>
+        <v>1.084</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>5.778</v>
+        <v>1.096</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8134,39 +8142,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0360</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SAG</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>0.625</v>
+        <v>0.76</v>
       </c>
       <c r="E171" s="15" t="n">
-        <v>-0.0234</v>
+        <v>0.0066</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>652200</v>
+        <v>888700</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>3.65</v>
+        <v>0.4</v>
       </c>
       <c r="H171" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="I171" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.75</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>0.637</v>
+        <v>0.735</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>0.644</v>
+        <v>0.656</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8179,39 +8187,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>0</v>
+        <v>2.13</v>
+      </c>
+      <c r="E172" s="15" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>639300</v>
+        <v>859700</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="H172" t="n">
-        <v>42.09</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.56</v>
+      </c>
+      <c r="I172" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>0.727</v>
+        <v>2.113</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>0.743</v>
+        <v>2.07</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8224,39 +8232,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SUPERLN</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>0.945</v>
+        <v>1.98</v>
       </c>
       <c r="E173" s="16" t="n">
-        <v>0.0161</v>
+        <v>-0.005</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>619700</v>
+        <v>855200</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="H173" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="I173" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.83</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>0.872</v>
+        <v>2.027</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>0.846</v>
+        <v>2.075</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8269,39 +8277,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>IGBREIT</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>0.88</v>
+        <v>2.77</v>
       </c>
       <c r="E174" s="15" t="n">
-        <v>-0.0112</v>
+        <v>0.0147</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>614000</v>
+        <v>803400</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.36</v>
+        <v>0.59</v>
       </c>
       <c r="H174" t="n">
-        <v>44.47</v>
-      </c>
-      <c r="I174" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.31</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>0.891</v>
+        <v>2.757</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>0.906</v>
+        <v>2.766</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8314,39 +8322,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>SUPERLN</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E175" s="16" t="n">
-        <v>0.0097</v>
+        <v>0.95</v>
+      </c>
+      <c r="E175" s="15" t="n">
+        <v>0.0215</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>594400</v>
+        <v>800100</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.39</v>
+        <v>1.96</v>
       </c>
       <c r="H175" t="n">
-        <v>51.31</v>
-      </c>
-      <c r="I175" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.05</v>
+      </c>
+      <c r="I175" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>3.163</v>
+        <v>0.872</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>2.911</v>
+        <v>0.846</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8359,28 +8367,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>0.75</v>
+        <v>1.3</v>
       </c>
       <c r="E176" s="15" t="n">
-        <v>-0.0066</v>
+        <v>0.0317</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>575500</v>
+        <v>799800</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="H176" t="n">
-        <v>59.2</v>
+        <v>55.45</v>
       </c>
       <c r="I176" s="13" t="inlineStr">
         <is>
@@ -8388,10 +8396,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>0.734</v>
+        <v>1.265</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>0.656</v>
+        <v>1.179</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8404,28 +8412,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E177" s="10" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E177" s="15" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>548800</v>
+        <v>770700</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="H177" t="n">
-        <v>37.04</v>
+        <v>49.82</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -8433,10 +8441,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>1.359</v>
+        <v>1.229</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.341</v>
+        <v>1.085</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8449,39 +8457,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E178" s="16" t="n">
-        <v>0.027</v>
+        <v>0.66</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>538300</v>
+        <v>762900</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.23</v>
+        <v>0.64</v>
       </c>
       <c r="H178" t="n">
-        <v>47.94</v>
-      </c>
-      <c r="I178" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.22</v>
+      </c>
+      <c r="I178" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.771</v>
+        <v>0.593</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.771</v>
+        <v>0.535</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8494,28 +8502,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>0.0049</v>
+        <v>-0.0178</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>537200</v>
+        <v>753900</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
       <c r="H179" t="n">
-        <v>42.57</v>
+        <v>31.92</v>
       </c>
       <c r="I179" s="13" t="inlineStr">
         <is>
@@ -8523,10 +8531,10 @@
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>2.111</v>
+        <v>1.747</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>2.265</v>
+        <v>1.785</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8539,39 +8547,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E180" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.635</v>
+      </c>
+      <c r="E180" s="16" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>528000</v>
+        <v>745100</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.18</v>
+        <v>0.67</v>
       </c>
       <c r="H180" t="n">
-        <v>39.41</v>
-      </c>
-      <c r="I180" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.02</v>
+      </c>
+      <c r="I180" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>2.543</v>
+        <v>0.633</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>2.669</v>
+        <v>0.631</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8584,28 +8592,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>1.26</v>
+        <v>3.12</v>
       </c>
       <c r="E181" s="15" t="n">
-        <v>-0.0156</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>527600</v>
+        <v>703600</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.27</v>
+        <v>0.46</v>
       </c>
       <c r="H181" t="n">
-        <v>21.98</v>
+        <v>50.58</v>
       </c>
       <c r="I181" s="13" t="inlineStr">
         <is>
@@ -8613,10 +8621,10 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>1.378</v>
+        <v>3.162</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>1.454</v>
+        <v>2.911</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8629,28 +8637,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.66</v>
+        <v>0.89</v>
       </c>
       <c r="E182" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>526300</v>
+        <v>666800</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="H182" t="n">
-        <v>75.22</v>
+        <v>47.71</v>
       </c>
       <c r="I182" s="17" t="inlineStr">
         <is>
@@ -8658,10 +8666,10 @@
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>0.593</v>
+        <v>0.892</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>0.535</v>
+        <v>0.906</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8674,28 +8682,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0360</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>SAG</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E183" s="15" t="n">
-        <v>-0.0097</v>
+        <v>0.625</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>520000</v>
+        <v>652200</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.75</v>
+        <v>3.65</v>
       </c>
       <c r="H183" t="n">
-        <v>57.62</v>
+        <v>43.91</v>
       </c>
       <c r="I183" s="17" t="inlineStr">
         <is>
@@ -8703,10 +8711,10 @@
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>1.008</v>
+        <v>0.637</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>0.986</v>
+        <v>0.644</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8719,28 +8727,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E184" s="16" t="n">
-        <v>0.0381</v>
+        <v>0.71</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>514500</v>
+        <v>651700</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="H184" t="n">
-        <v>49.94</v>
+        <v>42.09</v>
       </c>
       <c r="I184" s="13" t="inlineStr">
         <is>
@@ -8748,10 +8756,10 @@
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>2.497</v>
+        <v>0.727</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>2.266</v>
+        <v>0.743</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8764,28 +8772,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E185" s="10" t="n">
-        <v>0</v>
+        <v>1.39</v>
+      </c>
+      <c r="E185" s="15" t="n">
+        <v>0.0221</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>514500</v>
+        <v>643900</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.08</v>
+        <v>0.67</v>
       </c>
       <c r="H185" t="n">
-        <v>50.96</v>
+        <v>32.89</v>
       </c>
       <c r="I185" s="13" t="inlineStr">
         <is>
@@ -8793,16 +8801,556 @@
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>1.106</v>
+        <v>1.48</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>0.903</v>
+        <v>1.502</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5819</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>HLBANK</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>640100</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H186" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>21.638</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>22.094</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E187" s="16" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>619600</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H187" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>2.796</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E188" s="15" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>604300</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H188" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>594900</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H189" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>592000</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H190" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ITMAX</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E191" s="16" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>574600</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H191" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>4.574</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>4.486</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5325</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>WELLCHIP</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>572200</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H192" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="I192" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E193" s="15" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>567000</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H193" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E194" s="16" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>563400</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H194" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="n">
+        <v>5.526</v>
+      </c>
+      <c r="K194" s="9" t="n">
+        <v>5.779</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="14" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E195" s="15" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>543400</v>
+      </c>
+      <c r="G195" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H195" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J195" s="9" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="K195" s="9" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="14" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E196" s="16" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>520000</v>
+      </c>
+      <c r="G196" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H196" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="I196" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J196" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="K196" s="9" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="14" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E197" s="15" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G197" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H197" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="I197" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J197" s="9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K197" s="9" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M185"/>
+  <autoFilter ref="A1:M197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
+++ b/docs/downloads/2026-10-21/bursa-report-2026-10-21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-21" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-21'!$A$1:$M$205</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:M205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.47</v>
+        <v>0.455</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1325</v>
+        <v>0.0964</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>10042400</v>
+        <v>12007700</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.82</v>
+        <v>57.27</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.417</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 59.82未超买，现价0.47高于50日均线0.417，技术面信号可靠性偏正面。</t>
+          <t>SAR转多信号，RSI 57.27处中性区间未超买，现价高于50日均线约9%，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.42</v>
+        <v>0.425</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.012</v>
+        <v>0.0241</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>8007400</v>
+        <v>9141400</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>58.95</v>
+        <v>60.15</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.38</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 58.95未超买，现价高于50日均线约10.5%，技术面信号较为可靠。</t>
+          <t>SAR转多信号，RSI 60.15未超买，现价高于50日均线约11.8%，技术面信号较为可靠。</t>
         </is>
       </c>
     </row>
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.195</v>
+        <v>0.2</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>94794700</v>
+        <v>96262200</v>
       </c>
       <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.2143</v>
+        <v>0.1429</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>48328000</v>
+        <v>52763500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="H5" t="n">
-        <v>56.15</v>
+        <v>52.3</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.158</v>
+        <v>0.157</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.142</v>
@@ -759,10 +759,10 @@
         <v>-0.05</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>41227700</v>
+        <v>44445200</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="H6" t="n">
         <v>33.93</v>
@@ -798,27 +798,27 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>41097600</v>
+        <v>43859300</v>
       </c>
       <c r="G7" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
         <v>0.11</v>
-      </c>
-      <c r="H7" t="n">
-        <v>24.46</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0.111</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0.297</v>
@@ -834,28 +834,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.915</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>37416500</v>
+        <v>43728200</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.09</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>81.92</v>
+        <v>67.05</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.4</v>
+        <v>0.843</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.294</v>
+        <v>0.748</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -879,39 +879,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.47</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>35207000</v>
+        <v>40490400</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.42</v>
+        <v>1.18</v>
       </c>
       <c r="H9" t="n">
-        <v>67.47</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.92</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.311</v>
+        <v>0.4</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.261</v>
+        <v>0.294</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -924,28 +924,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>32444900</v>
+        <v>36169300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>2.39</v>
+        <v>0.44</v>
       </c>
       <c r="H10" t="n">
-        <v>31.27</v>
+        <v>66.27</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.154</v>
+        <v>0.31</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.184</v>
+        <v>0.261</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -969,39 +969,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.92</v>
+        <v>0.15</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.011</v>
+        <v>0.0345</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>31646200</v>
+        <v>32659300</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.44</v>
+        <v>2.41</v>
       </c>
       <c r="H11" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.84</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.843</v>
+        <v>0.155</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.748</v>
+        <v>0.184</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>25018400</v>
+        <v>25136700</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>1.17</v>
@@ -1059,39 +1059,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.1</v>
+        <v>0.155</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>23094100</v>
+        <v>23880200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>4.36</v>
+        <v>0.68</v>
       </c>
       <c r="H13" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.42</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.048</v>
+        <v>0.155</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.047</v>
+        <v>0.156</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1104,39 +1104,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>-0.0313</v>
+        <v>0.055</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.1</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>22300200</v>
+        <v>23094100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.63</v>
+        <v>4.36</v>
       </c>
       <c r="H14" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.49</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.155</v>
+        <v>0.048</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.156</v>
+        <v>0.047</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1149,39 +1149,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.575</v>
+        <v>0.715</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.036</v>
+        <v>0.0142</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>16152700</v>
+        <v>19530400</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="H15" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.19</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.572</v>
+        <v>0.635</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.544</v>
+        <v>0.543</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>15449000</v>
+        <v>17758700</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="H16" t="n">
         <v>55.6</v>
@@ -1239,39 +1239,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1.3</v>
+        <v>0.575</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.0236</v>
+        <v>0.036</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>14540100</v>
+        <v>17711500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.28</v>
+        <v>0.87</v>
       </c>
       <c r="H17" t="n">
-        <v>63.96</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.07</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.214</v>
+        <v>0.572</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1.197</v>
+        <v>0.544</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1284,28 +1284,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0142</v>
+        <v>0.77</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>14427000</v>
+        <v>15369200</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>81.19</v>
+        <v>46.5</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.635</v>
+        <v>0.774</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.543</v>
+        <v>0.776</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1329,39 +1329,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.305</v>
+        <v>0.865</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>13721300</v>
+        <v>15228800</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="H19" t="n">
-        <v>47.41</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.09</v>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.308</v>
+        <v>0.868</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.301</v>
+        <v>0.869</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1374,39 +1374,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.865</v>
+        <v>0.305</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>13146600</v>
+        <v>14938700</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="H20" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.41</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.868</v>
+        <v>0.308</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.869</v>
+        <v>0.301</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1419,28 +1419,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>1.31</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.0315</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>13081300</v>
+        <v>14589200</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.85</v>
+        <v>2.28</v>
       </c>
       <c r="H21" t="n">
-        <v>46.5</v>
+        <v>64.89</v>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.774</v>
+        <v>1.215</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.776</v>
+        <v>1.197</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.0361</v>
+        <v>0.0241</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>11923200</v>
+        <v>12672700</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H22" t="n">
-        <v>37.98</v>
+        <v>36.2</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1509,28 +1509,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.71</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-0.0667</v>
+        <v>-0.0042</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9384500</v>
+        <v>11591600</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>9.210000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H23" t="n">
-        <v>51.64</v>
+        <v>46.91</v>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>4.727</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>4.832</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1554,28 +1554,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0</v>
+        <v>4.45</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>9344000</v>
+        <v>11330300</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.45</v>
+        <v>1.39</v>
       </c>
       <c r="H24" t="n">
-        <v>58.07</v>
+        <v>36.09</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.427</v>
+        <v>4.588</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.375</v>
+        <v>4.64</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1608,19 +1608,19 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.505</v>
+        <v>0.49</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0538</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9324000</v>
+        <v>10601400</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="H25" t="n">
-        <v>78.48</v>
+        <v>75.95</v>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.429</v>
+        <v>0.428</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0.434</v>
@@ -1644,39 +1644,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>-0.0042</v>
+        <v>0.445</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9270200</v>
+        <v>10354800</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.07</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>4.727</v>
+        <v>0.427</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>4.832</v>
+        <v>0.375</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1689,39 +1689,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2.06</v>
+        <v>2.47</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>0.0404</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8440300</v>
+        <v>10095600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.3</v>
+        <v>0.87</v>
       </c>
       <c r="H27" t="n">
-        <v>59.89</v>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.44</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1.949</v>
+        <v>2.449</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1.766</v>
+        <v>2.4</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1734,25 +1734,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0204</v>
+        <v>0.105</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8425000</v>
+        <v>9462700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1772,39 +1772,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>-0.0667</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8392400</v>
+        <v>9384500</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.43</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>34.73</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.64</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.138</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.148</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1817,28 +1817,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>-0.025</v>
+        <v>2.43</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0611</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8339900</v>
+        <v>9305800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H30" t="n">
-        <v>27.8</v>
+        <v>35.27</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.499</v>
+        <v>2.728</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.601</v>
+        <v>2.868</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1862,39 +1862,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.45</v>
+        <v>7.33</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>0.0699</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>8305300</v>
+        <v>9302100</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.61</v>
+        <v>0.89</v>
       </c>
       <c r="H31" t="n">
-        <v>36.32</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.69</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.73</v>
+        <v>7.429</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.869</v>
+        <v>7.893</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1907,28 +1907,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>7.31</v>
+        <v>2.07</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>0.0014</v>
+        <v>0.0455</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>8278800</v>
+        <v>9012500</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.8</v>
+        <v>0.32</v>
       </c>
       <c r="H32" t="n">
-        <v>38.43</v>
+        <v>60.35</v>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>7.427</v>
+        <v>1.95</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>7.893</v>
+        <v>1.766</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1952,28 +1952,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>-0.0014</v>
+        <v>0.115</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7936200</v>
+        <v>8956900</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H33" t="n">
-        <v>32.57</v>
+        <v>34.73</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7.439</v>
+        <v>0.138</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>7.659</v>
+        <v>0.148</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1997,28 +1997,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>0.0849</v>
+        <v>0.39</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7739600</v>
+        <v>8816400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="H34" t="n">
-        <v>40.99</v>
+        <v>27.8</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.63</v>
+        <v>0.499</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.619</v>
+        <v>0.601</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2042,40 +2042,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>-0.013</v>
+        <v>0.25</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7695300</v>
+        <v>8815000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="H35" t="n">
-        <v>24.32</v>
+        <v>0.39</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J35" s="9" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>0.405</v>
-      </c>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
     </row>
@@ -2087,39 +2080,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.0455</v>
+        <v>7.14</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7689500</v>
+        <v>8646300</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.75</v>
+        <v>0.52</v>
       </c>
       <c r="H36" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.57</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.1</v>
+        <v>7.439</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.091</v>
+        <v>7.659</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2132,28 +2125,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TALAMT</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>0.57</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.0755</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7550100</v>
+        <v>8111500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>5.54</v>
+        <v>0.87</v>
       </c>
       <c r="H37" t="n">
-        <v>44.56</v>
+        <v>40.09</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2161,10 +2154,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.078</v>
+        <v>0.629</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.081</v>
+        <v>0.619</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2177,33 +2170,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.105</v>
+        <v>0.375</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.026</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>7523700</v>
+        <v>8040700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.21</v>
+        <v>0.82</v>
+      </c>
+      <c r="H38" t="n">
+        <v>21.23</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
+      <c r="J38" s="9" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>0.405</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
     </row>
@@ -2215,39 +2215,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>0.115</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>7510100</v>
+        <v>7964600</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.65</v>
+        <v>1.82</v>
       </c>
       <c r="H39" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.04000000000001</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>2.449</v>
+        <v>0.1</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>2.399</v>
+        <v>0.091</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2260,28 +2260,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>TALAMT</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>-0.0022</v>
+        <v>0.075</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>7221600</v>
+        <v>7550100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.89</v>
+        <v>5.54</v>
       </c>
       <c r="H40" t="n">
-        <v>36.71</v>
+        <v>44.56</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>4.589</v>
+        <v>0.078</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>4.64</v>
+        <v>0.081</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2305,28 +2305,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+        <v>0.965</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0266</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7142700</v>
+        <v>7469500</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="H41" t="n">
-        <v>38.25</v>
+        <v>41.97</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.292</v>
+        <v>1.032</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.28</v>
+        <v>0.969</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2350,28 +2350,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.965</v>
+        <v>2.57</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>0.0266</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>6750500</v>
+        <v>7311800</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.79</v>
+        <v>0.4</v>
       </c>
       <c r="H42" t="n">
-        <v>41.97</v>
+        <v>46.99</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>1.032</v>
+        <v>2.629</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.969</v>
+        <v>2.56</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2395,28 +2395,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0039</v>
+        <v>0.265</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>6710100</v>
+        <v>7308400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.37</v>
+        <v>0.73</v>
       </c>
       <c r="H43" t="n">
-        <v>46.33</v>
+        <v>38.25</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.628</v>
+        <v>0.292</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.559</v>
+        <v>0.28</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2440,36 +2440,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.0488</v>
+        <v>0.9</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>6331200</v>
+        <v>6902600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.66</v>
+        <v>1.65</v>
       </c>
       <c r="H44" t="n">
-        <v>87.13</v>
+        <v>57.54</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
+      <c r="J44" s="9" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.599</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2481,28 +2485,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>6319100</v>
+        <v>6825300</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="H45" t="n">
-        <v>42.25</v>
+        <v>37.82</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2510,10 +2514,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>5.471</v>
+        <v>2.127</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>5.483</v>
+        <v>2.235</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2535,19 +2539,19 @@
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.71</v>
+        <v>0.715</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>0.1008</v>
+        <v>0.1085</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>6305300</v>
+        <v>6661100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="H46" t="n">
-        <v>46.42</v>
+        <v>47.1</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2555,7 +2559,7 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.736</v>
+        <v>0.737</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0.723</v>
@@ -2571,39 +2575,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>6304600</v>
+        <v>6646900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="H47" t="n">
-        <v>28.46</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.97</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.229</v>
+        <v>0.372</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.279</v>
+        <v>0.37</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2616,39 +2620,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.925</v>
+        <v>0.6</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.0435</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>6284700</v>
+        <v>6645100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H48" t="n">
-        <v>59.23</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.86</v>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.855</v>
+        <v>0.524</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.599</v>
+        <v>0.475</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2661,39 +2665,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AIZO</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.1667</v>
+        <v>5.3</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5933100</v>
+        <v>6640900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>3.91</v>
+        <v>0.51</v>
       </c>
       <c r="H49" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="I49" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.25</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.034</v>
+        <v>5.471</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.036</v>
+        <v>5.483</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2706,28 +2710,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.275</v>
+        <v>0.21</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>0.0377</v>
+        <v>0.0244</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>5840600</v>
+        <v>6464800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.87</v>
+        <v>0.49</v>
       </c>
       <c r="H50" t="n">
-        <v>35.22</v>
+        <v>32.4</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2735,10 +2739,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.307</v>
+        <v>0.23</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.331</v>
+        <v>0.279</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2751,40 +2755,36 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.385</v>
+        <v>0.21</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>0.0267</v>
+        <v>0.0244</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>5755500</v>
+        <v>6444300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="H51" t="n">
-        <v>64.98</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J51" s="9" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="K51" s="9" t="n">
-        <v>0.37</v>
-      </c>
+        <v>86.73999999999999</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n"/>
+      <c r="K51" s="9" t="n"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
     </row>
@@ -2796,28 +2796,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>2.04</v>
+        <v>0.275</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0377</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>5594700</v>
+        <v>6263500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.48</v>
+        <v>0.93</v>
       </c>
       <c r="H52" t="n">
-        <v>36.35</v>
+        <v>35.22</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>2.126</v>
+        <v>0.307</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.235</v>
+        <v>0.331</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2841,39 +2841,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>0.0368</v>
+        <v>0.63</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>5569800</v>
+        <v>6259400</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.58</v>
+        <v>0.57</v>
       </c>
       <c r="H53" t="n">
-        <v>54.74</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I53" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.827</v>
+        <v>0.62</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.789</v>
+        <v>0.616</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2886,39 +2886,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.83</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>5405900</v>
+        <v>6111500</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.5</v>
+        <v>1.74</v>
       </c>
       <c r="H54" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.36</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.62</v>
+        <v>0.826</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.616</v>
+        <v>0.789</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2931,28 +2931,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>AIZO</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>0.04</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.3333</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>5382800</v>
+        <v>6033100</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>40.28</v>
+        <v>3.98</v>
       </c>
       <c r="H55" t="n">
-        <v>43.51</v>
+        <v>64.33</v>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.127</v>
+        <v>0.034</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.129</v>
+        <v>0.036</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2976,28 +2976,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.445</v>
+        <v>5.69</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>0.0114</v>
+        <v>0.0089</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>5373600</v>
+        <v>6025000</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.28</v>
+        <v>0.78</v>
       </c>
       <c r="H56" t="n">
-        <v>27.55</v>
+        <v>35.72</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.495</v>
+        <v>5.861</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.654</v>
+        <v>6.146</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3021,28 +3021,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>0.0106</v>
+        <v>0.015</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>5118200</v>
+        <v>5790500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="H57" t="n">
-        <v>36.46</v>
+        <v>46.29</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>5.861</v>
+        <v>2.748</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>6.146</v>
+        <v>2.743</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3066,39 +3066,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>-0.0049</v>
+        <v>1.95</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>5101200</v>
+        <v>5623600</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>1.56</v>
+        <v>0.93</v>
       </c>
       <c r="H58" t="n">
-        <v>44.19</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.97</v>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>2.041</v>
+        <v>1.926</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>2.068</v>
+        <v>1.951</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3111,28 +3111,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.175</v>
+        <v>0.44</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>5041600</v>
+        <v>5614300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.9</v>
+        <v>0.29</v>
       </c>
       <c r="H59" t="n">
-        <v>48.63</v>
+        <v>25.69</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.174</v>
+        <v>0.495</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.181</v>
+        <v>0.653</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3156,39 +3156,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.12</v>
+        <v>1.64</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4971900</v>
+        <v>5412800</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>44.15</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.4</v>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.122</v>
+        <v>1.626</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.124</v>
+        <v>1.686</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3201,39 +3201,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.044</v>
+        <v>0.125</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>4898400</v>
+        <v>5386800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.48</v>
+        <v>40.31</v>
       </c>
       <c r="H61" t="n">
-        <v>44.98</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.51</v>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.509</v>
+        <v>0.127</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.465</v>
+        <v>0.129</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         <v>0.003</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>4862700</v>
+        <v>5375700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="H62" t="n">
         <v>47</v>
@@ -3291,28 +3291,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>0.0126</v>
+        <v>2.02</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>4772000</v>
+        <v>5285800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.19</v>
+        <v>1.61</v>
       </c>
       <c r="H63" t="n">
-        <v>47.25</v>
+        <v>44.19</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>4.881</v>
+        <v>2.041</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>4.742</v>
+        <v>2.068</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3336,39 +3336,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.18</v>
+        <v>4.82</v>
       </c>
       <c r="E64" s="15" t="n">
-        <v>0.0286</v>
+        <v>0.0147</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>4726500</v>
+        <v>5210700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.87</v>
+        <v>0.21</v>
       </c>
       <c r="H64" t="n">
-        <v>62.97</v>
-      </c>
-      <c r="I64" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.8</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.164</v>
+        <v>4.882</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.165</v>
+        <v>4.742</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3381,39 +3381,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.69</v>
+        <v>3.33</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0.0113</v>
+        <v>0.0406</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>4639900</v>
+        <v>5182900</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.37</v>
+        <v>0.86</v>
       </c>
       <c r="H65" t="n">
-        <v>45.46</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.85</v>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.747</v>
+        <v>3.348</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.743</v>
+        <v>3.583</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3426,28 +3426,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.615</v>
+        <v>0.47</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.033</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>4395300</v>
+        <v>5167100</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="H66" t="n">
-        <v>58.6</v>
+        <v>44.03</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.574</v>
+        <v>0.509</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.477</v>
+        <v>0.465</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3471,28 +3471,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>-0.0199</v>
+        <v>0.175</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>4216100</v>
+        <v>5041600</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.52</v>
+        <v>0.9</v>
       </c>
       <c r="H67" t="n">
-        <v>42.48</v>
+        <v>48.63</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.767</v>
+        <v>0.174</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.771</v>
+        <v>0.181</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3516,39 +3516,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>0.0051</v>
+        <v>0.12</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>4215800</v>
+        <v>5021900</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.7</v>
+        <v>1.38</v>
       </c>
       <c r="H68" t="n">
-        <v>54.29</v>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.15</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.927</v>
+        <v>0.122</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.951</v>
+        <v>0.124</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>4091600</v>
+        <v>4968600</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="H69" t="n">
         <v>34.49</v>
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SYMLIFE</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>0.008</v>
+        <v>0.16</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3984500</v>
+        <v>4943000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1.17</v>
+        <v>6.89</v>
       </c>
       <c r="H70" t="n">
-        <v>75.14</v>
-      </c>
-      <c r="I70" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.06</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.619</v>
+        <v>0.168</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.608</v>
+        <v>0.174</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3651,28 +3651,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.79</v>
+        <v>0.18</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>0.026</v>
+        <v>0.0286</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3944500</v>
+        <v>4929700</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>1.49</v>
+        <v>0.91</v>
       </c>
       <c r="H71" t="n">
-        <v>59.75</v>
+        <v>62.97</v>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.744</v>
+        <v>0.164</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.707</v>
+        <v>0.165</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3705,19 +3705,19 @@
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>6.77</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3887200</v>
+        <v>4926700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="H72" t="n">
-        <v>49.35</v>
+        <v>51.02</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>6.755</v>
+        <v>6.757</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>6.82</v>
@@ -3741,28 +3741,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>-0.0169</v>
+        <v>0.61</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.08929999999999999</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3860900</v>
+        <v>4818500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>1.15</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>25.78</v>
+        <v>58.07</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.295</v>
+        <v>0.573</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.295</v>
+        <v>0.476</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3786,39 +3786,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.275</v>
+        <v>0.785</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>0.0377</v>
+        <v>0.0195</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3843300</v>
+        <v>4454600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.63</v>
+        <v>1.69</v>
       </c>
       <c r="H74" t="n">
-        <v>25.26</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.1</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.321</v>
+        <v>0.744</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.366</v>
+        <v>0.707</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3831,39 +3831,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>3.32</v>
+        <v>0.46</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>0.0375</v>
+        <v>0.0222</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3791600</v>
+        <v>4443900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H75" t="n">
-        <v>44.01</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.14</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>3.347</v>
+        <v>0.49</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>3.583</v>
+        <v>0.548</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3876,33 +3876,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
         <v>0.77</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0199</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>3666200</v>
+        <v>4331100</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.27</v>
+      </c>
+      <c r="H76" t="n">
+        <v>61.83</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J76" s="9" t="n"/>
-      <c r="K76" s="9" t="n"/>
+      <c r="J76" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.721</v>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
     </row>
@@ -3914,40 +3921,33 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>5.11</v>
+        <v>0.77</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>0.0323</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3646100</v>
+        <v>4305200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H77" t="n">
-        <v>53.94</v>
+        <v>0.08</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J77" s="9" t="n">
-        <v>5.054</v>
-      </c>
-      <c r="K77" s="9" t="n">
-        <v>5.049</v>
-      </c>
+      <c r="J77" s="9" t="n"/>
+      <c r="K77" s="9" t="n"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
     </row>
@@ -3959,28 +3959,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.765</v>
+        <v>5.11</v>
       </c>
       <c r="E78" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.0323</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>3633200</v>
+        <v>4275100</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2.74</v>
+        <v>1.05</v>
       </c>
       <c r="H78" t="n">
-        <v>60.12</v>
+        <v>53.94</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.749</v>
+        <v>5.054</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.721</v>
+        <v>5.049</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4004,28 +4004,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>6.2</v>
+        <v>0.745</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>-0.0016</v>
+        <v>-0.0132</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>3614100</v>
+        <v>4264300</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H79" t="n">
-        <v>37.39</v>
+        <v>43.54</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>6.357</v>
+        <v>0.768</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>6.709</v>
+        <v>0.771</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4049,39 +4049,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.59</v>
+        <v>1.24</v>
       </c>
       <c r="E80" s="15" t="n">
-        <v>0.0261</v>
+        <v>0.0164</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>3602900</v>
+        <v>4040500</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.87</v>
+        <v>0.47</v>
       </c>
       <c r="H80" t="n">
-        <v>66.63</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.31</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.523</v>
+        <v>1.286</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.475</v>
+        <v>1.315</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4094,39 +4094,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.24</v>
+        <v>0.63</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0.0164</v>
+        <v>0.008</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>3544500</v>
+        <v>3984500</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.41</v>
+        <v>1.17</v>
       </c>
       <c r="H81" t="n">
-        <v>41.31</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.14</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.286</v>
+        <v>0.619</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.315</v>
+        <v>0.608</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4139,28 +4139,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.415</v>
+        <v>0.85</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.0641</v>
+        <v>0.0241</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>3507900</v>
+        <v>3976700</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.59</v>
+        <v>1.24</v>
       </c>
       <c r="H82" t="n">
-        <v>55.93</v>
+        <v>26.29</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.394</v>
+        <v>0.902</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.363</v>
+        <v>0.967</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4184,39 +4184,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>0.0317</v>
+        <v>6.2</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>3386300</v>
+        <v>3971800</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1.64</v>
+        <v>0.61</v>
       </c>
       <c r="H83" t="n">
-        <v>59.35</v>
-      </c>
-      <c r="I83" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.39</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.638</v>
+        <v>6.357</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.625</v>
+        <v>6.709</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4229,28 +4229,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.255</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>3345600</v>
+        <v>3926300</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.29</v>
+        <v>0.49</v>
       </c>
       <c r="H84" t="n">
-        <v>21.29</v>
+        <v>27.73</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>1.644</v>
+        <v>0.272</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.918</v>
+        <v>0.298</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4274,28 +4274,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.125</v>
+        <v>1.71</v>
       </c>
       <c r="E85" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>3313200</v>
+        <v>3925000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>2.21</v>
+        <v>0.68</v>
       </c>
       <c r="H85" t="n">
-        <v>41.39</v>
+        <v>35.52</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.129</v>
+        <v>1.762</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.13</v>
+        <v>1.874</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4319,28 +4319,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>-0.0231</v>
+        <v>0.28</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0566</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>3275300</v>
+        <v>3913200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="H86" t="n">
-        <v>56.81</v>
+        <v>28.15</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>3.687</v>
+        <v>0.322</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>3.103</v>
+        <v>0.366</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4364,28 +4364,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.0241</v>
+        <v>0.295</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>3259600</v>
+        <v>3862100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="H87" t="n">
-        <v>26.29</v>
+        <v>49.15</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.902</v>
+        <v>0.295</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.967</v>
+        <v>0.295</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4409,28 +4409,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.97</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E88" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>3228400</v>
+        <v>3744700</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="H88" t="n">
-        <v>66.02</v>
+        <v>65</v>
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.797</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.883</v>
+        <v>0.774</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4454,28 +4454,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0.0196</v>
+        <v>3.79</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>-0.0257</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>3016200</v>
+        <v>3702600</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="H89" t="n">
-        <v>33.79</v>
+        <v>56.48</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.273</v>
+        <v>3.686</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.298</v>
+        <v>3.103</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4499,28 +4499,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.455</v>
+        <v>0.41</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.0111</v>
+        <v>0.0513</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>3004000</v>
+        <v>3680700</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.4</v>
+        <v>0.62</v>
       </c>
       <c r="H90" t="n">
-        <v>30.55</v>
+        <v>55.11</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.489</v>
+        <v>0.393</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.548</v>
+        <v>0.363</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4544,39 +4544,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>0.0672</v>
+        <v>1.42</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2932000</v>
+        <v>3667600</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="H91" t="n">
-        <v>44.76</v>
-      </c>
-      <c r="I91" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.29</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.718</v>
+        <v>1.644</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.782</v>
+        <v>1.918</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4589,28 +4589,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.355</v>
+        <v>0.335</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>0.0441</v>
+        <v>0.0308</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2897100</v>
+        <v>3652100</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>0.37</v>
       </c>
       <c r="H92" t="n">
-        <v>52.77</v>
+        <v>47.84</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.353</v>
+        <v>0.343</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.328</v>
+        <v>0.335</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4634,28 +4634,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.82</v>
+        <v>0.245</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>0.0061</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2890600</v>
+        <v>3627400</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.54</v>
+        <v>3.24</v>
       </c>
       <c r="H93" t="n">
-        <v>66.97</v>
+        <v>84.8</v>
       </c>
       <c r="I93" s="17" t="inlineStr">
         <is>
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.798</v>
+        <v>0.213</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.774</v>
+        <v>0.21</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4679,39 +4679,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.3</v>
+        <v>0.65</v>
       </c>
       <c r="E94" s="15" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.0317</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2873600</v>
+        <v>3437300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="H94" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.35</v>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.283</v>
+        <v>0.638</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.231</v>
+        <v>0.625</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4724,39 +4724,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.335</v>
+        <v>0.975</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>0.0308</v>
+        <v>0.0052</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2832400</v>
+        <v>3380700</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>47.84</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.08</v>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.343</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.335</v>
+        <v>0.883</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4769,28 +4769,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.15</v>
+        <v>6.83</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>0.0268</v>
+        <v>0.0119</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2803000</v>
+        <v>3379500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="H96" t="n">
-        <v>62.11</v>
+        <v>35.62</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.07</v>
+        <v>7.133</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4814,28 +4814,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0.0104</v>
+        <v>0.125</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2780500</v>
+        <v>3315200</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.26</v>
+        <v>2.21</v>
       </c>
       <c r="H97" t="n">
-        <v>35.19</v>
+        <v>41.39</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>7.132</v>
+        <v>0.129</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>7.56</v>
+        <v>0.13</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4859,28 +4859,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.68</v>
+        <v>1.17</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>0.0709</v>
+        <v>0.0446</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2760000</v>
+        <v>3234600</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.52</v>
+        <v>0.71</v>
       </c>
       <c r="H98" t="n">
-        <v>42.69</v>
+        <v>63.59</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.742</v>
+        <v>1.072</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4904,28 +4904,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>0.71</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0.0597</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2749400</v>
+        <v>3145100</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H99" t="n">
-        <v>50.4</v>
+        <v>43.22</v>
       </c>
       <c r="I99" s="17" t="inlineStr">
         <is>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.626</v>
+        <v>0.718</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.686</v>
+        <v>0.782</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4949,28 +4949,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0.06519999999999999</v>
+        <v>1.17</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2730000</v>
+        <v>3129400</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>2.44</v>
+        <v>0.4</v>
       </c>
       <c r="H100" t="n">
-        <v>84.8</v>
+        <v>36.42</v>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.213</v>
+        <v>1.222</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.21</v>
+        <v>1.31</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4994,39 +4994,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.0709</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2594800</v>
+        <v>3102400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>1.28</v>
+        <v>0.59</v>
       </c>
       <c r="H101" t="n">
-        <v>51.76</v>
-      </c>
-      <c r="I101" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.69</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.742</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5039,28 +5039,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.255</v>
+        <v>0.275</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>0.02</v>
+        <v>0.0185</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>2554700</v>
+        <v>3084000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="H102" t="n">
-        <v>41.5</v>
+        <v>45</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.27</v>
+        <v>0.287</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.29</v>
+        <v>0.283</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5084,28 +5084,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>-0.0097</v>
+        <v>0.355</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0.0441</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>2547900</v>
+        <v>3033800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="H103" t="n">
-        <v>31.45</v>
+        <v>52.77</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.537</v>
+        <v>0.353</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.328</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5129,28 +5129,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>-0.0167</v>
+        <v>1.29</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.0574</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>2534400</v>
+        <v>3007700</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.55</v>
+        <v>0.98</v>
       </c>
       <c r="H104" t="n">
-        <v>21.3</v>
+        <v>51.48</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.356</v>
+        <v>1.282</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.54</v>
+        <v>1.231</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5174,28 +5174,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0</v>
+        <v>4.39</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>2470400</v>
+        <v>2771200</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.31</v>
+        <v>0.54</v>
       </c>
       <c r="H105" t="n">
-        <v>36.42</v>
+        <v>50.13</v>
       </c>
       <c r="I105" s="17" t="inlineStr">
         <is>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.222</v>
+        <v>4.371</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.31</v>
+        <v>4.43</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5219,28 +5219,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>7.69</v>
+        <v>1.18</v>
       </c>
       <c r="E106" s="16" t="n">
-        <v>-0.0013</v>
+        <v>-0.0167</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>2426700</v>
+        <v>2746200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.85</v>
+        <v>0.59</v>
       </c>
       <c r="H106" t="n">
-        <v>39.05</v>
+        <v>21.3</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>7.824</v>
+        <v>1.356</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>7.858</v>
+        <v>1.54</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5264,39 +5264,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>0.0423</v>
+        <v>7.69</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>2271800</v>
+        <v>2707700</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.39</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H107" t="n">
-        <v>58.47</v>
-      </c>
-      <c r="I107" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.05</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>6.24</v>
+        <v>7.824</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>5.952</v>
+        <v>7.858</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5309,39 +5309,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.92</v>
+        <v>6.68</v>
       </c>
       <c r="E108" s="15" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.047</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>2212800</v>
+        <v>2674600</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H108" t="n">
-        <v>26.79</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.85</v>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.961</v>
+        <v>6.242</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.044</v>
+        <v>5.952</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>3.34</v>
+        <v>0.62</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>0.0245</v>
+        <v>0.0248</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>2182400</v>
+        <v>2633600</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="H109" t="n">
-        <v>87.79000000000001</v>
-      </c>
-      <c r="I109" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.89</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>2.916</v>
+        <v>0.667</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>2.485</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5399,28 +5399,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>0.0154</v>
+        <v>0.51</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>2173200</v>
+        <v>2628200</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.22</v>
+        <v>0.96</v>
       </c>
       <c r="H110" t="n">
-        <v>52.48</v>
+        <v>31.45</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>3.955</v>
+        <v>0.537</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>3.588</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5444,39 +5444,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>-0.018</v>
+        <v>0.255</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0.02</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>2172400</v>
+        <v>2612800</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>1.61</v>
+        <v>0.4</v>
       </c>
       <c r="H111" t="n">
-        <v>67.76000000000001</v>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.5</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>2.627</v>
+        <v>0.27</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>2.452</v>
+        <v>0.29</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5489,28 +5489,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0</v>
+        <v>0.925</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>2133500</v>
+        <v>2606200</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H112" t="n">
-        <v>51.48</v>
+        <v>29.55</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.865</v>
+        <v>0.961</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.86</v>
+        <v>1.044</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5534,39 +5534,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.57</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>0.0195</v>
+        <v>0.0089</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>2129200</v>
+        <v>2594800</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.35</v>
+        <v>1.28</v>
       </c>
       <c r="H113" t="n">
-        <v>33.14</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.76</v>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.692</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.757</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5579,28 +5579,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.62</v>
+        <v>2.79</v>
       </c>
       <c r="E114" s="15" t="n">
-        <v>0.0248</v>
+        <v>0.0109</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>2069600</v>
+        <v>2516200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H114" t="n">
-        <v>39.89</v>
+        <v>51.36</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5608,10 +5608,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.667</v>
+        <v>2.793</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>2.677</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5624,28 +5624,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.55</v>
+        <v>3.97</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.0179</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>2046500</v>
+        <v>2491800</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="H115" t="n">
-        <v>50.5</v>
+        <v>52.81</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.556</v>
+        <v>3.956</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.521</v>
+        <v>3.588</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5678,19 +5678,19 @@
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>0.0206</v>
+        <v>0.0155</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1970400</v>
+        <v>2445500</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.49</v>
+        <v>0.61</v>
       </c>
       <c r="H116" t="n">
-        <v>45.65</v>
+        <v>44.86</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -5714,28 +5714,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.865</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1958300</v>
+        <v>2378500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.21</v>
+        <v>0.79</v>
       </c>
       <c r="H117" t="n">
-        <v>51.91</v>
+        <v>51.48</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.794</v>
+        <v>0.865</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.677</v>
+        <v>0.86</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5768,19 +5768,19 @@
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="E118" s="16" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.018</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1952800</v>
+        <v>2268400</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="H118" t="n">
-        <v>53.75</v>
+        <v>52.14</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.083</v>
+        <v>1.082</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>1.05</v>
@@ -5804,38 +5804,40 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.39</v>
+        <v>0.545</v>
       </c>
       <c r="E119" s="15" t="n">
-        <v>0.0263</v>
+        <v>0.0481</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1925000</v>
+        <v>2233300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="H119" t="n">
-        <v>69.33</v>
-      </c>
-      <c r="I119" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.45</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="K119" s="9" t="n"/>
+        <v>0.555</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>0.52</v>
+      </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
     </row>
@@ -5847,39 +5849,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.23</v>
+        <v>1.58</v>
       </c>
       <c r="E120" s="15" t="n">
-        <v>0.0222</v>
+        <v>0.026</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1856400</v>
+        <v>2217100</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>5.34</v>
+        <v>0.36</v>
       </c>
       <c r="H120" t="n">
-        <v>65.31</v>
-      </c>
-      <c r="I120" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.63</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.225</v>
+        <v>1.693</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.225</v>
+        <v>1.757</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5892,40 +5894,38 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.845</v>
+        <v>0.39</v>
       </c>
       <c r="E121" s="15" t="n">
-        <v>0.0305</v>
+        <v>0.0263</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1817800</v>
+        <v>2209300</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="H121" t="n">
-        <v>41.84</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.33</v>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="K121" s="9" t="n">
-        <v>0.853</v>
-      </c>
+        <v>0.331</v>
+      </c>
+      <c r="K121" s="9" t="n"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
     </row>
@@ -5937,28 +5937,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.06</v>
+        <v>2.71</v>
       </c>
       <c r="E122" s="16" t="n">
-        <v>-0.0048</v>
+        <v>-0.0252</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1817100</v>
+        <v>2205200</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>9.859999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="H122" t="n">
-        <v>41.44</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.078</v>
+        <v>2.625</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>2.083</v>
+        <v>2.451</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5982,39 +5982,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.48</v>
+        <v>3.34</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>0.0213</v>
+        <v>0.0245</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1771300</v>
+        <v>2202300</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.21</v>
+        <v>0.68</v>
       </c>
       <c r="H123" t="n">
-        <v>40.66</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>87.79000000000001</v>
+      </c>
+      <c r="I123" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.501</v>
+        <v>2.916</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.521</v>
+        <v>2.485</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6027,28 +6027,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.09</v>
+        <v>0.755</v>
       </c>
       <c r="E124" s="15" t="n">
-        <v>0.0187</v>
+        <v>0.0486</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1738200</v>
+        <v>2095400</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="H124" t="n">
-        <v>43.04</v>
+        <v>54.29</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.142</v>
+        <v>0.742</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.105</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6072,39 +6072,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0</v>
+        <v>0.84</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1676100</v>
+        <v>2056800</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="H125" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I125" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.09</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>2.104</v>
+        <v>0.91</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>2.103</v>
+        <v>0.852</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6117,39 +6117,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>0</v>
+        <v>7.52</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1667200</v>
+        <v>2044800</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>42.76</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.9</v>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.287</v>
+        <v>7.563</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.283</v>
+        <v>7.745</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6162,28 +6162,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>3.76</v>
+        <v>0.835</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>0.0301</v>
+        <v>0.0121</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1613700</v>
+        <v>2016800</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H127" t="n">
-        <v>48.2</v>
+        <v>33.02</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>3.824</v>
+        <v>0.883</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>3.711</v>
+        <v>0.945</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6207,28 +6207,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.755</v>
+        <v>2.57</v>
       </c>
       <c r="E128" s="15" t="n">
-        <v>0.0486</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1602700</v>
+        <v>2012800</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H128" t="n">
-        <v>54.29</v>
+        <v>47.18</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.742</v>
+        <v>2.6</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>2.61</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6252,39 +6252,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1596700</v>
+        <v>1856400</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.27</v>
+        <v>5.34</v>
       </c>
       <c r="H129" t="n">
-        <v>35.52</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.31</v>
+      </c>
+      <c r="I129" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.762</v>
+        <v>0.225</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.874</v>
+        <v>0.225</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6297,39 +6297,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>0.0098</v>
+        <v>2.06</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1574000</v>
+        <v>1817100</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>1.15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H130" t="n">
-        <v>36.03</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.44</v>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.075</v>
+        <v>2.078</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.126</v>
+        <v>2.083</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6342,39 +6342,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.67</v>
+        <v>0.48</v>
       </c>
       <c r="E131" s="15" t="n">
-        <v>0.0229</v>
+        <v>0.0213</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1538200</v>
+        <v>1795800</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H131" t="n">
-        <v>58.73</v>
-      </c>
-      <c r="I131" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.66</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.649</v>
+        <v>0.501</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.521</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6387,39 +6387,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>7.51</v>
+        <v>1.09</v>
       </c>
       <c r="E132" s="15" t="n">
-        <v>0.004</v>
+        <v>0.0187</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1537300</v>
+        <v>1778300</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.61</v>
+        <v>0.49</v>
       </c>
       <c r="H132" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="I132" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.04</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>7.562</v>
+        <v>1.142</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>7.745</v>
+        <v>1.105</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6432,28 +6432,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>-0.0127</v>
+        <v>-0.0048</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1524500</v>
+        <v>1777900</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.44</v>
+        <v>0.12</v>
       </c>
       <c r="H133" t="n">
-        <v>59.79</v>
+        <v>45.87</v>
       </c>
       <c r="I133" s="17" t="inlineStr">
         <is>
@@ -6461,10 +6461,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>2.247</v>
+        <v>2.103</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>2.184</v>
+        <v>2.103</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6477,28 +6477,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>0.0121</v>
+        <v>1</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1506500</v>
+        <v>1746300</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.46</v>
+        <v>1.51</v>
       </c>
       <c r="H134" t="n">
-        <v>33.02</v>
+        <v>35.9</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.883</v>
+        <v>1.042</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.945</v>
+        <v>1.134</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6522,39 +6522,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="E135" s="16" t="n">
-        <v>-0.0178</v>
+        <v>3.75</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1477900</v>
+        <v>1737900</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.29</v>
+        <v>0.55</v>
       </c>
       <c r="H135" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I135" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.77</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>4.373</v>
+        <v>3.823</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>4.431</v>
+        <v>3.711</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6567,39 +6567,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="16" t="n">
-        <v>-0.0196</v>
+        <v>0.665</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>0.0153</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1473000</v>
+        <v>1688900</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1.28</v>
+        <v>0.62</v>
       </c>
       <c r="H136" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.79</v>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.042</v>
+        <v>0.649</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.134</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6612,28 +6612,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>HOCKSOON</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E137" s="15" t="n">
-        <v>0.0387</v>
+        <v>0.215</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>-0.0851</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1423400</v>
+        <v>1676200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.62</v>
+        <v>2.58</v>
       </c>
       <c r="H137" t="n">
-        <v>23.7</v>
+        <v>31.36</v>
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.912</v>
+        <v>0.238</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.063</v>
+        <v>0.276</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6657,28 +6657,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>0.0123</v>
+        <v>1.17</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1420300</v>
+        <v>1675200</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H138" t="n">
-        <v>42.99</v>
+        <v>50.65</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.432</v>
+        <v>1.172</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.437</v>
+        <v>1.143</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6702,39 +6702,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HOCKSOON</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.215</v>
+        <v>2.33</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>-0.0851</v>
+        <v>-0.0169</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1411100</v>
+        <v>1666800</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>2.17</v>
+        <v>0.48</v>
       </c>
       <c r="H139" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.82</v>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.238</v>
+        <v>2.246</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.276</v>
+        <v>2.184</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6747,28 +6747,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>2.57</v>
+        <v>10.72</v>
       </c>
       <c r="E140" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0408</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1387700</v>
+        <v>1654300</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.23</v>
+        <v>0.48</v>
       </c>
       <c r="H140" t="n">
-        <v>47.18</v>
+        <v>57.99</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>2.6</v>
+        <v>10.434</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>2.61</v>
+        <v>9.807</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6792,28 +6792,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>10.64</v>
+        <v>0.795</v>
       </c>
       <c r="E141" s="15" t="n">
-        <v>0.033</v>
+        <v>0.0258</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1384100</v>
+        <v>1636300</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="H141" t="n">
-        <v>56.81</v>
+        <v>20.98</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>10.426</v>
+        <v>0.911</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>9.805999999999999</v>
+        <v>1.063</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6852,10 +6852,10 @@
         <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1382400</v>
+        <v>1633000</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="H142" t="n">
         <v>49.59</v>
@@ -6882,28 +6882,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>0.0388</v>
+        <v>1.02</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1364900</v>
+        <v>1587700</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.3</v>
+        <v>1.16</v>
       </c>
       <c r="H143" t="n">
-        <v>50.18</v>
+        <v>32.98</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>7.306</v>
+        <v>1.074</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>6.915</v>
+        <v>1.126</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6927,28 +6927,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ABMB</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>4.52</v>
+        <v>7.24</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0.0022</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1345700</v>
+        <v>1540200</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1.21</v>
+        <v>0.34</v>
       </c>
       <c r="H144" t="n">
-        <v>34.03</v>
+        <v>50.38</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>4.621</v>
+        <v>7.307</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>4.766</v>
+        <v>6.915</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6972,28 +6972,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>0</v>
+        <v>5.47</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>0.04190000000000001</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1333200</v>
+        <v>1531000</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
       <c r="H145" t="n">
-        <v>36.07</v>
+        <v>50.3</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.251</v>
+        <v>5.486</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.272</v>
+        <v>5.384</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7017,28 +7017,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v>0.0314</v>
+        <v>0.235</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1317600</v>
+        <v>1513700</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="H146" t="n">
-        <v>44.65</v>
+        <v>36.07</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>2.082</v>
+        <v>0.251</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.993</v>
+        <v>0.272</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7062,28 +7062,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="E147" s="16" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0234</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1305200</v>
+        <v>1490300</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.19</v>
+        <v>0.78</v>
       </c>
       <c r="H147" t="n">
-        <v>52.11</v>
+        <v>21.18</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.173</v>
+        <v>1.377</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.143</v>
+        <v>1.454</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7107,28 +7107,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.66</v>
+        <v>1.48</v>
       </c>
       <c r="E148" s="15" t="n">
-        <v>0.0394</v>
+        <v>0.0137</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1288800</v>
+        <v>1476600</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>1.85</v>
+        <v>0.8</v>
       </c>
       <c r="H148" t="n">
-        <v>65.76000000000001</v>
+        <v>35.83</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7136,10 +7136,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.623</v>
+        <v>1.594</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.609</v>
+        <v>1.656</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7152,28 +7152,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>ABMB</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1.48</v>
+        <v>4.52</v>
       </c>
       <c r="E149" s="15" t="n">
-        <v>0.0137</v>
+        <v>0.0022</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1241100</v>
+        <v>1435200</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="H149" t="n">
-        <v>35.83</v>
+        <v>34.03</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>1.594</v>
+        <v>4.621</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>1.656</v>
+        <v>4.766</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7197,28 +7197,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E150" s="16" t="n">
-        <v>-0.0111</v>
+        <v>1.97</v>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>0.0314</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1224600</v>
+        <v>1429100</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="H150" t="n">
-        <v>47.29</v>
+        <v>44.65</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.912</v>
+        <v>2.082</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.882</v>
+        <v>1.993</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7242,39 +7242,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>-0.0213</v>
+        <v>4.22</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1206500</v>
+        <v>1428200</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>1.09</v>
+        <v>0.33</v>
       </c>
       <c r="H151" t="n">
-        <v>48.44</v>
-      </c>
-      <c r="I151" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.35</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.23</v>
+        <v>4.373</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.238</v>
+        <v>4.681</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7287,28 +7287,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>2.76</v>
+        <v>0.41</v>
       </c>
       <c r="E152" s="15" t="n">
-        <v>0.0073</v>
+        <v>0.0123</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1181600</v>
+        <v>1426200</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="H152" t="n">
-        <v>40.07</v>
+        <v>42.99</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>2.869</v>
+        <v>0.432</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>3.002</v>
+        <v>0.437</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7332,28 +7332,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>DESTINI</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E153" s="16" t="n">
-        <v>-0.0435</v>
+        <v>0.66</v>
+      </c>
+      <c r="E153" s="15" t="n">
+        <v>0.0394</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1160800</v>
+        <v>1358200</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>4.57</v>
+        <v>1.95</v>
       </c>
       <c r="H153" t="n">
-        <v>40.95</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.228</v>
+        <v>0.623</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.243</v>
+        <v>0.609</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7377,28 +7377,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>5.44</v>
+        <v>2.77</v>
       </c>
       <c r="E154" s="15" t="n">
-        <v>0.0362</v>
+        <v>0.0109</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1150500</v>
+        <v>1346900</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H154" t="n">
-        <v>49.61</v>
+        <v>40.89</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>5.483</v>
+        <v>2.87</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>5.384</v>
+        <v>3.002</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7422,39 +7422,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E155" s="16" t="n">
-        <v>-0.0182</v>
+        <v>5.25</v>
+      </c>
+      <c r="E155" s="15" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>1120400</v>
+        <v>1335100</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H155" t="n">
-        <v>44.32</v>
-      </c>
-      <c r="I155" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.72</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.272</v>
+        <v>5.441</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>0.276</v>
+        <v>5.778</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7467,39 +7467,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E156" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.89</v>
+      </c>
+      <c r="E156" s="16" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>1120100</v>
+        <v>1325700</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="H156" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="I156" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.29</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.356</v>
+        <v>0.912</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.384</v>
+        <v>0.882</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7512,28 +7512,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>0</v>
+        <v>1.34</v>
+      </c>
+      <c r="E157" s="15" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>1118200</v>
+        <v>1279600</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H157" t="n">
-        <v>56.16</v>
+        <v>41.93</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.266</v>
+        <v>1.36</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.257</v>
+        <v>1.342</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7566,19 +7566,19 @@
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>13.02</v>
+        <v>13</v>
       </c>
       <c r="E158" s="16" t="n">
-        <v>-0.0031</v>
+        <v>-0.0046</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>1089800</v>
+        <v>1256600</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H158" t="n">
-        <v>46.76</v>
+        <v>45.78</v>
       </c>
       <c r="I158" s="17" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>13.02</v>
+        <v>13.018</v>
       </c>
       <c r="K158" s="9" t="n">
         <v>13.37</v>
@@ -7602,28 +7602,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E159" s="16" t="n">
-        <v>-0.0156</v>
+        <v>8.460000000000001</v>
+      </c>
+      <c r="E159" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>1065100</v>
+        <v>1254200</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="H159" t="n">
-        <v>21.98</v>
+        <v>45.94</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.378</v>
+        <v>8.592000000000001</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.454</v>
+        <v>8.68</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7647,39 +7647,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E160" s="10" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>1047200</v>
+        <v>1231500</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.58</v>
+        <v>1.12</v>
       </c>
       <c r="H160" t="n">
-        <v>33</v>
-      </c>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.44</v>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.839</v>
+        <v>0.23</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.859</v>
+        <v>0.238</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7692,28 +7692,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="E161" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.27</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1043000</v>
+        <v>1218200</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="H161" t="n">
-        <v>45.94</v>
+        <v>56.16</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>8.592000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>8.68</v>
+        <v>0.257</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7737,28 +7737,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SCGM</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.335</v>
+        <v>4.15</v>
       </c>
       <c r="E162" s="15" t="n">
-        <v>0.0152</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>1016100</v>
+        <v>1200300</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>1.35</v>
+        <v>0.49</v>
       </c>
       <c r="H162" t="n">
-        <v>52.15</v>
+        <v>45.91</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.334</v>
+        <v>4.246</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>0.324</v>
+        <v>4.309</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7782,28 +7782,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>DESTINI</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E163" s="15" t="n">
-        <v>0.0407</v>
+        <v>0.22</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>1012200</v>
+        <v>1160800</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.3</v>
+        <v>4.57</v>
       </c>
       <c r="H163" t="n">
-        <v>35.5</v>
+        <v>40.95</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.707</v>
+        <v>0.228</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.742</v>
+        <v>0.243</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7827,39 +7827,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="E164" s="15" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.27</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>1005400</v>
+        <v>1120400</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.24</v>
+        <v>1.02</v>
       </c>
       <c r="H164" t="n">
-        <v>36.95</v>
-      </c>
-      <c r="I164" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.32</v>
+      </c>
+      <c r="I164" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>4.375</v>
+        <v>0.272</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>4.681</v>
+        <v>0.276</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7872,39 +7872,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E165" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E165" s="15" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>984300</v>
+        <v>1120100</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.48</v>
+        <v>0.72</v>
       </c>
       <c r="H165" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="I165" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.59</v>
+      </c>
+      <c r="I165" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.359</v>
+        <v>0.356</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.341</v>
+        <v>0.384</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7917,28 +7917,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>5.28</v>
+        <v>0.645</v>
       </c>
       <c r="E166" s="15" t="n">
-        <v>0.0154</v>
+        <v>0.0488</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>969900</v>
+        <v>1114800</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.76</v>
+        <v>0.33</v>
       </c>
       <c r="H166" t="n">
-        <v>36.82</v>
+        <v>36.61</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>5.444</v>
+        <v>0.707</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>5.778</v>
+        <v>0.742</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7962,28 +7962,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E167" s="15" t="n">
-        <v>0.05309999999999999</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>967800</v>
+        <v>1052700</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.22</v>
+        <v>0.59</v>
       </c>
       <c r="H167" t="n">
-        <v>50.6</v>
+        <v>33</v>
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
@@ -7991,10 +7991,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.595</v>
+        <v>0.839</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.586</v>
+        <v>0.859</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8007,28 +8007,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E168" s="10" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>939400</v>
+        <v>1020900</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.4</v>
+        <v>1.36</v>
       </c>
       <c r="H168" t="n">
-        <v>30.05</v>
+        <v>52.15</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8036,10 +8036,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>1.22</v>
+        <v>0.334</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.306</v>
+        <v>0.324</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8052,28 +8052,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="E169" s="15" t="n">
-        <v>0.04019999999999999</v>
+        <v>1.14</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>924700</v>
+        <v>979000</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H169" t="n">
-        <v>45.57</v>
+        <v>28.87</v>
       </c>
       <c r="I169" s="13" t="inlineStr">
         <is>
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>4.245</v>
+        <v>1.219</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>4.309</v>
+        <v>1.306</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8097,39 +8097,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="E170" s="15" t="n">
-        <v>0.0388</v>
+        <v>0.0442</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>890500</v>
+        <v>973800</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="H170" t="n">
-        <v>48.23</v>
-      </c>
-      <c r="I170" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.58</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.084</v>
+        <v>0.594</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.096</v>
+        <v>0.586</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         <v>0.0066</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>888700</v>
+        <v>956700</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="H171" t="n">
         <v>61.75</v>
@@ -8187,39 +8187,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E172" s="15" t="n">
-        <v>0.004699999999999999</v>
+        <v>1.98</v>
+      </c>
+      <c r="E172" s="16" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>859700</v>
+        <v>939300</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.41</v>
+        <v>1.19</v>
       </c>
       <c r="H172" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="I172" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.83</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>2.113</v>
+        <v>2.027</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>2.07</v>
+        <v>2.075</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8232,39 +8232,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E173" s="16" t="n">
-        <v>-0.005</v>
+        <v>1.06</v>
+      </c>
+      <c r="E173" s="15" t="n">
+        <v>0.0291</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>855200</v>
+        <v>934500</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H173" t="n">
-        <v>30.83</v>
-      </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.11</v>
+      </c>
+      <c r="I173" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>2.027</v>
+        <v>1.083</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>2.075</v>
+        <v>1.096</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8277,39 +8277,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>IGBREIT</t>
+          <t>SUPERLN</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>2.77</v>
+        <v>0.95</v>
       </c>
       <c r="E174" s="15" t="n">
-        <v>0.0147</v>
+        <v>0.0215</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>803400</v>
+        <v>900200</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.59</v>
+        <v>2.21</v>
       </c>
       <c r="H174" t="n">
-        <v>51.31</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.05</v>
+      </c>
+      <c r="I174" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>2.757</v>
+        <v>0.872</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>2.766</v>
+        <v>0.846</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8322,39 +8322,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SUPERLN</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="E175" s="15" t="n">
-        <v>0.0215</v>
+        <v>0.0345</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>800100</v>
+        <v>889600</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>1.96</v>
+        <v>0.28</v>
       </c>
       <c r="H175" t="n">
-        <v>69.05</v>
-      </c>
-      <c r="I175" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.82</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>0.872</v>
+        <v>1.229</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>0.846</v>
+        <v>1.085</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8376,19 +8376,19 @@
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="E176" s="15" t="n">
-        <v>0.0317</v>
+        <v>0.0238</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>799800</v>
+        <v>881400</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H176" t="n">
-        <v>55.45</v>
+        <v>54.64</v>
       </c>
       <c r="I176" s="13" t="inlineStr">
         <is>
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>1.265</v>
+        <v>1.264</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>1.179</v>
+        <v>1.178</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8412,39 +8412,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.2</v>
+        <v>2.13</v>
       </c>
       <c r="E177" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>770700</v>
+        <v>859700</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="H177" t="n">
-        <v>49.82</v>
-      </c>
-      <c r="I177" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.56</v>
+      </c>
+      <c r="I177" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>1.229</v>
+        <v>2.113</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.085</v>
+        <v>2.07</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8457,39 +8457,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>0</v>
+        <v>4.39</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>762900</v>
+        <v>856400</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="H178" t="n">
-        <v>75.22</v>
-      </c>
-      <c r="I178" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.82</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.593</v>
+        <v>4.573</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.535</v>
+        <v>4.485</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8502,28 +8502,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>IGBREIT</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E179" s="16" t="n">
-        <v>-0.0178</v>
+        <v>2.77</v>
+      </c>
+      <c r="E179" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>753900</v>
+        <v>839600</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.95</v>
+        <v>0.62</v>
       </c>
       <c r="H179" t="n">
-        <v>31.92</v>
+        <v>51.31</v>
       </c>
       <c r="I179" s="13" t="inlineStr">
         <is>
@@ -8531,10 +8531,10 @@
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>1.747</v>
+        <v>2.757</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>1.785</v>
+        <v>2.766</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8547,28 +8547,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E180" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.66</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>745100</v>
+        <v>832500</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="H180" t="n">
-        <v>55.02</v>
+        <v>75.22</v>
       </c>
       <c r="I180" s="17" t="inlineStr">
         <is>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.633</v>
+        <v>0.593</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.631</v>
+        <v>0.535</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8592,39 +8592,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E181" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.635</v>
+      </c>
+      <c r="E181" s="16" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>703600</v>
+        <v>815100</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="H181" t="n">
-        <v>50.58</v>
-      </c>
-      <c r="I181" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.02</v>
+      </c>
+      <c r="I181" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>3.162</v>
+        <v>0.633</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>2.911</v>
+        <v>0.631</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8637,39 +8637,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E182" s="10" t="n">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="E182" s="16" t="n">
+        <v>-0.0237</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>666800</v>
+        <v>781200</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.39</v>
+        <v>0.99</v>
       </c>
       <c r="H182" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="I182" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.9</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>0.892</v>
+        <v>1.746</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>0.906</v>
+        <v>1.785</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8682,39 +8682,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0360</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SAG</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E183" s="16" t="n">
-        <v>-0.0234</v>
+        <v>1.38</v>
+      </c>
+      <c r="E183" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>652200</v>
+        <v>769500</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>3.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H183" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="I183" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.62</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>0.637</v>
+        <v>1.479</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>0.644</v>
+        <v>1.502</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8727,28 +8727,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="E184" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>651700</v>
+        <v>734100</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.34</v>
+        <v>0.11</v>
       </c>
       <c r="H184" t="n">
-        <v>42.09</v>
+        <v>50.96</v>
       </c>
       <c r="I184" s="13" t="inlineStr">
         <is>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>0.727</v>
+        <v>1.106</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>0.743</v>
+        <v>0.903</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8772,39 +8772,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E185" s="15" t="n">
-        <v>0.0221</v>
+        <v>0.89</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>643900</v>
+        <v>731700</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H185" t="n">
-        <v>32.89</v>
-      </c>
-      <c r="I185" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.71</v>
+      </c>
+      <c r="I185" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>1.48</v>
+        <v>0.892</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>1.502</v>
+        <v>0.906</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8826,19 +8826,19 @@
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>21.5</v>
+        <v>21.52</v>
       </c>
       <c r="E186" s="15" t="n">
-        <v>0.0142</v>
+        <v>0.0151</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>640100</v>
+        <v>731400</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H186" t="n">
-        <v>45.39</v>
+        <v>45.78</v>
       </c>
       <c r="I186" s="13" t="inlineStr">
         <is>
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>21.638</v>
+        <v>21.64</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>22.094</v>
+        <v>22.095</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8862,28 +8862,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E187" s="16" t="n">
-        <v>-0.0174</v>
+        <v>3.11</v>
+      </c>
+      <c r="E187" s="15" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>619600</v>
+        <v>715800</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>0.13</v>
+        <v>0.47</v>
       </c>
       <c r="H187" t="n">
-        <v>55.51</v>
+        <v>49.84</v>
       </c>
       <c r="I187" s="13" t="inlineStr">
         <is>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>2.796</v>
+        <v>3.161</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>2.265</v>
+        <v>2.911</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8907,28 +8907,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E188" s="15" t="n">
-        <v>0.0508</v>
+        <v>2.5</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>604300</v>
+        <v>711800</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="H188" t="n">
-        <v>51.36</v>
+        <v>41.25</v>
       </c>
       <c r="I188" s="13" t="inlineStr">
         <is>
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>2.5</v>
+        <v>2.545</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>2.267</v>
+        <v>2.669</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8952,28 +8952,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E189" s="10" t="n">
-        <v>0</v>
+        <v>2.84</v>
+      </c>
+      <c r="E189" s="16" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>594900</v>
+        <v>704100</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="H189" t="n">
-        <v>50.96</v>
+        <v>56.44</v>
       </c>
       <c r="I189" s="13" t="inlineStr">
         <is>
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>1.106</v>
+        <v>2.798</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>0.903</v>
+        <v>2.266</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -8997,28 +8997,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E190" s="10" t="n">
-        <v>0</v>
+        <v>2.46</v>
+      </c>
+      <c r="E190" s="15" t="n">
+        <v>0.0424</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>592000</v>
+        <v>695000</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="H190" t="n">
-        <v>41.25</v>
+        <v>50.42</v>
       </c>
       <c r="I190" s="13" t="inlineStr">
         <is>
@@ -9026,10 +9026,10 @@
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>2.545</v>
+        <v>2.498</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>2.669</v>
+        <v>2.267</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9042,28 +9042,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E191" s="16" t="n">
-        <v>-0.02</v>
+        <v>0.71</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>574600</v>
+        <v>686000</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="H191" t="n">
-        <v>40.26</v>
+        <v>42.09</v>
       </c>
       <c r="I191" s="13" t="inlineStr">
         <is>
@@ -9071,10 +9071,10 @@
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>4.574</v>
+        <v>0.727</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>4.486</v>
+        <v>0.743</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
@@ -9087,28 +9087,28 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>0360</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>WELLCHIP</t>
+          <t>SAG</t>
         </is>
       </c>
       <c r="D192" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E192" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.625</v>
+      </c>
+      <c r="E192" s="16" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>572200</v>
+        <v>652200</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>0.7</v>
+        <v>3.65</v>
       </c>
       <c r="H192" t="n">
-        <v>42.34</v>
+        <v>43.91</v>
       </c>
       <c r="I192" s="17" t="inlineStr">
         <is>
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="J192" s="9" t="n">
-        <v>1.096</v>
+        <v>0.637</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>1.127</v>
+        <v>0.644</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="14" t="inlineStr"/>
@@ -9132,28 +9132,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D193" s="9" t="n">
-        <v>0.765</v>
+        <v>2.96</v>
       </c>
       <c r="E193" s="15" t="n">
-        <v>0.0338</v>
+        <v>0.0207</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>567000</v>
+        <v>616700</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H193" t="n">
-        <v>48.95</v>
+        <v>49.18</v>
       </c>
       <c r="I193" s="13" t="inlineStr">
         <is>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="J193" s="9" t="n">
-        <v>0.771</v>
+        <v>3.01</v>
       </c>
       <c r="K193" s="9" t="n">
-        <v>0.771</v>
+        <v>2.859</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="14" t="inlineStr"/>
@@ -9177,28 +9177,28 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D194" s="9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E194" s="16" t="n">
-        <v>-0.0187</v>
+        <v>2.04</v>
+      </c>
+      <c r="E194" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>563400</v>
+        <v>602400</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="H194" t="n">
-        <v>30.9</v>
+        <v>41.69</v>
       </c>
       <c r="I194" s="13" t="inlineStr">
         <is>
@@ -9206,10 +9206,10 @@
         </is>
       </c>
       <c r="J194" s="9" t="n">
-        <v>5.526</v>
+        <v>2.11</v>
       </c>
       <c r="K194" s="9" t="n">
-        <v>5.779</v>
+        <v>2.265</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="14" t="inlineStr"/>
@@ -9222,28 +9222,28 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D195" s="9" t="n">
-        <v>2.05</v>
+        <v>0.76</v>
       </c>
       <c r="E195" s="15" t="n">
-        <v>0.0049</v>
+        <v>0.027</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>543400</v>
+        <v>602000</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="H195" t="n">
-        <v>42.57</v>
+        <v>47.94</v>
       </c>
       <c r="I195" s="13" t="inlineStr">
         <is>
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="J195" s="9" t="n">
-        <v>2.111</v>
+        <v>0.771</v>
       </c>
       <c r="K195" s="9" t="n">
-        <v>2.265</v>
+        <v>0.771</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="14" t="inlineStr"/>
@@ -9267,39 +9267,39 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>SCIENTX</t>
         </is>
       </c>
       <c r="D196" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E196" s="16" t="n">
-        <v>-0.0097</v>
+        <v>3.54</v>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>520000</v>
+        <v>599000</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>0.75</v>
+        <v>1.12</v>
       </c>
       <c r="H196" t="n">
-        <v>57.62</v>
-      </c>
-      <c r="I196" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.02</v>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J196" s="9" t="n">
-        <v>1.008</v>
+        <v>3.643</v>
       </c>
       <c r="K196" s="9" t="n">
-        <v>0.986</v>
+        <v>3.695</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" s="14" t="inlineStr"/>
@@ -9312,28 +9312,28 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D197" s="9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E197" s="15" t="n">
-        <v>0.0207</v>
+        <v>5.26</v>
+      </c>
+      <c r="E197" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>500000</v>
+        <v>591500</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="H197" t="n">
-        <v>49.18</v>
+        <v>31.23</v>
       </c>
       <c r="I197" s="13" t="inlineStr">
         <is>
@@ -9341,16 +9341,376 @@
         </is>
       </c>
       <c r="J197" s="9" t="n">
-        <v>3.01</v>
+        <v>5.527</v>
       </c>
       <c r="K197" s="9" t="n">
-        <v>2.859</v>
+        <v>5.779</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" s="14" t="inlineStr"/>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F198" s="11" t="n">
+        <v>578800</v>
+      </c>
+      <c r="G198" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H198" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="I198" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J198" s="9" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="K198" s="9" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" s="14" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5325</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>WELLCHIP</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E199" s="15" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>577200</v>
+      </c>
+      <c r="G199" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H199" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="I199" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J199" s="9" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="K199" s="9" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" s="14" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E200" s="16" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F200" s="11" t="n">
+        <v>559300</v>
+      </c>
+      <c r="G200" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H200" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="I200" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J200" s="9" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="K200" s="9" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" s="14" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E201" s="16" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="F201" s="11" t="n">
+        <v>553600</v>
+      </c>
+      <c r="G201" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H201" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="I201" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J201" s="9" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="K201" s="9" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" s="14" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" s="11" t="n">
+        <v>530400</v>
+      </c>
+      <c r="G202" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H202" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="I202" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J202" s="9" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="K202" s="9" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" s="14" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E203" s="16" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="F203" s="11" t="n">
+        <v>520000</v>
+      </c>
+      <c r="G203" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H203" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="I203" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J203" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="K203" s="9" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" s="14" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>MFCB</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E204" s="16" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F204" s="11" t="n">
+        <v>509800</v>
+      </c>
+      <c r="G204" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H204" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I204" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J204" s="9" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="K204" s="9" t="n">
+        <v>2.847</v>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" s="14" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>7005</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>BIG</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E205" s="15" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>502200</v>
+      </c>
+      <c r="G205" s="12" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="H205" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="I205" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J205" s="9" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K205" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M197"/>
+  <autoFilter ref="A1:M205"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>